--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\data\items\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAA6783-A75B-4F4F-81AB-EB72B570BAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAEE410-1652-4FDD-88CE-14447CBC9653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="Q4" s="41"/>
       <c r="R4">
-        <f>J4*200+600</f>
+        <f t="shared" ref="R4:R16" si="0">J4*200+600</f>
         <v>800</v>
       </c>
       <c r="S4">
@@ -14529,11 +14529,11 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K15" si="0" xml:space="preserve"> (J5- 1) * (J5 - 1) * (J5 - 1) + 1</f>
+        <f t="shared" ref="K5:K15" si="1" xml:space="preserve"> (J5- 1) * (J5 - 1) * (J5 - 1) + 1</f>
         <v>2</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L15" si="1">_xlfn.FLOOR.MATH(0.5*(J5-1)*(J5-1)*(J5-1)+1)</f>
+        <f t="shared" ref="L5:L15" si="2">_xlfn.FLOOR.MATH(0.5*(J5-1)*(J5-1)*(J5-1)+1)</f>
         <v>1</v>
       </c>
       <c r="M5">
@@ -14545,23 +14545,23 @@
         <v>1</v>
       </c>
       <c r="O5" s="41">
-        <f t="shared" ref="O5:O16" si="2">0.25*(1+(J5-1)^4.2/216)-1</f>
+        <f t="shared" ref="O5:O16" si="3">0.25*(1+(J5-1)^4.2/216)-1</f>
         <v>-0.74884259259259256</v>
       </c>
       <c r="P5" s="41">
-        <f t="shared" ref="P5:P16" si="3">0.5*(1+(J5-1)^4.2/216)-0.7</f>
+        <f t="shared" ref="P5:P16" si="4">0.5*(1+(J5-1)^4.2/216)-0.7</f>
         <v>-0.19768518518518519</v>
       </c>
       <c r="Q5" s="41">
-        <f t="shared" ref="Q5:Q16" si="4">O5/M5</f>
+        <f t="shared" ref="Q5:Q16" si="5">O5/M5</f>
         <v>-0.74884259259259256</v>
       </c>
       <c r="R5">
-        <f>J5*200+600</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S16" si="5">M5*R5</f>
+        <f t="shared" ref="S5:S16" si="6">M5*R5</f>
         <v>1000</v>
       </c>
       <c r="T5" s="41">
@@ -14582,11 +14582,11 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="M6">
@@ -14598,35 +14598,35 @@
         <v>2</v>
       </c>
       <c r="O6" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.72872780824079564</v>
       </c>
       <c r="P6" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.15745561648159123</v>
       </c>
       <c r="Q6" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.24290926941359856</v>
       </c>
       <c r="R6">
-        <f>J6*200+600</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="S6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3600</v>
       </c>
       <c r="T6" s="41">
-        <f t="shared" ref="T6:T16" si="6">O6/N6</f>
+        <f t="shared" ref="T6:T16" si="7">O6/N6</f>
         <v>-0.36436390412039782</v>
       </c>
       <c r="U6" s="41">
-        <f t="shared" ref="U6:U16" si="7">P6/M6</f>
+        <f t="shared" ref="U6:U16" si="8">P6/M6</f>
         <v>-5.2485205493863742E-2</v>
       </c>
       <c r="V6" s="41">
-        <f t="shared" ref="V6:V15" si="8">P6/N6</f>
+        <f t="shared" ref="V6:V15" si="9">P6/N6</f>
         <v>-7.8727808240795616E-2</v>
       </c>
     </row>
@@ -14635,11 +14635,11 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="M7">
@@ -14651,35 +14651,35 @@
         <v>7</v>
       </c>
       <c r="O7" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.63321272441104515</v>
       </c>
       <c r="P7" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3574551177909751E-2</v>
       </c>
       <c r="Q7" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-5.276772703425376E-2</v>
       </c>
       <c r="R7">
-        <f>J7*200+600</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="S7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16800</v>
       </c>
       <c r="T7" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9.0458960630149313E-2</v>
       </c>
       <c r="U7" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.7978792648258124E-3</v>
       </c>
       <c r="V7" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.7963644539871075E-3</v>
       </c>
     </row>
@@ -14691,11 +14691,11 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="M8">
@@ -14707,35 +14707,35 @@
         <v>21</v>
       </c>
       <c r="O8" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.35903469310432778</v>
       </c>
       <c r="P8" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.58193061379134448</v>
       </c>
       <c r="Q8" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-8.9758673276081943E-3</v>
       </c>
       <c r="R8">
-        <f>J8*200+600</f>
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="S8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>64000</v>
       </c>
       <c r="T8" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.7096890147825134E-2</v>
       </c>
       <c r="U8" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4548265344783613E-2</v>
       </c>
       <c r="V8" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.7710981609111642E-2</v>
       </c>
     </row>
@@ -14750,11 +14750,11 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="M9">
@@ -14766,35 +14766,35 @@
         <v>54</v>
       </c>
       <c r="O9" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.24806833149682728</v>
       </c>
       <c r="P9" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.7961366629936546</v>
       </c>
       <c r="Q9" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3625555380650215E-3</v>
       </c>
       <c r="R9">
-        <f>J9*200+600</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="S9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>189000</v>
       </c>
       <c r="T9" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5938579906819868E-3</v>
       </c>
       <c r="U9" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7106063457082425E-2</v>
       </c>
       <c r="V9" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.3261790055438049E-2</v>
       </c>
     </row>
@@ -14810,11 +14810,11 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>217</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="M10">
@@ -14826,35 +14826,35 @@
         <v>117</v>
       </c>
       <c r="O10" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.396453621657884</v>
       </c>
       <c r="P10" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.0929072433157678</v>
       </c>
       <c r="Q10" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6.0452537734107534E-3</v>
       </c>
       <c r="R10">
-        <f>J10*200+600</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="S10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>462000</v>
       </c>
       <c r="T10" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.1935501039810975E-2</v>
       </c>
       <c r="U10" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7718213174527132E-2</v>
       </c>
       <c r="V10" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.4982113190733057E-2</v>
       </c>
     </row>
@@ -14870,11 +14870,11 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>344</v>
       </c>
       <c r="L11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="M11">
@@ -14886,35 +14886,35 @@
         <v>226</v>
       </c>
       <c r="O11" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.3510779641070823</v>
       </c>
       <c r="P11" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.0021559282141652</v>
       </c>
       <c r="Q11" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7.4800847413104511E-3</v>
       </c>
       <c r="R11">
-        <f>J11*200+600</f>
+        <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="S11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>985600</v>
       </c>
       <c r="T11" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.4827778602243727E-2</v>
       </c>
       <c r="U11" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7861955196906618E-2</v>
       </c>
       <c r="V11" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5407769593867988E-2</v>
       </c>
     </row>
@@ -14923,18 +14923,18 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <f t="shared" ref="D12:D18" si="9">2500+C12*2500</f>
+        <f t="shared" ref="D12:D18" si="10">2500+C12*2500</f>
         <v>10000</v>
       </c>
       <c r="J12">
         <v>9</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>513</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>257</v>
       </c>
       <c r="M12">
@@ -14946,35 +14946,35 @@
         <v>398</v>
       </c>
       <c r="O12" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.4356192782715125</v>
       </c>
       <c r="P12" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.171238556543026</v>
       </c>
       <c r="Q12" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.125781917009486E-3</v>
       </c>
       <c r="R12">
-        <f>J12*200+600</f>
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="S12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1900800</v>
       </c>
       <c r="T12" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6169897684099276E-2</v>
       </c>
       <c r="U12" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7892977975433114E-2</v>
       </c>
       <c r="V12" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5606127026490013E-2</v>
       </c>
     </row>
@@ -14983,18 +14983,18 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12500</v>
       </c>
       <c r="J13">
         <v>10</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>730</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>365</v>
       </c>
       <c r="M13">
@@ -15006,35 +15006,35 @@
         <v>655</v>
       </c>
       <c r="O13" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.034327326919785</v>
       </c>
       <c r="P13" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>23.36865465383957</v>
       </c>
       <c r="Q13" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4554232390189922E-3</v>
       </c>
       <c r="R13">
-        <f>J13*200+600</f>
+        <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="S13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3393000</v>
       </c>
       <c r="T13" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6846301262472954E-2</v>
       </c>
       <c r="U13" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7907015060413464E-2</v>
       </c>
       <c r="V13" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5677335349373389E-2</v>
       </c>
     </row>
@@ -15043,18 +15043,18 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15000</v>
       </c>
       <c r="J14">
         <v>11</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1001</v>
       </c>
       <c r="L14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>501</v>
       </c>
       <c r="M14">
@@ -15066,35 +15066,35 @@
         <v>1020</v>
       </c>
       <c r="O14" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17.593671209040679</v>
       </c>
       <c r="P14" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>36.487342418081354</v>
       </c>
       <c r="Q14" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.6455386776612669E-3</v>
       </c>
       <c r="R14">
-        <f>J14*200+600</f>
+        <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="S14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5698000</v>
       </c>
       <c r="T14" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.7248697263765371E-2</v>
       </c>
       <c r="U14" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7929897994143171E-2</v>
       </c>
       <c r="V14" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.577190433145231E-2</v>
       </c>
     </row>
@@ -15103,18 +15103,18 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17500</v>
       </c>
       <c r="J15">
         <v>12</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1332</v>
       </c>
       <c r="L15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>666</v>
       </c>
       <c r="M15">
@@ -15126,35 +15126,35 @@
         <v>1521</v>
       </c>
       <c r="O15" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26.623828068826533</v>
       </c>
       <c r="P15" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>54.547656137653064</v>
       </c>
       <c r="Q15" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.7693768342643388E-3</v>
       </c>
       <c r="R15">
-        <f>J15*200+600</f>
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
       <c r="S15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9108000</v>
       </c>
       <c r="T15" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.7504160466026649E-2</v>
       </c>
       <c r="U15" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.7966948661941061E-2</v>
       </c>
       <c r="V15" s="41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.586302178675415E-2</v>
       </c>
     </row>
@@ -15163,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20000</v>
       </c>
       <c r="J16">
@@ -15178,31 +15178,31 @@
         <v>2187</v>
       </c>
       <c r="O16" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38.700043908413448</v>
       </c>
       <c r="P16" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>78.700087816826894</v>
       </c>
       <c r="Q16" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.8599001621825664E-3</v>
       </c>
       <c r="R16">
-        <f>J16*200+600</f>
+        <f t="shared" si="0"/>
         <v>3200</v>
       </c>
       <c r="S16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13977600</v>
       </c>
       <c r="T16" s="41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.7695493328035414E-2</v>
       </c>
       <c r="U16" s="41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.8017419371984179E-2</v>
       </c>
       <c r="V16" s="41">
@@ -15215,7 +15215,7 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22500</v>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25000</v>
       </c>
     </row>
@@ -15242,7 +15242,7 @@
         <v>11</v>
       </c>
       <c r="D20">
-        <f t="shared" ref="D20:D58" si="10">C20*5000-20000</f>
+        <f t="shared" ref="D20:D58" si="11">C20*5000-20000</f>
         <v>35000</v>
       </c>
     </row>
@@ -15251,7 +15251,7 @@
         <v>12</v>
       </c>
       <c r="D21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>40000</v>
       </c>
     </row>
@@ -15260,7 +15260,7 @@
         <v>13</v>
       </c>
       <c r="D22">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>45000</v>
       </c>
     </row>
@@ -15269,7 +15269,7 @@
         <v>14</v>
       </c>
       <c r="D23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>50000</v>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
         <v>15</v>
       </c>
       <c r="D24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>55000</v>
       </c>
     </row>
@@ -15287,7 +15287,7 @@
         <v>16</v>
       </c>
       <c r="D25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>60000</v>
       </c>
     </row>
@@ -15296,7 +15296,7 @@
         <v>17</v>
       </c>
       <c r="D26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>65000</v>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         <v>18</v>
       </c>
       <c r="D27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>70000</v>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
         <v>19</v>
       </c>
       <c r="D28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>75000</v>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
         <v>20</v>
       </c>
       <c r="D29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>80000</v>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
         <v>21</v>
       </c>
       <c r="D30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>85000</v>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
         <v>22</v>
       </c>
       <c r="D31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>90000</v>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
         <v>23</v>
       </c>
       <c r="D32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>95000</v>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
         <v>24</v>
       </c>
       <c r="D33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>100000</v>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>105000</v>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
         <v>26</v>
       </c>
       <c r="D35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>110000</v>
       </c>
     </row>
@@ -15386,7 +15386,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>115000</v>
       </c>
     </row>
@@ -15395,7 +15395,7 @@
         <v>28</v>
       </c>
       <c r="D37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>120000</v>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
         <v>29</v>
       </c>
       <c r="D38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>125000</v>
       </c>
     </row>
@@ -15413,7 +15413,7 @@
         <v>30</v>
       </c>
       <c r="D39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>130000</v>
       </c>
     </row>
@@ -15422,7 +15422,7 @@
         <v>31</v>
       </c>
       <c r="D40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>135000</v>
       </c>
     </row>
@@ -15431,7 +15431,7 @@
         <v>32</v>
       </c>
       <c r="D41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>140000</v>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
         <v>33</v>
       </c>
       <c r="D42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>145000</v>
       </c>
     </row>
@@ -15458,7 +15458,7 @@
         <v>35</v>
       </c>
       <c r="D44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>155000</v>
       </c>
     </row>
@@ -15467,7 +15467,7 @@
         <v>36</v>
       </c>
       <c r="D45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>160000</v>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
         <v>37</v>
       </c>
       <c r="D46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>165000</v>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>170000</v>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
         <v>39</v>
       </c>
       <c r="D48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>175000</v>
       </c>
     </row>
@@ -15503,7 +15503,7 @@
         <v>40</v>
       </c>
       <c r="D49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>180000</v>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
         <v>41</v>
       </c>
       <c r="D50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>185000</v>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
         <v>42</v>
       </c>
       <c r="D51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>190000</v>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
         <v>43</v>
       </c>
       <c r="D52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>195000</v>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
         <v>44</v>
       </c>
       <c r="D53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200000</v>
       </c>
     </row>
@@ -15548,7 +15548,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>205000</v>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
         <v>46</v>
       </c>
       <c r="D55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>210000</v>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
         <v>47</v>
       </c>
       <c r="D56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>215000</v>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
         <v>48</v>
       </c>
       <c r="D57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>220000</v>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
         <v>49</v>
       </c>
       <c r="D58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>225000</v>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
         <v>50</v>
       </c>
       <c r="D59">
-        <f t="shared" ref="D59:D64" si="11">C59*25000-1000000</f>
+        <f t="shared" ref="D59:D64" si="12">C59*25000-1000000</f>
         <v>250000</v>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
         <v>51</v>
       </c>
       <c r="D60">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>275000</v>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
         <v>52</v>
       </c>
       <c r="D61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300000</v>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
         <v>53</v>
       </c>
       <c r="D62">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>325000</v>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
         <v>54</v>
       </c>
       <c r="D63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>350000</v>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
         <v>55</v>
       </c>
       <c r="D64">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>375000</v>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
         <v>56</v>
       </c>
       <c r="D65">
-        <f t="shared" ref="D65:D109" si="12">C65*25000-1000000</f>
+        <f t="shared" ref="D65:D109" si="13">C65*25000-1000000</f>
         <v>400000</v>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
         <v>57</v>
       </c>
       <c r="D66">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>425000</v>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
         <v>58</v>
       </c>
       <c r="D67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>450000</v>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
         <v>59</v>
       </c>
       <c r="D68">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>475000</v>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
         <v>60</v>
       </c>
       <c r="D69">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>500000</v>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
         <v>61</v>
       </c>
       <c r="D70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>525000</v>
       </c>
     </row>
@@ -15701,7 +15701,7 @@
         <v>62</v>
       </c>
       <c r="D71">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>550000</v>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
         <v>63</v>
       </c>
       <c r="D72">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>575000</v>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
         <v>64</v>
       </c>
       <c r="D73">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>600000</v>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
         <v>65</v>
       </c>
       <c r="D74">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>625000</v>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
         <v>66</v>
       </c>
       <c r="D75">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>650000</v>
       </c>
     </row>
@@ -15746,7 +15746,7 @@
         <v>67</v>
       </c>
       <c r="D76">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>675000</v>
       </c>
     </row>
@@ -15755,7 +15755,7 @@
         <v>68</v>
       </c>
       <c r="D77">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>700000</v>
       </c>
     </row>
@@ -15764,7 +15764,7 @@
         <v>69</v>
       </c>
       <c r="D78">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>725000</v>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
         <v>71</v>
       </c>
       <c r="D80">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>775000</v>
       </c>
     </row>
@@ -15791,7 +15791,7 @@
         <v>72</v>
       </c>
       <c r="D81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>800000</v>
       </c>
     </row>
@@ -15800,7 +15800,7 @@
         <v>73</v>
       </c>
       <c r="D82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>825000</v>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
         <v>74</v>
       </c>
       <c r="D83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>850000</v>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
         <v>75</v>
       </c>
       <c r="D84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>875000</v>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
         <v>76</v>
       </c>
       <c r="D85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>900000</v>
       </c>
     </row>
@@ -15836,7 +15836,7 @@
         <v>77</v>
       </c>
       <c r="D86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>925000</v>
       </c>
     </row>
@@ -15845,7 +15845,7 @@
         <v>78</v>
       </c>
       <c r="D87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>950000</v>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
         <v>79</v>
       </c>
       <c r="D88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>975000</v>
       </c>
     </row>
@@ -15863,7 +15863,7 @@
         <v>80</v>
       </c>
       <c r="D89">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1000000</v>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
         <v>81</v>
       </c>
       <c r="D90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1025000</v>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
         <v>82</v>
       </c>
       <c r="D91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1050000</v>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
         <v>83</v>
       </c>
       <c r="D92">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1075000</v>
       </c>
     </row>
@@ -15899,7 +15899,7 @@
         <v>84</v>
       </c>
       <c r="D93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1100000</v>
       </c>
     </row>
@@ -15908,7 +15908,7 @@
         <v>85</v>
       </c>
       <c r="D94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1125000</v>
       </c>
     </row>
@@ -15917,7 +15917,7 @@
         <v>86</v>
       </c>
       <c r="D95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1150000</v>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
         <v>87</v>
       </c>
       <c r="D96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1175000</v>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
         <v>88</v>
       </c>
       <c r="D97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1200000</v>
       </c>
     </row>
@@ -15944,7 +15944,7 @@
         <v>89</v>
       </c>
       <c r="D98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1225000</v>
       </c>
     </row>
@@ -15953,7 +15953,7 @@
         <v>90</v>
       </c>
       <c r="D99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1250000</v>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
         <v>91</v>
       </c>
       <c r="D100">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1275000</v>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
         <v>92</v>
       </c>
       <c r="D101">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1300000</v>
       </c>
     </row>
@@ -15980,7 +15980,7 @@
         <v>93</v>
       </c>
       <c r="D102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1325000</v>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
         <v>94</v>
       </c>
       <c r="D103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1350000</v>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
         <v>95</v>
       </c>
       <c r="D104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1375000</v>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
         <v>96</v>
       </c>
       <c r="D105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1400000</v>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
         <v>97</v>
       </c>
       <c r="D106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1425000</v>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
         <v>98</v>
       </c>
       <c r="D107">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1450000</v>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
         <v>99</v>
       </c>
       <c r="D108">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1475000</v>
       </c>
     </row>
@@ -16043,7 +16043,7 @@
         <v>100</v>
       </c>
       <c r="D109">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1500000</v>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>表2_4[[#This Row],[装备折算价格]]*0.25 * L16*3900*(1.6)^(M16)*O16/N16</f>
+        <f t="shared" ref="Q16:Q18" si="3">P16 * L16*3900*(1.6)^(M16)*O16/N16</f>
         <v>0</v>
       </c>
       <c r="R16" s="40">
@@ -19955,7 +19955,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>表2_4[[#This Row],[装备折算价格]]*0.25 * L17*3900*(1.6)^(M17)*O17/N17</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <f>表2_4[[#This Row],[装备折算价格]]*0.25 * L18*3900*(1.6)^(M18)*O18/N18</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -20013,6 +20013,25 @@
       <c r="K19" t="s">
         <v>380</v>
       </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" ref="Q19:Q20" si="4">P19 * L19*3900*(1.6)^(M19)*O19/N19</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
@@ -20030,6 +20049,25 @@
       </c>
       <c r="K20" t="s">
         <v>381</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="4:17" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAEE410-1652-4FDD-88CE-14447CBC9653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8283223F-A581-4BA8-A468-B50FF90D2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="415">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -17945,6 +17945,9 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -18043,7 +18046,7 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="40">
         <f>1.5*E5*1.25^H5*SQRT(G5/30)/(F5+0.5)</f>
         <v>2640.6704633232384</v>
       </c>
@@ -18063,21 +18066,27 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D12">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="E12">
-        <v>7500</v>
-      </c>
-      <c r="G12">
-        <f>E12</f>
-        <v>7500</v>
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <f>IF(E12 &gt; 800 +F12 * 200, 800 +F12 * 200 + (E12 - 800 -F12 * 200)/10,E12 )</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -18085,14 +18094,17 @@
         <v>54</v>
       </c>
       <c r="D13">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E13">
-        <v>7500</v>
-      </c>
-      <c r="G13">
-        <f>E13</f>
-        <v>7500</v>
+        <v>6000</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="H13" s="40">
+        <f>IF(E13 &gt; 800 +F13 * 200, 800 +F13 * 200 + (E13 - 800 -F13 * 200)/10,E13 )</f>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8283223F-A581-4BA8-A468-B50FF90D2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5D1B29-1F91-40BA-91A7-D9BEDE193A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="417">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -745,18 +745,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单件法抗均值上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单件法抗最高上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钢铁小熊均值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>军阀重装上身</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -765,10 +753,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注释：套装特殊部件可根据特点或重量等适当浮动或者面板转移，但同一套装不同部件之间不要偏差过大，否则可能导致混装的强度较高。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>过高的重量、价格、过低的射速或者其他减益效果可交换为1层的加权层级（可叠加）。价格加权仅限只可购买获得的装备，参考后续的装备价格计算。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -812,10 +796,6 @@
     <t>magicdefence</t>
   </si>
   <si>
-    <t>魔法抗性单件不要过高。全属性抗性目前仅供参考，上下身各10点封顶，请尽可能避免在无作弊可得的物品内实装。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请以当前总分≈加权总分为平衡标准，对前方可填写数值进行调整。 选择对应类型的一行填写即可。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -836,10 +816,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注释：由于项链通常限制等级填写不规范，可以获取时对应的玩家等级作为参考。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>具体装备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1657,6 +1633,38 @@
   </si>
   <si>
     <t>最大收益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀/枪总加成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法抗均值上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法抗最高上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法抗性单件不要过高。全属性抗性目前仅供参考，上下身各15点封顶，请尽可能避免在无作弊可得的物品内实装。特定法抗套装可有多种属性抗性，每种独立计算上限，但分数合并计算。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装特殊部件可根据特点或重量等适当浮动或者面板转移，但同一套装不同部件之间不要偏差过大，否则可能导致混装的强度较高。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御以外的单项属性占比过高时会占用更多数值模型，通常不要超过总分的一半。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于项链通常限制等级填写不规范，可以获取时对应的玩家等级作为参考。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢铁小熊鞋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1826,7 +1834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1893,6 +1901,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2260,8 +2269,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C986475-2ED4-459B-8875-CFCE36210C4F}" name="表2_2" displayName="表2_2" ref="B2:S18" totalsRowShown="0" headerRowDxfId="8">
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C986475-2ED4-459B-8875-CFCE36210C4F}" name="表2_2" displayName="表2_2" ref="B2:T19" totalsRowShown="0" headerRowDxfId="8">
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{2647E847-1A87-468E-AC67-15776089B268}" name="类型" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{8C4F1BC9-0719-4D06-910D-C32A022B3F84}" name="具体装备"/>
     <tableColumn id="3" xr3:uid="{10DE4A43-3155-4437-AAD9-C89D42BD8260}" name="限制等级"/>
@@ -2269,6 +2278,7 @@
     <tableColumn id="5" xr3:uid="{6AF448EE-2774-4637-AB35-F31ACE9BF3A8}" name="HP"/>
     <tableColumn id="6" xr3:uid="{26035CC6-D4F3-4F9F-8804-A4F09E0DCFB7}" name="MP"/>
     <tableColumn id="7" xr3:uid="{2720D73B-31C2-4C4E-A39C-F38374E106D1}" name="伤害加成"/>
+    <tableColumn id="20" xr3:uid="{98FF735E-0C81-4B78-998C-277C7A2E9E95}" name="刀/枪总加成"/>
     <tableColumn id="8" xr3:uid="{B552614C-768D-47B3-8728-023F25DB082B}" name="重量"/>
     <tableColumn id="9" xr3:uid="{0272C720-4E7F-4F88-ADFF-3EBC66F27ABF}" name="空手加成"/>
     <tableColumn id="10" xr3:uid="{7C739359-B25B-4B47-892E-89763D9142F1}" name="法抗"/>
@@ -2278,10 +2288,10 @@
     <tableColumn id="14" xr3:uid="{DCE00B25-EE37-46EB-B890-0A53E8A2CF68}" name="平衡总分"/>
     <tableColumn id="15" xr3:uid="{D87510E8-97D9-4692-95FD-9798328A3FC4}" name="加权总分"/>
     <tableColumn id="16" xr3:uid="{F940B2A9-FAF9-4D2C-AD63-1D3A0BB809DE}" name="列2"/>
-    <tableColumn id="19" xr3:uid="{18672C66-DEB8-45CE-A811-5B3388DD243B}" name="单件法抗均值上限" dataDxfId="6">
+    <tableColumn id="19" xr3:uid="{18672C66-DEB8-45CE-A811-5B3388DD243B}" name="法抗均值上限" dataDxfId="6">
       <calculatedColumnFormula>10+表2_2[[#This Row],[限制等级]]*0.2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{2A71EA5E-6A4C-44FD-9B0C-0AEFEAC81C2E}" name="单件法抗最高上限" dataDxfId="5">
+    <tableColumn id="17" xr3:uid="{2A71EA5E-6A4C-44FD-9B0C-0AEFEAC81C2E}" name="法抗最高上限" dataDxfId="5">
       <calculatedColumnFormula>25+表2_2[[#This Row],[限制等级]]*0.2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2645,7 +2655,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
@@ -2660,33 +2670,33 @@
         <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="L1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M1" t="s">
         <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O1" t="s">
         <v>165</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="V1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>50</v>
@@ -2716,94 +2726,94 @@
         <v>4</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>162</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="V2" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="X2" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="W2" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="X2" s="14" t="s">
-        <v>306</v>
-      </c>
       <c r="Y2" s="14" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AA2" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="AE2" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="AB2" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="AD2" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>399</v>
-      </c>
       <c r="AG2" s="14" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AH2" s="14" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AI2" s="14" t="s">
         <v>169</v>
       </c>
       <c r="AJ2" s="14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AK2" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AL2" s="14" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AM2" s="14" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AN2" s="14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
@@ -3075,7 +3085,7 @@
         <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -3211,7 +3221,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D6" s="12">
         <v>30</v>
@@ -3344,7 +3354,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D7" s="12">
         <v>28</v>
@@ -3477,7 +3487,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D8" s="12">
         <v>35</v>
@@ -3891,7 +3901,7 @@
         <v>157</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>47</v>
@@ -4032,7 +4042,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D13" s="12">
         <v>30</v>
@@ -4165,7 +4175,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D14" s="12">
         <v>32</v>
@@ -4294,11 +4304,11 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D15" s="12">
         <v>15</v>
@@ -4437,11 +4447,14 @@
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4" t="str">
+        <f>IF(OR(AF6&lt;0.7,AF7&lt;0.7,AF8&lt;0.7,AF13&lt;0.7,AF14&lt;0.7,AF15&lt;0.7),"异常提示：你的武器相对于当前限制等级的吃拐率过高，会导致dps惩罚过重，请降低射速、段数或穿刺能力！","")</f>
+        <v/>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -4449,40 +4462,40 @@
     <row r="18" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -4493,16 +4506,16 @@
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AL24" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="2:41" x14ac:dyDescent="0.3">
@@ -4514,10 +4527,10 @@
         <v>169</v>
       </c>
       <c r="AN25" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AO25" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="2:41" x14ac:dyDescent="0.3">
@@ -4525,10 +4538,10 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="AL26" s="28">
         <v>10</v>
@@ -4546,7 +4559,7 @@
     </row>
     <row r="27" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AL27" s="28">
         <v>20</v>
@@ -4564,7 +4577,7 @@
     </row>
     <row r="28" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AL28" s="28">
         <v>30</v>
@@ -4600,7 +4613,7 @@
     </row>
     <row r="30" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL30" s="28">
         <v>50</v>
@@ -4618,10 +4631,10 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AL31" s="12">
         <v>35</v>
@@ -4641,10 +4654,10 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AL32" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AM32" s="16">
         <f>IF(AL31&gt;=35,17*AL31-330,7*AL31+15) * IF(AL31&gt;=25, 1 + (MIN(13,(AL31-18)/3.5) - 1) * (MIN(13,(AL31-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(AL31-18)/3.5)  - 1),1)</f>
@@ -13129,7 +13142,7 @@
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F114" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G114">
         <v>393220.33898305101</v>
@@ -14419,7 +14432,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -14433,43 +14446,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K3" t="s">
+        <v>397</v>
+      </c>
+      <c r="L3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M3" t="s">
         <v>402</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>403</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
+        <v>401</v>
+      </c>
+      <c r="P3" t="s">
         <v>404</v>
       </c>
-      <c r="M3" t="s">
+      <c r="Q3" t="s">
+        <v>399</v>
+      </c>
+      <c r="R3" t="s">
+        <v>407</v>
+      </c>
+      <c r="S3" t="s">
         <v>408</v>
       </c>
-      <c r="N3" t="s">
-        <v>409</v>
-      </c>
-      <c r="O3" t="s">
-        <v>407</v>
-      </c>
-      <c r="P3" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
+        <v>400</v>
+      </c>
+      <c r="U3" t="s">
         <v>405</v>
       </c>
-      <c r="R3" t="s">
-        <v>413</v>
-      </c>
-      <c r="S3" t="s">
-        <v>414</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="V3" t="s">
         <v>406</v>
-      </c>
-      <c r="U3" t="s">
-        <v>411</v>
-      </c>
-      <c r="V3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -16076,12 +16089,12 @@
   <sheetData>
     <row r="1" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C1" s="29" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
@@ -16183,7 +16196,7 @@
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
@@ -16914,7 +16927,7 @@
     <row r="25" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C25" s="3"/>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.3">
@@ -16925,12 +16938,12 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.3">
@@ -16940,17 +16953,17 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
@@ -16980,7 +16993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09871776-299B-496E-8462-E6326FE1AD56}">
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -16989,54 +17002,54 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="7.9140625" customWidth="1"/>
     <col min="6" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="7" width="8.08203125" customWidth="1"/>
-    <col min="8" max="8" width="7.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="11" width="11.58203125" customWidth="1"/>
-    <col min="12" max="12" width="12.08203125" customWidth="1"/>
-    <col min="18" max="18" width="15.33203125" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="6.5" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.58203125" customWidth="1"/>
+    <col min="13" max="13" width="12.08203125" customWidth="1"/>
+    <col min="19" max="20" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
       </c>
       <c r="E1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K1" t="s">
+        <v>190</v>
+      </c>
+      <c r="L1" t="s">
         <v>191</v>
       </c>
-      <c r="H1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>165</v>
       </c>
-      <c r="N1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -17054,45 +17067,48 @@
         <v>169</v>
       </c>
       <c r="I2" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="R2" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="S2" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -17110,10 +17126,10 @@
         <v>10</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -17121,31 +17137,34 @@
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>240</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>240</v>
       </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P9" si="0">O3*1.25^L3</f>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q9" si="0">P3*1.25^M3</f>
         <v>240</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>12</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3">
         <v>18</v>
@@ -17163,42 +17182,45 @@
         <v>20</v>
       </c>
       <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
         <v>8</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>0</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>10</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>0</v>
       </c>
-      <c r="N4">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="O4">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>450</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>440</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>13.6</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>28.6</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D5" s="3">
         <v>21</v>
@@ -17216,45 +17238,48 @@
         <v>45</v>
       </c>
       <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
         <v>2</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>550</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>440</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <f t="shared" si="0"/>
         <v>550</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>14.2</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>29.2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>416</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -17272,45 +17297,48 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K6" s="3">
+        <v>35</v>
+      </c>
+      <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>3</v>
       </c>
-      <c r="N6">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
-        <v>950</v>
-      </c>
       <c r="O6">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <v>890</v>
+      </c>
+      <c r="P6">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
-        <v>500</v>
-      </c>
-      <c r="P6">
+        <v>460</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="0"/>
-        <v>976.5625</v>
-      </c>
-      <c r="R6">
+        <v>898.4375</v>
+      </c>
+      <c r="S6">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>14</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>150</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="19" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D7" s="3">
         <v>28</v>
@@ -17328,45 +17356,48 @@
         <v>60</v>
       </c>
       <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
         <v>8</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>0</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>20</v>
       </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>800</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>640</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>15.600000000000001</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>30.6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>151</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D8" s="3">
         <v>31</v>
@@ -17384,10 +17415,10 @@
         <v>30</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>-5</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -17395,34 +17426,37 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="N8">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>560</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>570</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <f t="shared" si="0"/>
         <v>570</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>16.2</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>31.2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>158</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D9" s="3">
         <v>33</v>
@@ -17440,39 +17474,42 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>10</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20</v>
       </c>
-      <c r="L9" s="3">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="M9" s="3">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>960</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
         <v>760</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>16.600000000000001</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>31.6</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>149</v>
       </c>
@@ -17481,54 +17518,57 @@
         <v>177</v>
       </c>
       <c r="D10" s="12">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E10" s="12">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="F10" s="12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H10" s="12">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I10" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12">
         <v>0</v>
-      </c>
-      <c r="K10" s="12">
-        <v>10</v>
       </c>
       <c r="L10" s="12">
         <v>0</v>
       </c>
-      <c r="N10" s="16">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
-        <v>705</v>
-      </c>
-      <c r="O10">
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <v>210</v>
+      </c>
+      <c r="P10">
         <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
-        <v>705</v>
-      </c>
-      <c r="P10" s="16">
-        <f>O10*1.25^L10</f>
-        <v>705</v>
-      </c>
-      <c r="R10">
+        <v>210</v>
+      </c>
+      <c r="Q10" s="16">
+        <f>P10*1.25^M10</f>
+        <v>210</v>
+      </c>
+      <c r="S10">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
-        <v>17</v>
-      </c>
-      <c r="S10">
+        <v>12</v>
+      </c>
+      <c r="T10">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>159</v>
       </c>
@@ -17542,16 +17582,19 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="3"/>
+      <c r="C12" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -17560,10 +17603,15 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B13" s="2"/>
-      <c r="D13" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>413</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -17572,136 +17620,142 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14">
+      <c r="M13" s="3"/>
+      <c r="S13" s="42" t="e">
+        <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T13" s="42" t="e">
+        <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15">
         <v>20</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>90</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>120</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>80</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>35</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>0</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>0</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>485</v>
       </c>
-      <c r="O14">
+      <c r="P15">
         <f>表2_2[[#This Row],[限制等级]]*20</f>
         <v>400</v>
       </c>
-      <c r="P14">
-        <f t="shared" ref="P14:P15" si="1">O14*1.25^L14</f>
+      <c r="Q15">
+        <f t="shared" ref="Q15:Q16" si="1">P15*1.25^M15</f>
         <v>500</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B15" s="3"/>
-      <c r="C15" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D15" s="12">
-        <v>60</v>
-      </c>
-      <c r="E15" s="12">
-        <v>200</v>
-      </c>
-      <c r="F15" s="12">
-        <v>300</v>
-      </c>
-      <c r="G15" s="12">
-        <v>300</v>
-      </c>
-      <c r="H15" s="12">
-        <v>70</v>
-      </c>
-      <c r="I15" s="12">
-        <v>0</v>
-      </c>
-      <c r="J15" s="12">
-        <v>0</v>
-      </c>
-      <c r="K15" s="12">
-        <v>0</v>
-      </c>
-      <c r="L15" s="12">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16">
-        <f>表2_2[[#This Row],[防御]]*2+表2_2[[#This Row],[HP]]+表2_2[[#This Row],[MP]]+表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
-        <v>1210</v>
-      </c>
-      <c r="O15">
-        <f>表2_2[[#This Row],[限制等级]]*20</f>
-        <v>1200</v>
-      </c>
-      <c r="P15" s="16">
-        <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" s="12">
+        <v>35</v>
+      </c>
+      <c r="E16" s="12">
+        <v>100</v>
+      </c>
+      <c r="F16" s="12">
+        <v>250</v>
+      </c>
+      <c r="G16" s="12">
+        <v>250</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <v>700</v>
+      </c>
+      <c r="P16">
+        <f>表2_2[[#This Row],[限制等级]]*20</f>
+        <v>700</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
-      <c r="C17" s="2" t="s">
-        <v>202</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -17718,68 +17772,94 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="C20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C20" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
+      <c r="C21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C22" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>331</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -17787,7 +17867,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="R14:S14 R15:S15" calculatedColumn="1"/>
+    <ignoredError sqref="S15:T15 S16:T16" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
@@ -17821,7 +17901,7 @@
         <v>170</v>
       </c>
       <c r="G2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -17885,41 +17965,41 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J15" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -17955,7 +18035,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -18442,7 +18522,7 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>82</v>
@@ -18584,28 +18664,28 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D11" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -18738,7 +18818,7 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
@@ -18748,12 +18828,12 @@
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -18790,13 +18870,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F1" t="s">
         <v>43</v>
@@ -18808,7 +18888,7 @@
         <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -18816,7 +18896,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -18825,37 +18905,37 @@
         <v>36</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O2" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="P2" s="26" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>154</v>
@@ -18866,7 +18946,7 @@
         <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D3">
         <v>21</v>
@@ -18914,10 +18994,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="12">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="G4" s="12">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12">
         <v>0</v>
@@ -18926,11 +19006,11 @@
         <v>0</v>
       </c>
       <c r="J4" s="12">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="N4" s="17">
         <f>表2_4[[#This Row],[金币需求]]+表2_4[[#This Row],[K点需求]]*30+表2_4[[#This Row],[材料价格]]+表2_4[[#This Row],[装备折算价格]]+表2_4[[#This Row],[掉落物折算价格]]</f>
-        <v>69000</v>
+        <v>70000</v>
       </c>
       <c r="O4">
         <f>表2_4[[#This Row],[限制等级]]*2000</f>
@@ -18960,10 +19040,10 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="3"/>
@@ -18990,22 +19070,22 @@
         <v>158</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="N8" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -19014,7 +19094,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D9" s="3">
         <v>5</v>
@@ -19058,7 +19138,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -19071,10 +19151,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>14</v>
@@ -19083,32 +19163,32 @@
         <v>36</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>88</v>
       </c>
       <c r="I12" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J12" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>236</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="14" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E13" s="21">
         <v>10</v>
@@ -19140,7 +19220,7 @@
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E14" s="21">
         <v>0</v>
@@ -19168,7 +19248,7 @@
         <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E15" s="22">
         <v>1</v>
@@ -19197,7 +19277,7 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E16" s="22">
         <v>1</v>
@@ -19222,7 +19302,7 @@
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E17" s="22">
         <v>1</v>
@@ -19248,7 +19328,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E18" s="22">
         <v>1</v>
@@ -19273,16 +19353,16 @@
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="D20" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
@@ -19290,52 +19370,52 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F22" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="L22" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="N22" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="P22" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q22" s="26" t="s">
         <v>245</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="J22" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="N22" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="P22" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q22" s="26" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E23" s="21">
         <v>1</v>
@@ -19380,7 +19460,7 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E24" s="22">
         <v>0</v>
@@ -19423,7 +19503,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="1"/>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E25" s="22">
         <v>0</v>
@@ -19462,7 +19542,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="1"/>
       <c r="D26" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E26" s="22">
         <v>0</v>
@@ -19500,10 +19580,10 @@
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
@@ -19511,14 +19591,14 @@
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="N27" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="24"/>
       <c r="D28" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -19529,7 +19609,7 @@
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="D29" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
@@ -19537,13 +19617,13 @@
         <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -19554,7 +19634,7 @@
         <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -19582,44 +19662,44 @@
   <sheetData>
     <row r="2" spans="3:18" x14ac:dyDescent="0.3">
       <c r="M2" s="29" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="3:18" x14ac:dyDescent="0.3">
       <c r="D3" s="33" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>94</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M3" s="35" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D4" s="34">
         <v>1.5</v>
@@ -19656,7 +19736,7 @@
     </row>
     <row r="5" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D5" s="34">
         <v>3.5</v>
@@ -19693,7 +19773,7 @@
     </row>
     <row r="6" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D6" s="34">
         <v>4</v>
@@ -19730,7 +19810,7 @@
     </row>
     <row r="7" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D7" s="36">
         <v>1</v>
@@ -19767,48 +19847,48 @@
     </row>
     <row r="9" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C9" s="24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="3:18" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="3:18" x14ac:dyDescent="0.3">
       <c r="D11" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="3:18" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="3:18" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="L14" s="33" t="s">
         <v>14</v>
@@ -19817,19 +19897,19 @@
         <v>36</v>
       </c>
       <c r="N14" s="38" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O14" s="38" t="s">
         <v>88</v>
       </c>
       <c r="P14" s="38" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Q14" s="38" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="R14" s="39" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="3:18" x14ac:dyDescent="0.3">
@@ -19837,7 +19917,7 @@
         <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -19857,7 +19937,7 @@
         <v>87</v>
       </c>
       <c r="K15" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="L15">
         <v>20</v>
@@ -19885,10 +19965,10 @@
     </row>
     <row r="16" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -19905,10 +19985,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="K16" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -19936,7 +20016,7 @@
     </row>
     <row r="17" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -19949,7 +20029,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -19973,7 +20053,7 @@
     </row>
     <row r="18" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -19986,7 +20066,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -20010,7 +20090,7 @@
     </row>
     <row r="19" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -20023,7 +20103,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -20047,7 +20127,7 @@
     </row>
     <row r="20" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -20060,7 +20140,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -20084,7 +20164,7 @@
     </row>
     <row r="21" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G21">
         <f t="shared" si="2"/>
@@ -20093,7 +20173,7 @@
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="G22">
         <f t="shared" si="2"/>
@@ -20102,7 +20182,7 @@
     </row>
     <row r="23" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G23">
         <f t="shared" si="2"/>
@@ -20111,7 +20191,7 @@
     </row>
     <row r="24" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G24">
         <f t="shared" si="2"/>
@@ -20120,7 +20200,7 @@
     </row>
     <row r="25" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G25">
         <f t="shared" si="2"/>
@@ -20129,7 +20209,7 @@
     </row>
     <row r="26" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G26">
         <f t="shared" si="2"/>
@@ -20138,7 +20218,7 @@
     </row>
     <row r="27" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G27">
         <f t="shared" si="2"/>
@@ -20147,7 +20227,7 @@
     </row>
     <row r="28" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G28">
         <f t="shared" si="2"/>
@@ -20156,7 +20236,7 @@
     </row>
     <row r="29" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G29">
         <f t="shared" si="2"/>
@@ -20165,7 +20245,7 @@
     </row>
     <row r="30" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G30">
         <f t="shared" si="2"/>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5D1B29-1F91-40BA-91A7-D9BEDE193A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1CBD5-EDF8-478D-94D4-EADCCFC1AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1834,7 +1834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1901,7 +1901,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -17141,7 +17140,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>240</v>
       </c>
       <c r="P3">
@@ -17197,7 +17196,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>450</v>
       </c>
       <c r="P4">
@@ -17253,7 +17252,7 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>550</v>
       </c>
       <c r="P5">
@@ -17312,7 +17311,7 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>890</v>
       </c>
       <c r="P6">
@@ -17371,7 +17370,7 @@
         <v>1</v>
       </c>
       <c r="O7">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>800</v>
       </c>
       <c r="P7">
@@ -17430,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>560</v>
       </c>
       <c r="P8">
@@ -17489,7 +17488,7 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>960</v>
       </c>
       <c r="P9">
@@ -17548,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="16">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>210</v>
       </c>
       <c r="P10">
@@ -17621,11 +17620,11 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="S13" s="42" t="e">
+      <c r="S13" t="e">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="T13" s="42" t="e">
+      <c r="T13" t="e">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>#VALUE!</v>
       </c>
@@ -17681,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="O15">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>485</v>
       </c>
       <c r="P15">
@@ -17735,7 +17734,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="16">
-        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>700</v>
       </c>
       <c r="P16">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1CBD5-EDF8-478D-94D4-EADCCFC1AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4466EDC8-63EA-4BB5-B69F-E226B138D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="419">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1665,6 +1665,13 @@
   </si>
   <si>
     <t>钢铁小熊鞋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害类型系数</t>
+  </si>
+  <si>
+    <t>物理伤害为1，魔法伤害为2，真实伤害为3。混杂类可填中间值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1834,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1901,6 +1908,9 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -18020,12 +18030,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702FAECF-80DC-495D-9C67-D5E0928DCAA6}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="11.58203125" customWidth="1"/>
     <col min="8" max="8" width="11.4140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18148,8 +18158,10 @@
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -18163,27 +18175,41 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="H12">
-        <f>IF(E12 &gt; 800 +F12 * 200, 800 +F12 * 200 + (E12 - 800 -F12 * 200)/10,E12 )</f>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <f>IF(E12 &gt; 800 +F12 * 200 + IF(F12 &gt;=30,1200 * (F12 - 29) * (F12 - 29),0), 800 +F12 * 200+ IF(F12 &gt;=30,1200  * (F12 - 29) * (F12 - 29),0) + (E12 - 800 -F12 * 200-IF(F12 &gt;=30,1200 * (F12 - 29) * (F12 - 29),0))/10,E12 )/G12</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D13">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="E13">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="F13">
         <v>30</v>
       </c>
-      <c r="H13" s="40">
-        <f>IF(E13 &gt; 800 +F13 * 200, 800 +F13 * 200 + (E13 - 800 -F13 * 200)/10,E13 )</f>
-        <v>6000</v>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="40">
+        <f>IF(E13 &gt; 800 +F13 * 200 + IF(F13 &gt;=30,1200 * (F13 - 29) * (F13 - 29),0), 800 +F13 * 200+ IF(F13 &gt;=30,1200  * (F13 - 29) * (F13 - 29),0) + (E13 - 800 -F13 * 200-IF(F13 &gt;=30,1200 * (F13 - 29) * (F13 - 29),0))/10,E13 )/G13</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4466EDC8-63EA-4BB5-B69F-E226B138D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887ED831-0985-4E9B-B729-E2FC83B60053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -21,11 +21,12 @@
     <sheet name="装备价格" sheetId="5" r:id="rId6"/>
     <sheet name="合成表成本" sheetId="11" r:id="rId7"/>
     <sheet name="副本收益" sheetId="13" r:id="rId8"/>
-    <sheet name="敌方或战宠经验" sheetId="6" r:id="rId9"/>
-    <sheet name="根据等级计算怪物属性" sheetId="7" r:id="rId10"/>
-    <sheet name="伤害公式" sheetId="8" r:id="rId11"/>
-    <sheet name="其余计算" sheetId="9" r:id="rId12"/>
-    <sheet name="旧版-枪械" sheetId="1" r:id="rId13"/>
+    <sheet name="怪物大致面板" sheetId="14" r:id="rId9"/>
+    <sheet name="敌方或战宠经验" sheetId="6" r:id="rId10"/>
+    <sheet name="根据等级计算怪物属性" sheetId="7" r:id="rId11"/>
+    <sheet name="伤害公式" sheetId="8" r:id="rId12"/>
+    <sheet name="其余计算" sheetId="9" r:id="rId13"/>
+    <sheet name="旧版-枪械" sheetId="1" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="481">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1422,24 +1423,6 @@
     <t>素材9</t>
   </si>
   <si>
-    <t>素材10</t>
-  </si>
-  <si>
-    <t>素材11</t>
-  </si>
-  <si>
-    <t>素材12</t>
-  </si>
-  <si>
-    <t>素材13</t>
-  </si>
-  <si>
-    <t>素材14</t>
-  </si>
-  <si>
-    <t>素材15</t>
-  </si>
-  <si>
     <t>单价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1504,10 +1487,6 @@
     <t>装备5</t>
   </si>
   <si>
-    <t>以当前收益≈期望收益为平衡标准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>装备等效价值辅助计算（取总价值填入上方，如果赠送的是装备合成材料则根据可合成装备等级、类型与数量以0层加权填入）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1672,6 +1651,277 @@
   </si>
   <si>
     <t>物理伤害为1，魔法伤害为2，真实伤害为3。混杂类可填中间值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废城</t>
+  </si>
+  <si>
+    <t>阶段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>军阀</t>
+  </si>
+  <si>
+    <t>注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总堂前期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总堂后期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诺亚前期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诺亚后期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主线完结</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主线后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10~15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑龙~深入禁区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爪豪之后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包括初见爪豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包括通缉犯，不包括黑龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备6</t>
+  </si>
+  <si>
+    <t>主线末尾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段系数</t>
+  </si>
+  <si>
+    <t>阶段系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应阶段系数参考下方表格。达到当前流程中后期时可+0.5。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>档次系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>档次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型小怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型小怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大型小怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低级精英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级精英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级精英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低级boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶级boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>举例和注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同档次之间的系数有间隔，根据具体情况可插空或上下浮动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：小僵尸（废城）。注释：毫无威胁的杂毛，凑数的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：胖僵尸（废城）左轮（盗贼）。注释：常规/偏科较强其他较弱的小怪，大量出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：普通重装兵（军阀）重装改造僵尸（诺亚前期）。注释：整体较强/偏科强其他中等的小怪，大量出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：精英战术少女（盗贼）黑铁游侠（总堂前期）。可经常复数出现的低级精英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：军阀精英突击（军阀）黑铁武士（总堂后期）。注释：有威胁的精英怪，有时复数出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：军阀精英重装（军阀）黑铁重锤（总堂后期）。注释：数值接近小boss，出场数量需要控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>档次定位仅相对于当前阶段，所举的例子也是仅相对于同阶段的档次，不代表具体数值强度。后期阶段的低档次怪物可比前期阶段的高档次怪物更强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：黑铁（总堂后期）兽王（诺亚后期）。注释：同期阶段下极强的boss，预计将给玩家的存在感极高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：单体摇滚公园（盗贼）半人马（诺亚前期）。注释：数值和高级精英差别不大，但基本性能强（通常表现在霸体或破韧），可能复数出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：巨斧僵尸（废城）方舟武士（军阀）大部分通缉犯（总堂前期）。注释：最常规的单体boss，在诺亚后期之前的流程不会同时出现超过1个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应阶段和档次系数参考下方表格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高防低血系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高攻低血防系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>段数系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速系数只看整体攻击动作的总时长和前后摇的长度，范围为1~5，代表极慢、慢、中等、快、极快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击倍率、段数系数均为大致平均值即可，攻击倍率默认为1，通常为1~3。段数系数默认为3，大致区间为1~10。攻击倍率为平均每次攻击的平均倍率，段数系数为平均每次攻击的平均段数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高攻低血防系数代表这个单位是否有更偏向攻击或防御的数值倾向，默认为1，范围为0.5~2。2代表攻击力明显更高，但血防明显更低，0.5代表血防明显更高，攻击力更低。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高防低血系数代表这个单位是否有防御和血量的比例倾向，默认为1，范围为0.2~5。数值越高代表防御越高，血量越低，但等效血防差别不大。视觉和设定上更硬的单位应该给更高的高防低血系数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意，以上数值以物理伤害为标准值，如果有法伤、真伤招式，应进一步控制攻击倍率。目前不再据此对面板进行调整。怪物魔抗属性目前没有硬性限制，根据情况配置即可。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP最大值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空手攻击MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空手攻击MIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP最小值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力MIX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验MIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度系数为移动速度，分为1~3三个档次，分别为慢、中、快。慢速度大约在10-40区间，中速度大约在40-60区间，快速度大约在60-90区间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：高级通缉犯（总堂前期）黑龙两阶段之和（总堂后期）方舟爪豪（诺亚前期）。注释：较强的boss</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1841,7 +2091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1910,6 +2160,18 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="58" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2694,7 +2956,7 @@
         <v>165</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="V1" t="s">
         <v>310</v>
@@ -2777,28 +3039,28 @@
         <v>308</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="AE2" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="AA2" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AF2" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="AC2" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>393</v>
-      </c>
       <c r="AG2" s="14" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="AH2" s="14" t="s">
         <v>290</v>
@@ -4504,7 +4766,7 @@
         <v>278</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -4536,7 +4798,7 @@
         <v>169</v>
       </c>
       <c r="AN25" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AO25" t="s">
         <v>271</v>
@@ -4640,7 +4902,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -4666,7 +4928,7 @@
         <v>331</v>
       </c>
       <c r="AL32" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AM32" s="16">
         <f>IF(AL31&gt;=35,17*AL31-330,7*AL31+15) * IF(AL31&gt;=25, 1 + (MIN(13,(AL31-18)/3.5) - 1) * (MIN(13,(AL31-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(AL31-18)/3.5)  - 1),1)</f>
@@ -4688,6 +4950,1054 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D62D51-4A85-49A4-AACE-F79C8F6223AF}">
+  <dimension ref="A2:R68"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.9140625" customWidth="1"/>
+    <col min="11" max="11" width="4.9140625" customWidth="1"/>
+    <col min="12" max="12" width="9.4140625" customWidth="1"/>
+    <col min="13" max="13" width="9.58203125" customWidth="1"/>
+    <col min="14" max="14" width="11.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+      <c r="D8">
+        <v>55000</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <f>(C8+(D8-C8)/(E8-1)*B8)</f>
+        <v>10762.71186440678</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>10000</v>
+      </c>
+      <c r="M8">
+        <v>55000</v>
+      </c>
+      <c r="N8">
+        <v>60</v>
+      </c>
+      <c r="O8">
+        <f>(L8+(M8-L8)/(N8-1)*K8)</f>
+        <v>10762.71186440678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>55000</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <f>(C9+(D9-C9)/(E9-1)*B9)</f>
+        <v>11525.423728813559</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>10000</v>
+      </c>
+      <c r="M9">
+        <v>55000</v>
+      </c>
+      <c r="N9">
+        <v>60</v>
+      </c>
+      <c r="O9">
+        <f>(L9+(M9-L9)/(N9-1)*K9)</f>
+        <v>11525.423728813559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+      <c r="D10">
+        <v>55000</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ref="F10:F17" si="0">(C10+(D10-C10)/(E10-1)*B10)</f>
+        <v>12288.135593220339</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>10000</v>
+      </c>
+      <c r="M10">
+        <v>55000</v>
+      </c>
+      <c r="N10">
+        <v>60</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ref="O10" si="1">(L10+(M10-L10)/(N10-1)*K10)</f>
+        <v>12288.135593220339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+      <c r="D11">
+        <v>55000</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>13050.847457627118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
+      </c>
+      <c r="D12">
+        <v>55000</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>13813.559322033898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>10000</v>
+      </c>
+      <c r="D13">
+        <v>55000</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>14576.271186440677</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>10000</v>
+      </c>
+      <c r="D14">
+        <v>55000</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>15338.983050847459</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>10000</v>
+      </c>
+      <c r="D15">
+        <v>55000</v>
+      </c>
+      <c r="E15">
+        <v>60</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>16101.694915254237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>10000</v>
+      </c>
+      <c r="D16">
+        <v>55000</v>
+      </c>
+      <c r="E16">
+        <v>60</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>16864.406779661018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>10000</v>
+      </c>
+      <c r="D17">
+        <v>55000</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>17627.118644067796</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>20000</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <f>(C20+(D20-C20)/(E20-1)*B20)</f>
+        <v>348.81355932203388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>20000</v>
+      </c>
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <f>(C21+(D21-C21)/(E21-1)*B21)</f>
+        <v>687.62711864406776</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>20000</v>
+      </c>
+      <c r="E22">
+        <v>60</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:F29" si="2">(C22+(D22-C22)/(E22-1)*B22)</f>
+        <v>1026.4406779661017</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>20000</v>
+      </c>
+      <c r="E23">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>1365.2542372881355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>20000</v>
+      </c>
+      <c r="E24">
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>1704.0677966101694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>20000</v>
+      </c>
+      <c r="E25">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>2042.8813559322034</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>20000</v>
+      </c>
+      <c r="E26">
+        <v>60</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>2381.694915254237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>20000</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>2720.5084745762711</v>
+      </c>
+      <c r="Q27">
+        <f>SUM(O8:O119)</f>
+        <v>34576.271186440674</v>
+      </c>
+      <c r="R27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>20000</v>
+      </c>
+      <c r="E28">
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>3059.3220338983051</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>20000</v>
+      </c>
+      <c r="E29">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="2"/>
+        <v>3398.1355932203387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>11</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>20000</v>
+      </c>
+      <c r="E30">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <f>(C30+(D30-C30)/(E30-1)*B30)</f>
+        <v>3736.9491525423728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>20000</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <f>(C31+(D31-C31)/(E31-1)*B31)</f>
+        <v>4075.7627118644068</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>20000</v>
+      </c>
+      <c r="E32">
+        <v>60</v>
+      </c>
+      <c r="F32">
+        <f t="shared" ref="F32:F38" si="3">(C32+(D32-C32)/(E32-1)*B32)</f>
+        <v>4414.5762711864409</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>20000</v>
+      </c>
+      <c r="E33">
+        <v>60</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>4753.389830508474</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>20000</v>
+      </c>
+      <c r="E34">
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>5092.2033898305081</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>16</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>20000</v>
+      </c>
+      <c r="E35">
+        <v>60</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>5431.0169491525421</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>20000</v>
+      </c>
+      <c r="E36">
+        <v>60</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>5769.8305084745762</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>20000</v>
+      </c>
+      <c r="E37">
+        <v>60</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>6108.6440677966102</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>20000</v>
+      </c>
+      <c r="E38">
+        <v>60</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>6447.4576271186434</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>20000</v>
+      </c>
+      <c r="E39">
+        <v>60</v>
+      </c>
+      <c r="F39">
+        <f>(C39+(D39-C39)/(E39-1)*B39)</f>
+        <v>6786.2711864406774</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>21</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>20000</v>
+      </c>
+      <c r="E40">
+        <v>60</v>
+      </c>
+      <c r="F40">
+        <f>(C40+(D40-C40)/(E40-1)*B40)</f>
+        <v>7125.0847457627115</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>22</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41">
+        <v>20000</v>
+      </c>
+      <c r="E41">
+        <v>60</v>
+      </c>
+      <c r="F41">
+        <f t="shared" ref="F41:F48" si="4">(C41+(D41-C41)/(E41-1)*B41)</f>
+        <v>7463.8983050847455</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>20000</v>
+      </c>
+      <c r="E42">
+        <v>60</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="4"/>
+        <v>7802.7118644067796</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>24</v>
+      </c>
+      <c r="C43">
+        <v>10</v>
+      </c>
+      <c r="D43">
+        <v>20000</v>
+      </c>
+      <c r="E43">
+        <v>60</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="4"/>
+        <v>8141.5254237288136</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>25</v>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>20000</v>
+      </c>
+      <c r="E44">
+        <v>60</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="4"/>
+        <v>8480.3389830508477</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>26</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>20000</v>
+      </c>
+      <c r="E45">
+        <v>60</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="4"/>
+        <v>8819.1525423728817</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>27</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46">
+        <v>20000</v>
+      </c>
+      <c r="E46">
+        <v>60</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="4"/>
+        <v>9157.966101694914</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>28</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>20000</v>
+      </c>
+      <c r="E47">
+        <v>60</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="4"/>
+        <v>9496.779661016948</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>29</v>
+      </c>
+      <c r="C48">
+        <v>10</v>
+      </c>
+      <c r="D48">
+        <v>20000</v>
+      </c>
+      <c r="E48">
+        <v>60</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="4"/>
+        <v>9835.5932203389821</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49">
+        <v>20000</v>
+      </c>
+      <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49">
+        <f>(C49+(D49-C49)/(E49-1)*B49)</f>
+        <v>10174.406779661016</v>
+      </c>
+      <c r="H49">
+        <f>SUM(F20:F49)</f>
+        <v>157848.30508474578</v>
+      </c>
+      <c r="I49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>31</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>20000</v>
+      </c>
+      <c r="E50">
+        <v>60</v>
+      </c>
+      <c r="F50">
+        <f t="shared" ref="F50:F59" si="5">(C50+(D50-C50)/(E50-1)*B50)</f>
+        <v>10513.22033898305</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51">
+        <v>20000</v>
+      </c>
+      <c r="E51">
+        <v>60</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="5"/>
+        <v>10852.033898305084</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>33</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>20000</v>
+      </c>
+      <c r="E52">
+        <v>60</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="5"/>
+        <v>11190.847457627118</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>34</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>20000</v>
+      </c>
+      <c r="E53">
+        <v>60</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="5"/>
+        <v>11529.661016949152</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>35</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>20000</v>
+      </c>
+      <c r="E54">
+        <v>60</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="5"/>
+        <v>11868.474576271186</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>36</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55">
+        <v>20000</v>
+      </c>
+      <c r="E55">
+        <v>60</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="5"/>
+        <v>12207.28813559322</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>37</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+      <c r="D56">
+        <v>20000</v>
+      </c>
+      <c r="E56">
+        <v>60</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="5"/>
+        <v>12546.101694915254</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>38</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <v>20000</v>
+      </c>
+      <c r="E57">
+        <v>60</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="5"/>
+        <v>12884.915254237287</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>20000</v>
+      </c>
+      <c r="E58">
+        <v>60</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="5"/>
+        <v>13223.728813559321</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>40</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59">
+        <v>20000</v>
+      </c>
+      <c r="E59">
+        <v>60</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="5"/>
+        <v>13562.542372881355</v>
+      </c>
+      <c r="H59">
+        <f>SUM(F20:F59)</f>
+        <v>278227.11864406784</v>
+      </c>
+      <c r="I59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <f>SUM(F20:F128)</f>
+        <v>278227.11864406784</v>
+      </c>
+      <c r="I68" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD734CB-80FA-4C48-97CD-26CCAF18120C}">
   <dimension ref="B2:AH115"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -13169,7 +14479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766352B4-FCC2-4228-99C9-8C03AC6B458D}">
   <dimension ref="A1:W46"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -14415,7 +15725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B898794B-1561-478F-8317-69AF6D6FD6BA}">
   <dimension ref="B2:V109"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -14441,7 +15751,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -14455,43 +15765,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K3" t="s">
+        <v>390</v>
+      </c>
+      <c r="L3" t="s">
+        <v>391</v>
+      </c>
+      <c r="M3" t="s">
+        <v>395</v>
+      </c>
+      <c r="N3" t="s">
         <v>396</v>
       </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
+        <v>394</v>
+      </c>
+      <c r="P3" t="s">
         <v>397</v>
       </c>
-      <c r="L3" t="s">
+      <c r="Q3" t="s">
+        <v>392</v>
+      </c>
+      <c r="R3" t="s">
+        <v>400</v>
+      </c>
+      <c r="S3" t="s">
+        <v>401</v>
+      </c>
+      <c r="T3" t="s">
+        <v>393</v>
+      </c>
+      <c r="U3" t="s">
         <v>398</v>
       </c>
-      <c r="M3" t="s">
-        <v>402</v>
-      </c>
-      <c r="N3" t="s">
-        <v>403</v>
-      </c>
-      <c r="O3" t="s">
-        <v>401</v>
-      </c>
-      <c r="P3" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="V3" t="s">
         <v>399</v>
-      </c>
-      <c r="R3" t="s">
-        <v>407</v>
-      </c>
-      <c r="S3" t="s">
-        <v>408</v>
-      </c>
-      <c r="T3" t="s">
-        <v>400</v>
-      </c>
-      <c r="U3" t="s">
-        <v>405</v>
-      </c>
-      <c r="V3" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -16076,7 +17386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:W35"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -17076,7 +18386,7 @@
         <v>169</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>170</v>
@@ -17106,10 +18416,10 @@
         <v>154</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -17288,7 +18598,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -17602,7 +18912,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -17619,7 +18929,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -17789,7 +19099,7 @@
         <v>236</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -17863,7 +19173,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
@@ -18159,7 +19469,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -18209,7 +19519,7 @@
         <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -19163,7 +20473,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -19395,7 +20705,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>225</v>
@@ -19616,7 +20926,7 @@
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="N27" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
@@ -19674,606 +20984,697 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F594B-8471-4760-8349-0BF477107C61}">
-  <dimension ref="C2:R30"/>
+  <dimension ref="C2:P32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.1640625" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="9.1640625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="5.58203125" customWidth="1"/>
+    <col min="16" max="16" width="8.25" customWidth="1"/>
     <col min="17" max="17" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="M2" s="29" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="3" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="D3" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="E3" s="33" t="s">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="D2" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G2" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="H3" s="33" t="s">
-        <v>362</v>
-      </c>
-      <c r="I3" s="33" t="s">
+      <c r="H2" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="I2" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="K3" s="33" t="s">
+      <c r="J2" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="K2" s="33" t="s">
         <v>339</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="M2" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O2" s="35" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="4" spans="3:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="45">
+        <v>20000</v>
+      </c>
+      <c r="H3" s="27">
+        <v>22000</v>
+      </c>
+      <c r="I3" s="27">
+        <v>20000</v>
+      </c>
+      <c r="J3" s="45">
+        <v>0</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0</v>
+      </c>
+      <c r="M3" s="45">
+        <f>G3+H3*0.5+I3/D3+IF(D3&gt;4,K3*300/(D3-2.5),K3*300)+J3*0.5</f>
+        <v>44333.333333333336</v>
+      </c>
+      <c r="O3" s="45">
+        <f>(D3*13000*E3*F3)</f>
+        <v>43875</v>
+      </c>
+    </row>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="D4" s="34">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="27">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="27">
         <v>1.5</v>
       </c>
-      <c r="G4">
-        <v>20000</v>
-      </c>
-      <c r="H4">
-        <v>22000</v>
-      </c>
-      <c r="I4">
-        <v>20000</v>
-      </c>
-      <c r="J4">
+      <c r="G4" s="45">
+        <v>50000</v>
+      </c>
+      <c r="H4" s="27">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="27">
+        <v>60000</v>
+      </c>
+      <c r="J4" s="45">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f>G4+H4*0.5+I4/D4+IF(D4&gt;3,K4*300/(D4-2),K4*300)+J4*0.5</f>
-        <v>44333.333333333336</v>
-      </c>
-      <c r="O4">
-        <f>(D4*13000*E4*F4)</f>
-        <v>43875</v>
-      </c>
-    </row>
-    <row r="5" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="K4" s="27">
+        <v>300</v>
+      </c>
+      <c r="M4" s="45">
+        <f t="shared" ref="M4:M6" si="0">G4+H4*0.5+I4/D4+IF(D4&gt;4,K4*300/(D4-2.5),K4*300)+J4*0.5</f>
+        <v>160000</v>
+      </c>
+      <c r="O4" s="45">
+        <f t="shared" ref="O4:O6" si="1">(D4*13000*E4*F4)</f>
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D5" s="34">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="27">
         <v>2</v>
       </c>
       <c r="F5" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="45">
         <v>50000</v>
       </c>
-      <c r="H5">
-        <v>10000</v>
-      </c>
-      <c r="I5">
-        <v>60000</v>
-      </c>
-      <c r="J5">
+      <c r="H5" s="27">
+        <v>4000</v>
+      </c>
+      <c r="I5" s="27">
+        <v>50000</v>
+      </c>
+      <c r="J5" s="45">
+        <v>260000</v>
+      </c>
+      <c r="K5" s="27">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>300</v>
-      </c>
-      <c r="M5">
-        <f t="shared" ref="M5:M7" si="0">G5+H5*0.5+I5/D5+IF(D5&gt;3,K5*300/(D5-2),K5*300)+J5*0.5</f>
-        <v>132142.85714285716</v>
-      </c>
-      <c r="O5">
-        <f t="shared" ref="O5:O7" si="1">(D5*13000*E5*F5)</f>
-        <v>136500</v>
-      </c>
-    </row>
-    <row r="6" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D6" s="34">
-        <v>4</v>
-      </c>
-      <c r="E6" s="27">
-        <v>2</v>
-      </c>
-      <c r="F6" s="27">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>50000</v>
-      </c>
-      <c r="H6">
-        <v>4000</v>
-      </c>
-      <c r="I6">
-        <v>50000</v>
-      </c>
-      <c r="J6">
-        <v>260000</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="M5" s="45">
         <f t="shared" si="0"/>
         <v>194500</v>
       </c>
-      <c r="O6">
+      <c r="O5" s="45">
         <f t="shared" si="1"/>
         <v>208000</v>
       </c>
     </row>
-    <row r="7" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C7" s="1" t="s">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D7" s="36">
-        <v>1</v>
-      </c>
-      <c r="E7" s="37">
-        <v>1</v>
-      </c>
-      <c r="F7" s="37">
-        <v>1</v>
-      </c>
-      <c r="G7" s="37">
+      <c r="D6" s="36">
+        <v>1</v>
+      </c>
+      <c r="E6" s="37">
+        <v>1</v>
+      </c>
+      <c r="F6" s="37">
+        <v>1</v>
+      </c>
+      <c r="G6" s="37">
         <v>0</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H6" s="37">
         <v>0</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I6" s="37">
         <v>0</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J6" s="37">
         <v>0</v>
       </c>
-      <c r="K7" s="37">
+      <c r="K6" s="37">
         <v>0</v>
       </c>
-      <c r="M7" s="40">
+      <c r="M6" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="40">
+      <c r="O6" s="40">
         <f t="shared" si="1"/>
         <v>13000</v>
       </c>
     </row>
-    <row r="9" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C9" s="24" t="s">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C8" s="24" t="s">
         <v>236</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" spans="3:18" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="11" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="D11" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="I11" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="I12" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="M12" s="35" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="J13" s="45">
+        <v>20</v>
+      </c>
+      <c r="K13" s="45">
+        <v>500</v>
+      </c>
+      <c r="L13" s="45">
+        <f>J13*K13</f>
+        <v>10000</v>
+      </c>
+      <c r="M13">
+        <f>SUM(L13:L13)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="D14" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="J14" s="45">
+        <v>0</v>
+      </c>
+      <c r="K14" s="45">
+        <v>0</v>
+      </c>
+      <c r="L14" s="45">
+        <f>J14*K14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="40">
+        <f>SUM(L14:L22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="40">
+        <v>1</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="J15" s="45">
+        <v>0</v>
+      </c>
+      <c r="K15" s="45">
+        <v>0</v>
+      </c>
+      <c r="L15" s="45">
+        <f>J15*K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>415</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="J16" s="45">
+        <v>0</v>
+      </c>
+      <c r="K16" s="45">
+        <v>0</v>
+      </c>
+      <c r="L16" s="45">
+        <f>J16*K16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>416</v>
+      </c>
+      <c r="E17" s="40">
+        <v>3</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="J17" s="45">
+        <v>0</v>
+      </c>
+      <c r="K17" s="45">
+        <v>0</v>
+      </c>
+      <c r="L17" s="45">
+        <f>J17*K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>418</v>
+      </c>
+      <c r="E18" s="40">
+        <v>4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>429</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="J18" s="45">
+        <v>0</v>
+      </c>
+      <c r="K18" s="45">
+        <v>0</v>
+      </c>
+      <c r="L18" s="45">
+        <f>J18*K18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>419</v>
+      </c>
+      <c r="E19" s="40">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>426</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="J19" s="45">
+        <v>0</v>
+      </c>
+      <c r="K19" s="45">
+        <v>0</v>
+      </c>
+      <c r="L19" s="45">
+        <f>J19*K19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>420</v>
+      </c>
+      <c r="E20" s="40">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>428</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20" s="45">
+        <v>0</v>
+      </c>
+      <c r="K20" s="45">
+        <v>0</v>
+      </c>
+      <c r="L20" s="45">
+        <f>J20*K20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>421</v>
+      </c>
+      <c r="E21" s="40">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>427</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="J21" s="45">
+        <v>0</v>
+      </c>
+      <c r="K21" s="45">
+        <v>0</v>
+      </c>
+      <c r="L21" s="45">
+        <f>J21*K21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>422</v>
+      </c>
+      <c r="E22" s="40">
+        <v>8</v>
+      </c>
+      <c r="I22" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="J22" s="45">
+        <v>0</v>
+      </c>
+      <c r="K22" s="45">
+        <v>0</v>
+      </c>
+      <c r="L22" s="45">
+        <f>J22*K22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" s="40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>424</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>425</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I25" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K25" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="M25" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="N25" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="O25" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="P25" s="39" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="J26" s="45">
+        <v>20</v>
+      </c>
+      <c r="K26" s="45">
+        <v>0</v>
+      </c>
+      <c r="L26" s="45">
+        <v>1.5</v>
+      </c>
+      <c r="M26" s="34">
+        <v>1</v>
+      </c>
+      <c r="N26" s="45">
+        <v>5</v>
+      </c>
+      <c r="O26" s="45">
+        <f>N26 * J26*3900*(1.6)^(K26)*M26/L26</f>
+        <v>260000</v>
+      </c>
+      <c r="P26">
+        <f>SUM(O26:O26)</f>
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="H27" s="1" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="13" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="D13" s="2" t="s">
+      <c r="I27" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="J27" s="45">
+        <v>0</v>
+      </c>
+      <c r="K27" s="45">
+        <v>0</v>
+      </c>
+      <c r="L27" s="45">
+        <v>1</v>
+      </c>
+      <c r="M27" s="34">
+        <v>1</v>
+      </c>
+      <c r="N27" s="45">
+        <v>0</v>
+      </c>
+      <c r="O27" s="45">
+        <f t="shared" ref="O27:O29" si="2">N27 * J27*3900*(1.6)^(K27)*M27/L27</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="40">
+        <f>SUM(O27:O32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I28" s="46" t="s">
         <v>366</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="D14" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="K14" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="O14" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="P14" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q14" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="R14" s="39" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="15" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>343</v>
-      </c>
-      <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15">
-        <v>500</v>
-      </c>
-      <c r="G15">
-        <f>E15*F15</f>
-        <v>10000</v>
-      </c>
-      <c r="H15">
-        <f>SUM(G15:G15)</f>
-        <v>10000</v>
-      </c>
-      <c r="J15" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" t="s">
-        <v>367</v>
-      </c>
-      <c r="L15">
-        <v>20</v>
-      </c>
-      <c r="M15">
+      <c r="J28" s="45">
         <v>0</v>
       </c>
-      <c r="N15">
-        <v>1.5</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>5</v>
-      </c>
-      <c r="Q15">
-        <f>P15 * L15*3900*(1.6)^(M15)*O15/N15</f>
-        <v>260000</v>
-      </c>
-      <c r="R15">
-        <f>SUM(Q15:Q15)</f>
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="16" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C16" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D16" t="s">
-        <v>344</v>
-      </c>
-      <c r="E16">
+      <c r="K28" s="45">
         <v>0</v>
       </c>
-      <c r="F16">
+      <c r="L28" s="45">
+        <v>1</v>
+      </c>
+      <c r="M28" s="34">
+        <v>1</v>
+      </c>
+      <c r="N28" s="45">
         <v>0</v>
       </c>
-      <c r="G16">
-        <f t="shared" ref="G16:G30" si="2">E16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="40">
-        <f>SUM(G16:G30)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="K16" t="s">
-        <v>371</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" ref="Q16:Q18" si="3">P16 * L16*3900*(1.6)^(M16)*O16/N16</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="40">
-        <f>SUM(Q16:Q30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>345</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
+      <c r="O28" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K17" t="s">
-        <v>372</v>
-      </c>
-      <c r="L17">
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I29" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="J29" s="45">
         <v>0</v>
       </c>
-      <c r="M17">
+      <c r="K29" s="45">
         <v>0</v>
       </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
+      <c r="L29" s="45">
+        <v>1</v>
+      </c>
+      <c r="M29" s="34">
+        <v>1</v>
+      </c>
+      <c r="N29" s="45">
         <v>0</v>
       </c>
-      <c r="Q17">
+      <c r="O29" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I30" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="J30" s="45">
+        <v>0</v>
+      </c>
+      <c r="K30" s="45">
+        <v>0</v>
+      </c>
+      <c r="L30" s="45">
+        <v>1</v>
+      </c>
+      <c r="M30" s="34">
+        <v>1</v>
+      </c>
+      <c r="N30" s="45">
+        <v>0</v>
+      </c>
+      <c r="O30" s="45">
+        <f t="shared" ref="O30:O31" si="3">N30 * J30*3900*(1.6)^(K30)*M30/L30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I31" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="J31" s="45">
+        <v>0</v>
+      </c>
+      <c r="K31" s="45">
+        <v>0</v>
+      </c>
+      <c r="L31" s="45">
+        <v>1</v>
+      </c>
+      <c r="M31" s="34">
+        <v>1</v>
+      </c>
+      <c r="N31" s="45">
+        <v>0</v>
+      </c>
+      <c r="O31" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>346</v>
-      </c>
-      <c r="E18">
+    <row r="32" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="I32" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="J32" s="45">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="K32" s="45">
         <v>0</v>
       </c>
-      <c r="G18">
-        <f t="shared" si="2"/>
+      <c r="L32" s="45">
+        <v>1</v>
+      </c>
+      <c r="M32" s="34">
+        <v>1</v>
+      </c>
+      <c r="N32" s="45">
         <v>0</v>
       </c>
-      <c r="K18" t="s">
-        <v>373</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>347</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K19" t="s">
-        <v>374</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" ref="Q19:Q20" si="4">P19 * L19*3900*(1.6)^(M19)*O19/N19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>375</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>349</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>350</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>351</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>352</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>353</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D26" t="s">
-        <v>354</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>355</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
-        <v>356</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
-        <v>357</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:17" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>358</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="2"/>
+      <c r="O32" s="45">
+        <f t="shared" ref="O32" si="4">N32 * J32*3900*(1.6)^(K32)*M32/L32</f>
         <v>0</v>
       </c>
     </row>
@@ -20284,1049 +21685,583 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D62D51-4A85-49A4-AACE-F79C8F6223AF}">
-  <dimension ref="A2:R68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D334537-191E-473E-8F5E-E80A13E62C45}">
+  <dimension ref="C2:T30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.9140625" customWidth="1"/>
-    <col min="11" max="11" width="4.9140625" customWidth="1"/>
-    <col min="12" max="12" width="9.4140625" customWidth="1"/>
-    <col min="13" max="13" width="9.58203125" customWidth="1"/>
-    <col min="14" max="14" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.08203125" customWidth="1"/>
+    <col min="8" max="9" width="8.9140625" customWidth="1"/>
+    <col min="10" max="10" width="13.08203125" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" customWidth="1"/>
+    <col min="18" max="18" width="9.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="J6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" t="s">
-        <v>90</v>
-      </c>
-      <c r="L7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M7" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" t="s">
-        <v>93</v>
-      </c>
-      <c r="O7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>10000</v>
-      </c>
-      <c r="D8">
-        <v>55000</v>
-      </c>
-      <c r="E8">
-        <v>60</v>
-      </c>
-      <c r="F8">
-        <f>(C8+(D8-C8)/(E8-1)*B8)</f>
-        <v>10762.71186440678</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>10000</v>
-      </c>
-      <c r="M8">
-        <v>55000</v>
-      </c>
-      <c r="N8">
-        <v>60</v>
-      </c>
-      <c r="O8">
-        <f>(L8+(M8-L8)/(N8-1)*K8)</f>
-        <v>10762.71186440678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B9">
+    <row r="2" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="D2" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>465</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>464</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="M2" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="R2" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="S2" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="27">
+        <v>1</v>
+      </c>
+      <c r="G3" s="27">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27">
+        <v>3</v>
+      </c>
+      <c r="I3" s="27">
+        <v>20000</v>
+      </c>
+      <c r="J3" s="27">
+        <v>0</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0</v>
+      </c>
+      <c r="M3" s="27">
+        <f>G3+H3*0.5+I3/D3+IF(D3&gt;3,K3*300/(D3-2),K3*300)+J3*0.5</f>
+        <v>13335.833333333334</v>
+      </c>
+      <c r="N3" s="27">
+        <f t="shared" ref="N3:R6" si="0">H3+I3*0.5+J3/E3+IF(E3&gt;3,L3*300/(E3-2),L3*300)+K3*0.5</f>
+        <v>10003</v>
+      </c>
+      <c r="O3" s="27">
+        <f t="shared" si="0"/>
+        <v>4020750</v>
+      </c>
+      <c r="P3" s="27">
+        <f t="shared" si="0"/>
+        <v>3007567.9166666665</v>
+      </c>
+      <c r="Q3" s="27">
+        <f t="shared" si="0"/>
+        <v>1206234446.7777777</v>
+      </c>
+      <c r="R3" s="27">
+        <f t="shared" si="0"/>
+        <v>2062161.447369722</v>
+      </c>
+      <c r="S3" s="27" t="e">
+        <f t="shared" ref="S3:S6" si="1">M3+N3*0.5+O3/J3+IF(J3&gt;3,Q3*300/(J3-2),Q3*300)+P3*0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T3" s="27" t="e">
+        <f t="shared" ref="T3:T6" si="2">N3+O3*0.5+P3/K3+IF(K3&gt;3,R3*300/(K3-2),R3*300)+Q3*0.5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="E4" s="27">
         <v>2</v>
       </c>
-      <c r="C9">
-        <v>10000</v>
-      </c>
-      <c r="D9">
-        <v>55000</v>
-      </c>
-      <c r="E9">
-        <v>60</v>
-      </c>
-      <c r="F9">
-        <f>(C9+(D9-C9)/(E9-1)*B9)</f>
-        <v>11525.423728813559</v>
-      </c>
-      <c r="K9">
+      <c r="F4" s="27">
+        <v>1</v>
+      </c>
+      <c r="G4" s="27">
+        <v>1</v>
+      </c>
+      <c r="H4" s="27">
+        <v>3</v>
+      </c>
+      <c r="I4" s="27">
+        <v>60000</v>
+      </c>
+      <c r="J4" s="27">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27">
+        <v>300</v>
+      </c>
+      <c r="M4" s="27">
+        <f t="shared" ref="M4:M6" si="3">G4+H4*0.5+I4/D4+IF(D4&gt;3,K4*300/(D4-2),K4*300)+J4*0.5</f>
+        <v>77145.357142857145</v>
+      </c>
+      <c r="N4" s="27">
+        <f t="shared" si="0"/>
+        <v>30153</v>
+      </c>
+      <c r="O4" s="27">
+        <f t="shared" si="0"/>
+        <v>23203907.142857142</v>
+      </c>
+      <c r="P4" s="27">
+        <f t="shared" si="0"/>
+        <v>9084622.6785714291</v>
+      </c>
+      <c r="Q4" s="27">
+        <f t="shared" si="0"/>
+        <v>6961213234.4761896</v>
+      </c>
+      <c r="R4" s="27">
+        <f t="shared" si="0"/>
+        <v>11685951.380097108</v>
+      </c>
+      <c r="S4" s="27" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T4" s="27">
+        <f t="shared" si="2"/>
+        <v>3504033386.4691091</v>
+      </c>
+    </row>
+    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" s="34">
+        <v>4</v>
+      </c>
+      <c r="E5" s="27">
         <v>2</v>
       </c>
-      <c r="L9">
-        <v>10000</v>
-      </c>
-      <c r="M9">
-        <v>55000</v>
-      </c>
-      <c r="N9">
-        <v>60</v>
-      </c>
-      <c r="O9">
-        <f>(L9+(M9-L9)/(N9-1)*K9)</f>
-        <v>11525.423728813559</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B10">
+      <c r="F5" s="27">
+        <v>1</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1</v>
+      </c>
+      <c r="H5" s="27">
         <v>3</v>
       </c>
-      <c r="C10">
-        <v>10000</v>
-      </c>
-      <c r="D10">
-        <v>55000</v>
-      </c>
-      <c r="E10">
-        <v>60</v>
-      </c>
-      <c r="F10">
-        <f t="shared" ref="F10:F17" si="0">(C10+(D10-C10)/(E10-1)*B10)</f>
-        <v>12288.135593220339</v>
-      </c>
-      <c r="K10">
+      <c r="I5" s="27">
+        <v>50000</v>
+      </c>
+      <c r="J5" s="27">
+        <v>260000</v>
+      </c>
+      <c r="K5" s="27">
+        <v>0</v>
+      </c>
+      <c r="M5" s="27">
+        <f t="shared" si="3"/>
+        <v>142502.5</v>
+      </c>
+      <c r="N5" s="27">
+        <f t="shared" si="0"/>
+        <v>155003</v>
+      </c>
+      <c r="O5" s="27">
+        <f t="shared" si="0"/>
+        <v>42930750</v>
+      </c>
+      <c r="P5" s="27">
+        <f t="shared" si="0"/>
+        <v>46832151.25</v>
+      </c>
+      <c r="Q5" s="27">
+        <f t="shared" si="0"/>
+        <v>12879350002.333334</v>
+      </c>
+      <c r="R5" s="27">
+        <f t="shared" si="0"/>
+        <v>21817633.497725908</v>
+      </c>
+      <c r="S5" s="27">
+        <f t="shared" si="1"/>
+        <v>38497147.522136763</v>
+      </c>
+      <c r="T5" s="27" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" s="36">
+        <v>1</v>
+      </c>
+      <c r="E6" s="37">
+        <v>1</v>
+      </c>
+      <c r="F6" s="37">
+        <v>1</v>
+      </c>
+      <c r="G6" s="37">
+        <v>1</v>
+      </c>
+      <c r="H6" s="37">
         <v>3</v>
       </c>
-      <c r="L10">
-        <v>10000</v>
-      </c>
-      <c r="M10">
-        <v>55000</v>
-      </c>
-      <c r="N10">
-        <v>60</v>
-      </c>
-      <c r="O10">
-        <f t="shared" ref="O10" si="1">(L10+(M10-L10)/(N10-1)*K10)</f>
-        <v>12288.135593220339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B11">
+      <c r="I6" s="37">
+        <v>3</v>
+      </c>
+      <c r="J6" s="37">
+        <v>0</v>
+      </c>
+      <c r="K6" s="37">
+        <v>0</v>
+      </c>
+      <c r="M6" s="40">
+        <f t="shared" si="3"/>
+        <v>5.5</v>
+      </c>
+      <c r="N6" s="40">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="O6" s="40">
+        <f t="shared" si="0"/>
+        <v>1653</v>
+      </c>
+      <c r="P6" s="40">
+        <f t="shared" si="0"/>
+        <v>1352.75</v>
+      </c>
+      <c r="Q6" s="40">
+        <f t="shared" si="0"/>
+        <v>495904.08333333331</v>
+      </c>
+      <c r="R6" s="40">
+        <f t="shared" si="0"/>
+        <v>406655.75</v>
+      </c>
+      <c r="S6" s="40" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T6" s="40" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="D8" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E9" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="12" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="13" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E14" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="15" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>412</v>
+      </c>
+      <c r="D18" s="40">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>437</v>
+      </c>
+      <c r="I18" s="40">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>415</v>
+      </c>
+      <c r="D19" s="40">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>438</v>
+      </c>
+      <c r="I19" s="40">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>416</v>
+      </c>
+      <c r="D20" s="40">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>439</v>
+      </c>
+      <c r="I20" s="40">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>418</v>
+      </c>
+      <c r="D21" s="40">
         <v>4</v>
       </c>
-      <c r="C11">
-        <v>10000</v>
-      </c>
-      <c r="D11">
-        <v>55000</v>
-      </c>
-      <c r="E11">
-        <v>60</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>13050.847457627118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12">
+      <c r="E21" t="s">
+        <v>429</v>
+      </c>
+      <c r="H21" t="s">
+        <v>440</v>
+      </c>
+      <c r="I21" s="40">
         <v>5</v>
       </c>
-      <c r="C12">
-        <v>10000</v>
-      </c>
-      <c r="D12">
-        <v>55000</v>
-      </c>
-      <c r="E12">
-        <v>60</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>13813.559322033898</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13">
+      <c r="J21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>419</v>
+      </c>
+      <c r="D22" s="40">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>426</v>
+      </c>
+      <c r="H22" t="s">
+        <v>441</v>
+      </c>
+      <c r="I22" s="40">
+        <v>7</v>
+      </c>
+      <c r="J22" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>420</v>
+      </c>
+      <c r="D23" s="40">
         <v>6</v>
       </c>
-      <c r="C13">
-        <v>10000</v>
-      </c>
-      <c r="D13">
-        <v>55000</v>
-      </c>
-      <c r="E13">
-        <v>60</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>14576.271186440677</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B14">
+      <c r="E23" t="s">
+        <v>428</v>
+      </c>
+      <c r="H23" t="s">
+        <v>442</v>
+      </c>
+      <c r="I23" s="40">
+        <v>9</v>
+      </c>
+      <c r="J23" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>421</v>
+      </c>
+      <c r="D24" s="40">
         <v>7</v>
       </c>
-      <c r="C14">
-        <v>10000</v>
-      </c>
-      <c r="D14">
-        <v>55000</v>
-      </c>
-      <c r="E14">
-        <v>60</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>15338.983050847459</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15">
+      <c r="E24" t="s">
+        <v>427</v>
+      </c>
+      <c r="H24" t="s">
+        <v>443</v>
+      </c>
+      <c r="I24" s="40">
+        <v>10</v>
+      </c>
+      <c r="J24" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>422</v>
+      </c>
+      <c r="D25" s="40">
         <v>8</v>
       </c>
-      <c r="C15">
-        <v>10000</v>
-      </c>
-      <c r="D15">
-        <v>55000</v>
-      </c>
-      <c r="E15">
-        <v>60</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>16101.694915254237</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B16">
+      <c r="H25" t="s">
+        <v>444</v>
+      </c>
+      <c r="I25" s="40">
+        <v>13</v>
+      </c>
+      <c r="J25" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>423</v>
+      </c>
+      <c r="D26" s="40">
         <v>9</v>
       </c>
-      <c r="C16">
-        <v>10000</v>
-      </c>
-      <c r="D16">
-        <v>55000</v>
-      </c>
-      <c r="E16">
-        <v>60</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>16864.406779661018</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17">
-        <v>10000</v>
-      </c>
-      <c r="D17">
-        <v>55000</v>
-      </c>
-      <c r="E17">
-        <v>60</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>17627.118644067796</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-      <c r="D20">
-        <v>20000</v>
-      </c>
-      <c r="E20">
-        <v>60</v>
-      </c>
-      <c r="F20">
-        <f>(C20+(D20-C20)/(E20-1)*B20)</f>
-        <v>348.81355932203388</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>10</v>
-      </c>
-      <c r="D21">
-        <v>20000</v>
-      </c>
-      <c r="E21">
-        <v>60</v>
-      </c>
-      <c r="F21">
-        <f>(C21+(D21-C21)/(E21-1)*B21)</f>
-        <v>687.62711864406776</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>10</v>
-      </c>
-      <c r="D22">
-        <v>20000</v>
-      </c>
-      <c r="E22">
-        <v>60</v>
-      </c>
-      <c r="F22">
-        <f t="shared" ref="F22:F29" si="2">(C22+(D22-C22)/(E22-1)*B22)</f>
-        <v>1026.4406779661017</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23">
-        <v>10</v>
-      </c>
-      <c r="D23">
-        <v>20000</v>
-      </c>
-      <c r="E23">
-        <v>60</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="2"/>
-        <v>1365.2542372881355</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24">
-        <v>10</v>
-      </c>
-      <c r="D24">
-        <v>20000</v>
-      </c>
-      <c r="E24">
-        <v>60</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="2"/>
-        <v>1704.0677966101694</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="D25">
-        <v>20000</v>
-      </c>
-      <c r="E25">
-        <v>60</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="2"/>
-        <v>2042.8813559322034</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B26">
-        <v>7</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>20000</v>
-      </c>
-      <c r="E26">
-        <v>60</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="2"/>
-        <v>2381.694915254237</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B27">
-        <v>8</v>
-      </c>
-      <c r="C27">
-        <v>10</v>
-      </c>
-      <c r="D27">
-        <v>20000</v>
-      </c>
-      <c r="E27">
-        <v>60</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="2"/>
-        <v>2720.5084745762711</v>
-      </c>
-      <c r="Q27">
-        <f>SUM(O8:O119)</f>
-        <v>34576.271186440674</v>
-      </c>
-      <c r="R27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B28">
-        <v>9</v>
-      </c>
-      <c r="C28">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>20000</v>
-      </c>
-      <c r="E28">
-        <v>60</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="2"/>
-        <v>3059.3220338983051</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B29">
-        <v>10</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>20000</v>
-      </c>
-      <c r="E29">
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="2"/>
-        <v>3398.1355932203387</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B30">
-        <v>11</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>20000</v>
-      </c>
-      <c r="E30">
-        <v>60</v>
-      </c>
-      <c r="F30">
-        <f>(C30+(D30-C30)/(E30-1)*B30)</f>
-        <v>3736.9491525423728</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>12</v>
-      </c>
-      <c r="C31">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>20000</v>
-      </c>
-      <c r="E31">
-        <v>60</v>
-      </c>
-      <c r="F31">
-        <f>(C31+(D31-C31)/(E31-1)*B31)</f>
-        <v>4075.7627118644068</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <v>13</v>
-      </c>
-      <c r="C32">
-        <v>10</v>
-      </c>
-      <c r="D32">
-        <v>20000</v>
-      </c>
-      <c r="E32">
-        <v>60</v>
-      </c>
-      <c r="F32">
-        <f t="shared" ref="F32:F38" si="3">(C32+(D32-C32)/(E32-1)*B32)</f>
-        <v>4414.5762711864409</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33">
-        <v>14</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-      <c r="D33">
-        <v>20000</v>
-      </c>
-      <c r="E33">
-        <v>60</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="3"/>
-        <v>4753.389830508474</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34">
-        <v>15</v>
-      </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>20000</v>
-      </c>
-      <c r="E34">
-        <v>60</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="3"/>
-        <v>5092.2033898305081</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35">
+      <c r="H26" t="s">
+        <v>445</v>
+      </c>
+      <c r="I26" s="40">
         <v>16</v>
       </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>20000</v>
-      </c>
-      <c r="E35">
-        <v>60</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="3"/>
-        <v>5431.0169491525421</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36">
-        <v>17</v>
-      </c>
-      <c r="C36">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <v>20000</v>
-      </c>
-      <c r="E36">
-        <v>60</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="3"/>
-        <v>5769.8305084745762</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37">
-        <v>18</v>
-      </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>20000</v>
-      </c>
-      <c r="E37">
-        <v>60</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="3"/>
-        <v>6108.6440677966102</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38">
-        <v>19</v>
-      </c>
-      <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>20000</v>
-      </c>
-      <c r="E38">
-        <v>60</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="3"/>
-        <v>6447.4576271186434</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39">
-        <v>20</v>
-      </c>
-      <c r="C39">
-        <v>10</v>
-      </c>
-      <c r="D39">
-        <v>20000</v>
-      </c>
-      <c r="E39">
-        <v>60</v>
-      </c>
-      <c r="F39">
-        <f>(C39+(D39-C39)/(E39-1)*B39)</f>
-        <v>6786.2711864406774</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40">
-        <v>21</v>
-      </c>
-      <c r="C40">
-        <v>10</v>
-      </c>
-      <c r="D40">
-        <v>20000</v>
-      </c>
-      <c r="E40">
-        <v>60</v>
-      </c>
-      <c r="F40">
-        <f>(C40+(D40-C40)/(E40-1)*B40)</f>
-        <v>7125.0847457627115</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41">
-        <v>22</v>
-      </c>
-      <c r="C41">
-        <v>10</v>
-      </c>
-      <c r="D41">
-        <v>20000</v>
-      </c>
-      <c r="E41">
-        <v>60</v>
-      </c>
-      <c r="F41">
-        <f t="shared" ref="F41:F48" si="4">(C41+(D41-C41)/(E41-1)*B41)</f>
-        <v>7463.8983050847455</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42">
-        <v>23</v>
-      </c>
-      <c r="C42">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>20000</v>
-      </c>
-      <c r="E42">
-        <v>60</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="4"/>
-        <v>7802.7118644067796</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43">
-        <v>24</v>
-      </c>
-      <c r="C43">
-        <v>10</v>
-      </c>
-      <c r="D43">
-        <v>20000</v>
-      </c>
-      <c r="E43">
-        <v>60</v>
-      </c>
-      <c r="F43">
-        <f t="shared" si="4"/>
-        <v>8141.5254237288136</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44">
+      <c r="J26" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>424</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>425</v>
+      </c>
+      <c r="H27" t="s">
+        <v>446</v>
+      </c>
+      <c r="I27" s="40">
         <v>25</v>
       </c>
-      <c r="C44">
-        <v>10</v>
-      </c>
-      <c r="D44">
-        <v>20000</v>
-      </c>
-      <c r="E44">
-        <v>60</v>
-      </c>
-      <c r="F44">
-        <f t="shared" si="4"/>
-        <v>8480.3389830508477</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45">
-        <v>26</v>
-      </c>
-      <c r="C45">
-        <v>10</v>
-      </c>
-      <c r="D45">
-        <v>20000</v>
-      </c>
-      <c r="E45">
-        <v>60</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="4"/>
-        <v>8819.1525423728817</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46">
-        <v>27</v>
-      </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>20000</v>
-      </c>
-      <c r="E46">
-        <v>60</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="4"/>
-        <v>9157.966101694914</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47">
-        <v>28</v>
-      </c>
-      <c r="C47">
-        <v>10</v>
-      </c>
-      <c r="D47">
-        <v>20000</v>
-      </c>
-      <c r="E47">
-        <v>60</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="4"/>
-        <v>9496.779661016948</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48">
-        <v>29</v>
-      </c>
-      <c r="C48">
-        <v>10</v>
-      </c>
-      <c r="D48">
-        <v>20000</v>
-      </c>
-      <c r="E48">
-        <v>60</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="4"/>
-        <v>9835.5932203389821</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49">
-        <v>30</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>20000</v>
-      </c>
-      <c r="E49">
-        <v>60</v>
-      </c>
-      <c r="F49">
-        <f>(C49+(D49-C49)/(E49-1)*B49)</f>
-        <v>10174.406779661016</v>
-      </c>
-      <c r="H49">
-        <f>SUM(F20:F49)</f>
-        <v>157848.30508474578</v>
-      </c>
-      <c r="I49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50">
-        <v>31</v>
-      </c>
-      <c r="C50">
-        <v>10</v>
-      </c>
-      <c r="D50">
-        <v>20000</v>
-      </c>
-      <c r="E50">
-        <v>60</v>
-      </c>
-      <c r="F50">
-        <f t="shared" ref="F50:F59" si="5">(C50+(D50-C50)/(E50-1)*B50)</f>
-        <v>10513.22033898305</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51">
-        <v>32</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>20000</v>
-      </c>
-      <c r="E51">
-        <v>60</v>
-      </c>
-      <c r="F51">
-        <f t="shared" si="5"/>
-        <v>10852.033898305084</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52">
-        <v>33</v>
-      </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="D52">
-        <v>20000</v>
-      </c>
-      <c r="E52">
-        <v>60</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="5"/>
-        <v>11190.847457627118</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53">
-        <v>34</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-      <c r="D53">
-        <v>20000</v>
-      </c>
-      <c r="E53">
-        <v>60</v>
-      </c>
-      <c r="F53">
-        <f t="shared" si="5"/>
-        <v>11529.661016949152</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54">
-        <v>35</v>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-      <c r="D54">
-        <v>20000</v>
-      </c>
-      <c r="E54">
-        <v>60</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="5"/>
-        <v>11868.474576271186</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55">
-        <v>36</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
-      </c>
-      <c r="D55">
-        <v>20000</v>
-      </c>
-      <c r="E55">
-        <v>60</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="5"/>
-        <v>12207.28813559322</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B56">
-        <v>37</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>20000</v>
-      </c>
-      <c r="E56">
-        <v>60</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="5"/>
-        <v>12546.101694915254</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57">
-        <v>38</v>
-      </c>
-      <c r="C57">
-        <v>10</v>
-      </c>
-      <c r="D57">
-        <v>20000</v>
-      </c>
-      <c r="E57">
-        <v>60</v>
-      </c>
-      <c r="F57">
-        <f t="shared" si="5"/>
-        <v>12884.915254237287</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58">
-        <v>39</v>
-      </c>
-      <c r="C58">
-        <v>10</v>
-      </c>
-      <c r="D58">
-        <v>20000</v>
-      </c>
-      <c r="E58">
-        <v>60</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="5"/>
-        <v>13223.728813559321</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B59">
-        <v>40</v>
-      </c>
-      <c r="C59">
-        <v>10</v>
-      </c>
-      <c r="D59">
-        <v>20000</v>
-      </c>
-      <c r="E59">
-        <v>60</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="5"/>
-        <v>13562.542372881355</v>
-      </c>
-      <c r="H59">
-        <f>SUM(F20:F59)</f>
-        <v>278227.11864406784</v>
-      </c>
-      <c r="I59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H68">
-        <f>SUM(F20:F128)</f>
-        <v>278227.11864406784</v>
-      </c>
-      <c r="I68" t="s">
-        <v>99</v>
+      <c r="J27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="H29" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I30" s="2" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887ED831-0985-4E9B-B729-E2FC83B60053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43C1F6A-8762-4C7E-9DE3-131E1FB8BBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="合成表成本" sheetId="11" r:id="rId7"/>
     <sheet name="副本收益" sheetId="13" r:id="rId8"/>
     <sheet name="怪物大致面板" sheetId="14" r:id="rId9"/>
-    <sheet name="敌方或战宠经验" sheetId="6" r:id="rId10"/>
+    <sheet name="经验辅助计算" sheetId="6" r:id="rId10"/>
     <sheet name="根据等级计算怪物属性" sheetId="7" r:id="rId11"/>
     <sheet name="伤害公式" sheetId="8" r:id="rId12"/>
     <sheet name="其余计算" sheetId="9" r:id="rId13"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="492">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1801,10 +1801,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>例子：胖僵尸（废城）左轮（盗贼）。注释：常规/偏科较强其他较弱的小怪，大量出现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>例子：普通重装兵（军阀）重装改造僵尸（诺亚前期）。注释：整体较强/偏科强其他中等的小怪，大量出现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1837,10 +1833,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对应阶段和档次系数参考下方表格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高防低血系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1865,22 +1857,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻速系数只看整体攻击动作的总时长和前后摇的长度，范围为1~5，代表极慢、慢、中等、快、极快</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击倍率、段数系数均为大致平均值即可，攻击倍率默认为1，通常为1~3。段数系数默认为3，大致区间为1~10。攻击倍率为平均每次攻击的平均倍率，段数系数为平均每次攻击的平均段数。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高攻低血防系数代表这个单位是否有更偏向攻击或防御的数值倾向，默认为1，范围为0.5~2。2代表攻击力明显更高，但血防明显更低，0.5代表血防明显更高，攻击力更低。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>高防低血系数代表这个单位是否有防御和血量的比例倾向，默认为1，范围为0.2~5。数值越高代表防御越高，血量越低，但等效血防差别不大。视觉和设定上更硬的单位应该给更高的高防低血系数。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>注意，以上数值以物理伤害为标准值，如果有法伤、真伤招式，应进一步控制攻击倍率。目前不再据此对面板进行调整。怪物魔抗属性目前没有硬性限制，根据情况配置即可。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1922,6 +1902,67 @@
   </si>
   <si>
     <t>例子：高级通缉犯（总堂前期）黑龙两阶段之和（总堂后期）方舟爪豪（诺亚前期）。注释：较强的boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例3</t>
+  </si>
+  <si>
+    <t>你的怪物：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：胖僵尸（废城）左轮（盗贼）。注释：常规水平/偏科较强其他较弱的小怪，大量出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据对应主线进度+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应阶段和档次系数参考下方表格。这两项将决定整体数值大致水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成长系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速系数只看单次攻击动作的总时长和前后摇的长度，实际代表攻击节奏快慢，默认为3，范围为1~5，代表极慢、慢、中等、快、极快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击倍率、段数系数均为大致平均值即可，攻击倍率默认为1~2，通常为1~3。段数系数默认为3，大致区间为1~10。攻击倍率为平均每次攻击的平均倍率，段数系数为平均每次攻击的平均段数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例4</t>
+  </si>
+  <si>
+    <t>示例5</t>
+  </si>
+  <si>
+    <t>小僵尸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成长系数代表战宠跟随等级的面板与经验成长率，范围为0.5-2，默认为1。系数高代表低级时更弱但高等级时更强。其他参数不变时攻击、HP、防御力可以分别用不同的成长系数，经验则取以上成长系数的均值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高防低血系数代表这个单位是否有防御和血量的比例倾向，默认为1，范围为0.2~5。数值越高代表防御越高，血量越低。视觉和设定上更硬的单位应该给更高的高防低血系数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K点价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大致约等于推荐参考值即可</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1929,6 +1970,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2091,7 +2135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2173,6 +2217,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -14267,20 +14317,20 @@
     </row>
     <row r="107" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B107">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C107">
-        <v>20000</v>
+        <v>3072.4028101962735</v>
       </c>
       <c r="D107">
-        <v>65000</v>
+        <v>3508.2253446625268</v>
       </c>
       <c r="E107">
         <v>60</v>
       </c>
       <c r="F107">
         <f t="shared" si="12"/>
-        <v>54322.033898305082</v>
+        <v>3367.875714919157</v>
       </c>
       <c r="H107">
         <v>100</v>
@@ -14339,20 +14389,20 @@
     </row>
     <row r="108" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B108">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C108">
-        <v>-200000</v>
+        <v>1985</v>
       </c>
       <c r="D108">
-        <v>130000</v>
+        <v>4500</v>
       </c>
       <c r="E108">
         <v>60</v>
       </c>
       <c r="F108">
         <f t="shared" si="12"/>
-        <v>359322.03389830515</v>
+        <v>3690.0847457627119</v>
       </c>
       <c r="H108">
         <v>60</v>
@@ -14411,20 +14461,20 @@
     </row>
     <row r="109" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B109">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C109">
-        <v>-200000</v>
+        <v>1480.8048651498614</v>
       </c>
       <c r="D109">
-        <v>130000</v>
+        <v>5019.3495504995381</v>
       </c>
       <c r="E109">
         <v>60</v>
       </c>
       <c r="F109">
         <f t="shared" si="12"/>
-        <v>359322.03389830515</v>
+        <v>3879.8182111496426</v>
       </c>
       <c r="H109">
         <v>100</v>
@@ -14448,15 +14498,65 @@
       </c>
     </row>
     <row r="110" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B110">
+        <v>30</v>
+      </c>
+      <c r="C110">
+        <v>265.61398339158382</v>
+      </c>
+      <c r="D110">
+        <v>360.61398339158387</v>
+      </c>
+      <c r="E110">
+        <v>60</v>
+      </c>
+      <c r="F110">
+        <f t="shared" ref="F110:F112" si="26">C110+((D110-C110)/(E110-1))*B110</f>
+        <v>313.91906813734658</v>
+      </c>
       <c r="M110">
         <f>L106/L109</f>
         <v>0.24842767295597482</v>
       </c>
     </row>
     <row r="111" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B111">
+        <v>30</v>
+      </c>
+      <c r="C111">
+        <v>189.28191492822722</v>
+      </c>
+      <c r="D111">
+        <v>468.56382985645445</v>
+      </c>
+      <c r="E111">
+        <v>60</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="26"/>
+        <v>331.28966828156308</v>
+      </c>
       <c r="M111">
         <f>L109/L106</f>
         <v>4.0253164556962027</v>
+      </c>
+    </row>
+    <row r="112" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B112">
+        <v>30</v>
+      </c>
+      <c r="C112">
+        <v>135.30699169579191</v>
+      </c>
+      <c r="D112">
+        <v>621.22796678316774</v>
+      </c>
+      <c r="E112">
+        <v>60</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="26"/>
+        <v>382.38545360462706</v>
       </c>
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.3">
@@ -19400,7 +19500,7 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="50">
         <f>1.5*E3*1.25^H3*SQRT(G3/30)/(F3+0.5)</f>
         <v>3181.9805153394641</v>
       </c>
@@ -19421,7 +19521,7 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="50">
         <f>1.5*E4*1.25^H4*SQRT(G4/30)/(F4+0.5)</f>
         <v>1815.2460833714163</v>
       </c>
@@ -19445,7 +19545,7 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="48">
         <f>1.5*E5*1.25^H5*SQRT(G5/30)/(F5+0.5)</f>
         <v>2640.6704633232384</v>
       </c>
@@ -19488,7 +19588,7 @@
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="50">
         <f>IF(E12 &gt; 800 +F12 * 200 + IF(F12 &gt;=30,1200 * (F12 - 29) * (F12 - 29),0), 800 +F12 * 200+ IF(F12 &gt;=30,1200  * (F12 - 29) * (F12 - 29),0) + (E12 - 800 -F12 * 200-IF(F12 &gt;=30,1200 * (F12 - 29) * (F12 - 29),0))/10,E12 )/G12</f>
         <v>1000</v>
       </c>
@@ -19509,7 +19609,7 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="48">
         <f>IF(E13 &gt; 800 +F13 * 200 + IF(F13 &gt;=30,1200 * (F13 - 29) * (F13 - 29),0), 800 +F13 * 200+ IF(F13 &gt;=30,1200  * (F13 - 29) * (F13 - 29),0) + (E13 - 800 -F13 * 200-IF(F13 &gt;=30,1200 * (F13 - 29) * (F13 - 29),0))/10,E13 )/G13</f>
         <v>8000</v>
       </c>
@@ -21232,7 +21332,7 @@
         <v>500</v>
       </c>
       <c r="L13" s="45">
-        <f>J13*K13</f>
+        <f t="shared" ref="L13:L22" si="2">J13*K13</f>
         <v>10000</v>
       </c>
       <c r="M13">
@@ -21263,7 +21363,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="45">
-        <f>J14*K14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14" s="40">
@@ -21288,7 +21388,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="45">
-        <f>J15*K15</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21309,7 +21409,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="45">
-        <f>J16*K16</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21330,7 +21430,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="45">
-        <f>J17*K17</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21354,7 +21454,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="45">
-        <f>J18*K18</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21378,7 +21478,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="45">
-        <f>J19*K19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21402,7 +21502,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="45">
-        <f>J20*K20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21426,7 +21526,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="45">
-        <f>J21*K21</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21447,7 +21547,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="45">
-        <f>J22*K22</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21550,7 +21650,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="45">
-        <f t="shared" ref="O27:O29" si="2">N27 * J27*3900*(1.6)^(K27)*M27/L27</f>
+        <f t="shared" ref="O27:O29" si="3">N27 * J27*3900*(1.6)^(K27)*M27/L27</f>
         <v>0</v>
       </c>
       <c r="P27" s="40">
@@ -21578,7 +21678,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -21602,7 +21702,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -21626,7 +21726,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="45">
-        <f t="shared" ref="O30:O31" si="3">N30 * J30*3900*(1.6)^(K30)*M30/L30</f>
+        <f t="shared" ref="O30:O31" si="4">N30 * J30*3900*(1.6)^(K30)*M30/L30</f>
         <v>0</v>
       </c>
     </row>
@@ -21650,7 +21750,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -21674,7 +21774,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="45">
-        <f t="shared" ref="O32" si="4">N32 * J32*3900*(1.6)^(K32)*M32/L32</f>
+        <f t="shared" ref="O32" si="5">N32 * J32*3900*(1.6)^(K32)*M32/L32</f>
         <v>0</v>
       </c>
     </row>
@@ -21686,582 +21786,803 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D334537-191E-473E-8F5E-E80A13E62C45}">
-  <dimension ref="C2:T30"/>
+  <dimension ref="B1:V33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="8.9140625" customWidth="1"/>
+    <col min="4" max="4" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="7.9140625" customWidth="1"/>
+    <col min="6" max="6" width="8.25" customWidth="1"/>
     <col min="7" max="7" width="8.08203125" customWidth="1"/>
-    <col min="8" max="9" width="8.9140625" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
     <col min="10" max="10" width="13.08203125" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="12" max="12" width="6.58203125" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="11.5" customWidth="1"/>
     <col min="17" max="17" width="10.6640625" customWidth="1"/>
     <col min="18" max="18" width="9.9140625" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="33" t="s">
+        <v>238</v>
+      </c>
       <c r="D2" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="M2" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="R2" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="S2" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="U2" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="34">
+        <v>1</v>
+      </c>
+      <c r="D3" s="27">
+        <v>1</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1</v>
+      </c>
+      <c r="F3" s="27">
+        <v>3</v>
+      </c>
+      <c r="G3" s="27">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27">
+        <v>1</v>
+      </c>
+      <c r="I3" s="27">
+        <v>1</v>
+      </c>
+      <c r="J3" s="27">
+        <v>1</v>
+      </c>
+      <c r="K3" s="27">
+        <v>1</v>
+      </c>
+      <c r="M3" s="49">
+        <f>5+C3*D3*9*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2)*SQRT(E3))</f>
+        <v>14.9</v>
+      </c>
+      <c r="N3" s="49">
+        <f>40+(50+C3*D3*23)*SQRT(E3)*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2))</f>
+        <v>120.3</v>
+      </c>
+      <c r="O3" s="49">
+        <f>MAX(-318+C3*D3*390*1.3^(1-E3)/(1.2^(I3-2)*SQRT(E3)*J3*SQRT(K3)),50)</f>
+        <v>150</v>
+      </c>
+      <c r="P3" s="49">
+        <f>-240+C3*D3*950*SQRT(E3)*1.3^(1-E3)/(1.2^(I3-2)*J3*SQRT(K3))</f>
+        <v>900</v>
+      </c>
+      <c r="Q3" s="49">
+        <f>30/SQRT(E3)+(50+C3*D3)*K3/(J3*SQRT(E3))+30*(K3-1)</f>
+        <v>81</v>
+      </c>
+      <c r="R3" s="49">
+        <f>210+(190+C3*D3)*K3*SQRT(E3)/(J3*1.1^(I3-2))</f>
+        <v>420.1</v>
+      </c>
+      <c r="S3" s="49">
+        <f t="shared" ref="S3:S7" si="0">C3^1.38*D3^1.38*12*1.25^(1-E3)*J3/(SQRT(E3))</f>
+        <v>12</v>
+      </c>
+      <c r="T3" s="49">
+        <f t="shared" ref="T3:T7" si="1">88+C3^1.38*D3^1.38*32*1.25^(1-E3)*J3*SQRT(E3)/1</f>
+        <v>120</v>
+      </c>
+      <c r="U3" s="49">
+        <f>_xlfn.FLOOR.MATH(C3^0.9*D3^1.51+IF(D3&gt;16,C3^0.9*(D3-11)^1.51,0))*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="V3" s="49">
+        <f t="shared" ref="V3:V8" si="2">U3/25</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="34">
+        <v>10</v>
+      </c>
+      <c r="D4" s="27">
+        <v>20</v>
+      </c>
+      <c r="E4" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="27">
+        <v>3</v>
+      </c>
+      <c r="G4" s="27">
+        <v>1</v>
+      </c>
+      <c r="H4" s="27">
+        <v>1</v>
+      </c>
+      <c r="I4" s="27">
+        <v>1</v>
+      </c>
+      <c r="J4" s="27">
+        <v>1</v>
+      </c>
+      <c r="K4" s="27">
+        <v>1</v>
+      </c>
+      <c r="M4" s="49">
+        <f t="shared" ref="M4:M8" si="3">5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
+        <v>3135.6548835666954</v>
+      </c>
+      <c r="N4" s="49">
+        <f t="shared" ref="N4:N8" si="4">40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
+        <v>4083.7625579403157</v>
+      </c>
+      <c r="O4" s="49">
+        <f t="shared" ref="O4:O8" si="5">MAX(-318+C4*D4*390*1.3^(1-E4)/(1.2^(I4-2)*SQRT(E4)*J4*SQRT(K4)),50)</f>
+        <v>150607.46504814885</v>
+      </c>
+      <c r="P4" s="49">
+        <f t="shared" ref="P4:P8" si="6">-240+C4*D4*950*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(K4))</f>
+        <v>183579.47666120695</v>
+      </c>
+      <c r="Q4" s="49">
+        <f t="shared" ref="Q4:Q8" si="7">30/SQRT(E4)+(50+C4*D4)*K4/(J4*SQRT(E4))+30*(K4-1)</f>
+        <v>395.97979746446657</v>
+      </c>
+      <c r="R4" s="49">
+        <f t="shared" ref="R4:R8" si="8">210+(190+C4*D4)*K4*SQRT(E4)/(J4*1.1^(I4-2))</f>
+        <v>513.34880912902895</v>
+      </c>
+      <c r="S4" s="49">
+        <f t="shared" si="0"/>
+        <v>28416.634700313542</v>
+      </c>
+      <c r="T4" s="49">
+        <f t="shared" si="1"/>
+        <v>37976.846267084722</v>
+      </c>
+      <c r="U4" s="49">
+        <f t="shared" ref="U4:U8" si="9">_xlfn.FLOOR.MATH(C4^0.9*D4^1.51+IF(D4&gt;16,C4^0.9*(D4-11)^1.51,0))*1000</f>
+        <v>951000</v>
+      </c>
+      <c r="V4" s="49">
+        <f t="shared" si="2"/>
+        <v>38040</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C5" s="34">
+        <v>10</v>
+      </c>
+      <c r="D5" s="27">
+        <v>20</v>
+      </c>
+      <c r="E5" s="27">
+        <v>1</v>
+      </c>
+      <c r="F5" s="27">
+        <v>3</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1</v>
+      </c>
+      <c r="H5" s="27">
+        <v>1</v>
+      </c>
+      <c r="I5" s="27">
+        <v>1</v>
+      </c>
+      <c r="J5" s="27">
+        <v>1</v>
+      </c>
+      <c r="K5" s="27">
+        <v>1</v>
+      </c>
+      <c r="M5" s="49">
+        <f t="shared" si="3"/>
+        <v>1985</v>
+      </c>
+      <c r="N5" s="49">
+        <f t="shared" si="4"/>
+        <v>5155</v>
+      </c>
+      <c r="O5" s="49">
+        <f t="shared" si="5"/>
+        <v>93282</v>
+      </c>
+      <c r="P5" s="49">
+        <f t="shared" si="6"/>
+        <v>227760</v>
+      </c>
+      <c r="Q5" s="49">
+        <f t="shared" si="7"/>
+        <v>280</v>
+      </c>
+      <c r="R5" s="49">
+        <f t="shared" si="8"/>
+        <v>639</v>
+      </c>
+      <c r="S5" s="49">
+        <f t="shared" si="0"/>
+        <v>17972.257817993417</v>
+      </c>
+      <c r="T5" s="49">
+        <f t="shared" si="1"/>
+        <v>48014.020847982443</v>
+      </c>
+      <c r="U5" s="49">
+        <f t="shared" si="9"/>
+        <v>951000</v>
+      </c>
+      <c r="V5" s="49">
+        <f t="shared" si="2"/>
+        <v>38040</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C6" s="34">
+        <v>10</v>
+      </c>
+      <c r="D6" s="27">
+        <v>20</v>
+      </c>
+      <c r="E6" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="27">
+        <v>3</v>
+      </c>
+      <c r="G6" s="27">
+        <v>1</v>
+      </c>
+      <c r="H6" s="27">
+        <v>1</v>
+      </c>
+      <c r="I6" s="27">
+        <v>1</v>
+      </c>
+      <c r="J6" s="27">
+        <v>1</v>
+      </c>
+      <c r="K6" s="27">
+        <v>1</v>
+      </c>
+      <c r="M6" s="49">
+        <f t="shared" si="3"/>
+        <v>1450.9875518136387</v>
+      </c>
+      <c r="N6" s="49">
+        <f t="shared" si="4"/>
+        <v>5643.2017632778488</v>
+      </c>
+      <c r="O6" s="49">
+        <f t="shared" si="5"/>
+        <v>66710.352210090903</v>
+      </c>
+      <c r="P6" s="49">
+        <f t="shared" si="6"/>
+        <v>244671.286921486</v>
+      </c>
+      <c r="Q6" s="49">
+        <f t="shared" si="7"/>
+        <v>228.61904265976329</v>
+      </c>
+      <c r="R6" s="49">
+        <f t="shared" si="8"/>
+        <v>735.41554982699165</v>
+      </c>
+      <c r="S6" s="49">
+        <f t="shared" si="0"/>
+        <v>13125.08135495143</v>
+      </c>
+      <c r="T6" s="49">
+        <f t="shared" si="1"/>
+        <v>52588.325419805697</v>
+      </c>
+      <c r="U6" s="49">
+        <f t="shared" si="9"/>
+        <v>951000</v>
+      </c>
+      <c r="V6" s="49">
+        <f t="shared" si="2"/>
+        <v>38040</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="34">
+        <v>5</v>
+      </c>
+      <c r="D7" s="27">
+        <v>7</v>
+      </c>
+      <c r="E7" s="27">
+        <v>2</v>
+      </c>
+      <c r="F7" s="27">
+        <v>3</v>
+      </c>
+      <c r="G7" s="27">
+        <v>1</v>
+      </c>
+      <c r="H7" s="27">
+        <v>1</v>
+      </c>
+      <c r="I7" s="27">
+        <v>1</v>
+      </c>
+      <c r="J7" s="27">
+        <v>1</v>
+      </c>
+      <c r="K7" s="27">
+        <v>1</v>
+      </c>
+      <c r="M7" s="49">
+        <f t="shared" si="3"/>
+        <v>201.00999974491097</v>
+      </c>
+      <c r="N7" s="49">
+        <f t="shared" si="4"/>
+        <v>1104.0542843295168</v>
+      </c>
+      <c r="O7" s="49">
+        <f t="shared" si="5"/>
+        <v>8591.5454429504971</v>
+      </c>
+      <c r="P7" s="49">
+        <f t="shared" si="6"/>
+        <v>43165.477798989603</v>
+      </c>
+      <c r="Q7" s="49">
+        <f t="shared" si="7"/>
+        <v>81.317279836452954</v>
+      </c>
+      <c r="R7" s="49">
+        <f t="shared" si="8"/>
+        <v>560.01785668734101</v>
+      </c>
+      <c r="S7" s="49">
+        <f t="shared" si="0"/>
+        <v>917.42408287903868</v>
+      </c>
+      <c r="T7" s="49">
+        <f t="shared" si="1"/>
+        <v>4980.9284420215408</v>
+      </c>
+      <c r="U7" s="49">
+        <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="V7" s="49">
+        <f t="shared" si="2"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C8" s="36">
+        <v>5</v>
+      </c>
+      <c r="D8" s="37">
+        <v>20</v>
+      </c>
+      <c r="E8" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="37">
+        <v>4</v>
+      </c>
+      <c r="G8" s="37">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="37">
+        <v>10</v>
+      </c>
+      <c r="I8" s="37">
+        <v>3</v>
+      </c>
+      <c r="J8" s="37">
+        <v>1</v>
+      </c>
+      <c r="K8" s="37">
+        <v>2</v>
+      </c>
+      <c r="M8" s="48">
+        <f t="shared" si="3"/>
+        <v>136.21597027036952</v>
+      </c>
+      <c r="N8" s="48">
+        <f>40+(50+C8*D8*23)*SQRT(E8)*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2))</f>
+        <v>553.92921689228058</v>
+      </c>
+      <c r="O8" s="48">
+        <f t="shared" si="5"/>
+        <v>16139.014715109584</v>
+      </c>
+      <c r="P8" s="48">
+        <f t="shared" si="6"/>
+        <v>59891.399920592696</v>
+      </c>
+      <c r="Q8" s="48">
+        <f>30/SQRT(E8)+(50+C8*D8)*K8/(J8*SQRT(E8))+30*(K8-1)</f>
+        <v>299.44387170614959</v>
+      </c>
+      <c r="R8" s="48">
+        <f t="shared" si="8"/>
+        <v>855.77456855192861</v>
+      </c>
+      <c r="S8" s="48">
+        <f>C8^1.38*D8^1.38*12*1.25^(1-E8)*J8/(SQRT(E8))</f>
+        <v>5042.9029467027194</v>
+      </c>
+      <c r="T8" s="48">
+        <f>88+C8^1.38*D8^1.38*32*1.25^(1-E8)*J8*SQRT(E8)/1</f>
+        <v>20259.611786810874</v>
+      </c>
+      <c r="U8" s="48">
+        <f t="shared" si="9"/>
+        <v>509000</v>
+      </c>
+      <c r="V8" s="48">
+        <f t="shared" si="2"/>
+        <v>20360</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C10" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C11" s="24"/>
+      <c r="D11" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D17" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="H19" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>463</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>465</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>461</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>464</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>460</v>
-      </c>
-      <c r="M2" s="35" t="s">
-        <v>473</v>
-      </c>
-      <c r="N2" s="35" t="s">
-        <v>472</v>
-      </c>
-      <c r="O2" s="35" t="s">
-        <v>474</v>
-      </c>
-      <c r="P2" s="35" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q2" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="S2" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="T2" s="35" t="s">
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>412</v>
+      </c>
+      <c r="C21" s="40">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>437</v>
+      </c>
+      <c r="I21" s="40">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>415</v>
+      </c>
+      <c r="C22" s="40">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>438</v>
+      </c>
+      <c r="I22" s="40">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" s="34">
-        <v>1.5</v>
-      </c>
-      <c r="E3" s="27">
-        <v>1.5</v>
-      </c>
-      <c r="F3" s="27">
-        <v>1</v>
-      </c>
-      <c r="G3" s="27">
-        <v>1</v>
-      </c>
-      <c r="H3" s="27">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="40">
         <v>3</v>
       </c>
-      <c r="I3" s="27">
-        <v>20000</v>
-      </c>
-      <c r="J3" s="27">
-        <v>0</v>
-      </c>
-      <c r="K3" s="27">
-        <v>0</v>
-      </c>
-      <c r="M3" s="27">
-        <f>G3+H3*0.5+I3/D3+IF(D3&gt;3,K3*300/(D3-2),K3*300)+J3*0.5</f>
-        <v>13335.833333333334</v>
-      </c>
-      <c r="N3" s="27">
-        <f t="shared" ref="N3:R6" si="0">H3+I3*0.5+J3/E3+IF(E3&gt;3,L3*300/(E3-2),L3*300)+K3*0.5</f>
-        <v>10003</v>
-      </c>
-      <c r="O3" s="27">
-        <f t="shared" si="0"/>
-        <v>4020750</v>
-      </c>
-      <c r="P3" s="27">
-        <f t="shared" si="0"/>
-        <v>3007567.9166666665</v>
-      </c>
-      <c r="Q3" s="27">
-        <f t="shared" si="0"/>
-        <v>1206234446.7777777</v>
-      </c>
-      <c r="R3" s="27">
-        <f t="shared" si="0"/>
-        <v>2062161.447369722</v>
-      </c>
-      <c r="S3" s="27" t="e">
-        <f t="shared" ref="S3:S6" si="1">M3+N3*0.5+O3/J3+IF(J3&gt;3,Q3*300/(J3-2),Q3*300)+P3*0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T3" s="27" t="e">
-        <f t="shared" ref="T3:T6" si="2">N3+O3*0.5+P3/K3+IF(K3&gt;3,R3*300/(K3-2),R3*300)+Q3*0.5</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="E4" s="27">
-        <v>2</v>
-      </c>
-      <c r="F4" s="27">
-        <v>1</v>
-      </c>
-      <c r="G4" s="27">
-        <v>1</v>
-      </c>
-      <c r="H4" s="27">
+      <c r="H23" t="s">
+        <v>439</v>
+      </c>
+      <c r="I23" s="40">
         <v>3</v>
       </c>
-      <c r="I4" s="27">
-        <v>60000</v>
-      </c>
-      <c r="J4" s="27">
-        <v>0</v>
-      </c>
-      <c r="K4" s="27">
-        <v>300</v>
-      </c>
-      <c r="M4" s="27">
-        <f t="shared" ref="M4:M6" si="3">G4+H4*0.5+I4/D4+IF(D4&gt;3,K4*300/(D4-2),K4*300)+J4*0.5</f>
-        <v>77145.357142857145</v>
-      </c>
-      <c r="N4" s="27">
-        <f t="shared" si="0"/>
-        <v>30153</v>
-      </c>
-      <c r="O4" s="27">
-        <f t="shared" si="0"/>
-        <v>23203907.142857142</v>
-      </c>
-      <c r="P4" s="27">
-        <f t="shared" si="0"/>
-        <v>9084622.6785714291</v>
-      </c>
-      <c r="Q4" s="27">
-        <f t="shared" si="0"/>
-        <v>6961213234.4761896</v>
-      </c>
-      <c r="R4" s="27">
-        <f t="shared" si="0"/>
-        <v>11685951.380097108</v>
-      </c>
-      <c r="S4" s="27" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" s="27">
-        <f t="shared" si="2"/>
-        <v>3504033386.4691091</v>
-      </c>
-    </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D5" s="34">
+      <c r="J23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>418</v>
+      </c>
+      <c r="C24" s="40">
         <v>4</v>
       </c>
-      <c r="E5" s="27">
-        <v>2</v>
-      </c>
-      <c r="F5" s="27">
-        <v>1</v>
-      </c>
-      <c r="G5" s="27">
-        <v>1</v>
-      </c>
-      <c r="H5" s="27">
-        <v>3</v>
-      </c>
-      <c r="I5" s="27">
-        <v>50000</v>
-      </c>
-      <c r="J5" s="27">
-        <v>260000</v>
-      </c>
-      <c r="K5" s="27">
-        <v>0</v>
-      </c>
-      <c r="M5" s="27">
-        <f t="shared" si="3"/>
-        <v>142502.5</v>
-      </c>
-      <c r="N5" s="27">
-        <f t="shared" si="0"/>
-        <v>155003</v>
-      </c>
-      <c r="O5" s="27">
-        <f t="shared" si="0"/>
-        <v>42930750</v>
-      </c>
-      <c r="P5" s="27">
-        <f t="shared" si="0"/>
-        <v>46832151.25</v>
-      </c>
-      <c r="Q5" s="27">
-        <f t="shared" si="0"/>
-        <v>12879350002.333334</v>
-      </c>
-      <c r="R5" s="27">
-        <f t="shared" si="0"/>
-        <v>21817633.497725908</v>
-      </c>
-      <c r="S5" s="27">
-        <f t="shared" si="1"/>
-        <v>38497147.522136763</v>
-      </c>
-      <c r="T5" s="27" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C6" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" s="36">
-        <v>1</v>
-      </c>
-      <c r="E6" s="37">
-        <v>1</v>
-      </c>
-      <c r="F6" s="37">
-        <v>1</v>
-      </c>
-      <c r="G6" s="37">
-        <v>1</v>
-      </c>
-      <c r="H6" s="37">
-        <v>3</v>
-      </c>
-      <c r="I6" s="37">
-        <v>3</v>
-      </c>
-      <c r="J6" s="37">
-        <v>0</v>
-      </c>
-      <c r="K6" s="37">
-        <v>0</v>
-      </c>
-      <c r="M6" s="40">
-        <f t="shared" si="3"/>
-        <v>5.5</v>
-      </c>
-      <c r="N6" s="40">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="O6" s="40">
-        <f t="shared" si="0"/>
-        <v>1653</v>
-      </c>
-      <c r="P6" s="40">
-        <f t="shared" si="0"/>
-        <v>1352.75</v>
-      </c>
-      <c r="Q6" s="40">
-        <f t="shared" si="0"/>
-        <v>495904.08333333331</v>
-      </c>
-      <c r="R6" s="40">
-        <f t="shared" si="0"/>
-        <v>406655.75</v>
-      </c>
-      <c r="S6" s="40" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" s="40" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="D8" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E9" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E10" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="11" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E11" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="12" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E12" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="13" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E13" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="14" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E14" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="15" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C16" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="33" t="s">
-        <v>413</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>417</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>412</v>
-      </c>
-      <c r="D18" s="40">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>437</v>
-      </c>
-      <c r="I18" s="40">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>415</v>
-      </c>
-      <c r="D19" s="40">
-        <v>2</v>
-      </c>
-      <c r="H19" t="s">
-        <v>438</v>
-      </c>
-      <c r="I19" s="40">
-        <v>2</v>
-      </c>
-      <c r="J19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
-        <v>416</v>
-      </c>
-      <c r="D20" s="40">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>439</v>
-      </c>
-      <c r="I20" s="40">
-        <v>3</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="D24" t="s">
+        <v>429</v>
+      </c>
+      <c r="H24" t="s">
+        <v>440</v>
+      </c>
+      <c r="I24" s="40">
+        <v>5</v>
+      </c>
+      <c r="J24" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>418</v>
-      </c>
-      <c r="D21" s="40">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>429</v>
-      </c>
-      <c r="H21" t="s">
-        <v>440</v>
-      </c>
-      <c r="I21" s="40">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>419</v>
+      </c>
+      <c r="C25" s="40">
         <v>5</v>
       </c>
-      <c r="J21" t="s">
+      <c r="D25" t="s">
+        <v>426</v>
+      </c>
+      <c r="H25" t="s">
+        <v>441</v>
+      </c>
+      <c r="I25" s="40">
+        <v>7</v>
+      </c>
+      <c r="J25" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="40">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>426</v>
-      </c>
-      <c r="H22" t="s">
-        <v>441</v>
-      </c>
-      <c r="I22" s="40">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>420</v>
+      </c>
+      <c r="C26" s="40">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>428</v>
+      </c>
+      <c r="H26" t="s">
+        <v>442</v>
+      </c>
+      <c r="I26" s="40">
+        <v>9</v>
+      </c>
+      <c r="J26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>421</v>
+      </c>
+      <c r="C27" s="40">
         <v>7</v>
       </c>
-      <c r="J22" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>420</v>
-      </c>
-      <c r="D23" s="40">
-        <v>6</v>
-      </c>
-      <c r="E23" t="s">
-        <v>428</v>
-      </c>
-      <c r="H23" t="s">
-        <v>442</v>
-      </c>
-      <c r="I23" s="40">
-        <v>9</v>
-      </c>
-      <c r="J23" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>421</v>
-      </c>
-      <c r="D24" s="40">
-        <v>7</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D27" t="s">
         <v>427</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H27" t="s">
         <v>443</v>
       </c>
-      <c r="I24" s="40">
+      <c r="I27" s="40">
         <v>10</v>
-      </c>
-      <c r="J24" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>422</v>
-      </c>
-      <c r="D25" s="40">
-        <v>8</v>
-      </c>
-      <c r="H25" t="s">
-        <v>444</v>
-      </c>
-      <c r="I25" s="40">
-        <v>13</v>
-      </c>
-      <c r="J25" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>423</v>
-      </c>
-      <c r="D26" s="40">
-        <v>9</v>
-      </c>
-      <c r="H26" t="s">
-        <v>445</v>
-      </c>
-      <c r="I26" s="40">
-        <v>16</v>
-      </c>
-      <c r="J26" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
-        <v>424</v>
-      </c>
-      <c r="D27" s="44" t="s">
-        <v>425</v>
-      </c>
-      <c r="H27" t="s">
-        <v>446</v>
-      </c>
-      <c r="I27" s="40">
-        <v>25</v>
       </c>
       <c r="J27" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="H29" s="24" t="s">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>422</v>
+      </c>
+      <c r="C28" s="40">
+        <v>8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>444</v>
+      </c>
+      <c r="I28" s="40">
+        <v>13</v>
+      </c>
+      <c r="J28" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>423</v>
+      </c>
+      <c r="C29" s="40">
+        <v>9</v>
+      </c>
+      <c r="H29" t="s">
+        <v>445</v>
+      </c>
+      <c r="I29" s="40">
+        <v>16</v>
+      </c>
+      <c r="J29" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>424</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>425</v>
+      </c>
+      <c r="H30" t="s">
+        <v>446</v>
+      </c>
+      <c r="I30" s="40">
+        <v>20</v>
+      </c>
+      <c r="J30" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>479</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>480</v>
+      </c>
+      <c r="D32" s="44"/>
+      <c r="H32" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="I30" s="2" t="s">
+      <c r="I32" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I33" s="2" t="s">
         <v>448</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43C1F6A-8762-4C7E-9DE3-131E1FB8BBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7DA384-14F4-41A0-9A84-BC6B1B60950B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
     <sheet name="防具" sheetId="10" r:id="rId2"/>
     <sheet name="刀" sheetId="2" r:id="rId3"/>
     <sheet name="爆炸类" sheetId="3" r:id="rId4"/>
-    <sheet name="技能" sheetId="4" r:id="rId5"/>
-    <sheet name="装备价格" sheetId="5" r:id="rId6"/>
-    <sheet name="合成表成本" sheetId="11" r:id="rId7"/>
-    <sheet name="副本收益" sheetId="13" r:id="rId8"/>
-    <sheet name="怪物大致面板" sheetId="14" r:id="rId9"/>
-    <sheet name="经验辅助计算" sheetId="6" r:id="rId10"/>
-    <sheet name="根据等级计算怪物属性" sheetId="7" r:id="rId11"/>
+    <sheet name="装备价格" sheetId="5" r:id="rId5"/>
+    <sheet name="合成表成本" sheetId="11" r:id="rId6"/>
+    <sheet name="副本收益" sheetId="13" r:id="rId7"/>
+    <sheet name="怪物大致面板" sheetId="14" r:id="rId8"/>
+    <sheet name="经验辅助计算" sheetId="6" r:id="rId9"/>
+    <sheet name="技能格式" sheetId="4" r:id="rId10"/>
+    <sheet name="等级计算怪物属性" sheetId="7" r:id="rId11"/>
     <sheet name="伤害公式" sheetId="8" r:id="rId12"/>
     <sheet name="其余计算" sheetId="9" r:id="rId13"/>
     <sheet name="旧版-枪械" sheetId="1" r:id="rId14"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="497">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1805,10 +1805,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>例子：精英战术少女（盗贼）黑铁游侠（总堂前期）。可经常复数出现的低级精英</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>例子：军阀精英突击（军阀）黑铁武士（总堂后期）。注释：有威胁的精英怪，有时复数出现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1905,9 +1901,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>示例3</t>
-  </si>
-  <si>
     <t>你的怪物：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1924,45 +1917,74 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对应阶段和档次系数参考下方表格。这两项将决定整体数值大致水平。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>成长系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻速系数只看单次攻击动作的总时长和前后摇的长度，实际代表攻击节奏快慢，默认为3，范围为1~5，代表极慢、慢、中等、快、极快</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击倍率、段数系数均为大致平均值即可，攻击倍率默认为1~2，通常为1~3。段数系数默认为3，大致区间为1~10。攻击倍率为平均每次攻击的平均倍率，段数系数为平均每次攻击的平均段数。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>示例4</t>
-  </si>
-  <si>
-    <t>示例5</t>
-  </si>
-  <si>
-    <t>小僵尸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>成长系数代表战宠跟随等级的面板与经验成长率，范围为0.5-2，默认为1。系数高代表低级时更弱但高等级时更强。其他参数不变时攻击、HP、防御力可以分别用不同的成长系数，经验则取以上成长系数的均值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>高防低血系数代表这个单位是否有防御和血量的比例倾向，默认为1，范围为0.2~5。数值越高代表防御越高，血量越低。视觉和设定上更硬的单位应该给更高的高防低血系数。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>K点价格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>大致约等于推荐参考值即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胖僵尸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boss大僵尸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方舟武士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应阶段和档次系数参考下方表格。这两项将决定整体数值大致水平。对于拥有暖机、强力buff、多阶段等显著影响面板的特殊机制单位可能不适用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颜色标注：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑铁流锤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>例子：精英战术少女（盗贼）黑铁流锤（总堂前期）。可经常复数出现的低级精英</t>
+  </si>
+  <si>
+    <t>3~4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5~6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8~9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高防低血系数代表这个单位是否有防御和血量的比例倾向，默认为1，通常范围为0.2~5，最大范围为0.1~10。数值越高代表防御越高，血量越低。视觉和设定上更硬的单位应该给更高的高防低血系数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击倍率、段数系数均为大致平均值即可，攻击倍率默认为1~2，通常为1~3。段数系数默认为3，大致区间为1~10。攻击倍率为平均每次攻击的平均倍率，同理段数系数为每次平均段数。固定值伤害根据大致比例进行平均。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速系数只看单次攻击动作的总时长和前后摇的长度，实际代表攻击节奏快慢，默认为3，范围为1~5，代表极慢、慢、中等、快、极快。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3841,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" s="12">
         <v>0</v>
@@ -3852,11 +3874,11 @@
       </c>
       <c r="S8" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>10402.50499808108</v>
+        <v>10608.682012142001</v>
       </c>
       <c r="V8">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>10661.050257518782</v>
+        <v>10849.242444199579</v>
       </c>
       <c r="W8">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -3864,11 +3886,11 @@
       </c>
       <c r="X8">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
-        <v>41450.400000000001</v>
+        <v>42810.400000000001</v>
       </c>
       <c r="Y8">
         <f>表2_5[[#This Row],[平衡周期伤害]]*1.25^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>41450.400000000001</v>
+        <v>42810.400000000001</v>
       </c>
       <c r="Z8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3876,7 +3898,7 @@
       </c>
       <c r="AA8">
         <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>4993.5212356865841</v>
+        <v>5153.2323332905817</v>
       </c>
       <c r="AB8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3884,7 +3906,7 @@
       </c>
       <c r="AC8">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>5667.529021832197</v>
+        <v>5696.0101109089965</v>
       </c>
       <c r="AD8">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3900,7 +3922,7 @@
       </c>
       <c r="AG8">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>9349.3300693153997</v>
+        <v>9621.340695062765</v>
       </c>
       <c r="AH8">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
@@ -3916,11 +3938,11 @@
       </c>
       <c r="AK8">
         <f>0.9+(1.1-0.9)*表2_5[[#This Row],[冲击力]]/(表2_5[[#This Row],[冲击力]]+50)</f>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="AL8">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>1.07248463532297</v>
+        <v>1.0747551830293407</v>
       </c>
       <c r="AM8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3932,7 +3954,7 @@
       </c>
       <c r="AO8">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.97574861264204615</v>
+        <v>0.97782698346959784</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
@@ -5000,1050 +5022,300 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D62D51-4A85-49A4-AACE-F79C8F6223AF}">
-  <dimension ref="A2:R68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24AEF7F8-A3BA-4168-B91A-0B80F65D101C}">
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="8" max="8" width="9.9140625" customWidth="1"/>
-    <col min="11" max="11" width="4.9140625" customWidth="1"/>
-    <col min="12" max="12" width="9.4140625" customWidth="1"/>
-    <col min="13" max="13" width="9.58203125" customWidth="1"/>
-    <col min="14" max="14" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="7.75" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.75" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="J6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" t="s">
-        <v>90</v>
-      </c>
-      <c r="L7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M7" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" t="s">
-        <v>93</v>
-      </c>
-      <c r="O7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>10000</v>
-      </c>
-      <c r="D8">
-        <v>55000</v>
-      </c>
-      <c r="E8">
-        <v>60</v>
-      </c>
-      <c r="F8">
-        <f>(C8+(D8-C8)/(E8-1)*B8)</f>
-        <v>10762.71186440678</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>10000</v>
-      </c>
-      <c r="M8">
-        <v>55000</v>
-      </c>
-      <c r="N8">
-        <v>60</v>
-      </c>
-      <c r="O8">
-        <f>(L8+(M8-L8)/(N8-1)*K8)</f>
-        <v>10762.71186440678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>10000</v>
-      </c>
-      <c r="D9">
-        <v>55000</v>
-      </c>
-      <c r="E9">
-        <v>60</v>
-      </c>
-      <c r="F9">
-        <f>(C9+(D9-C9)/(E9-1)*B9)</f>
-        <v>11525.423728813559</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>10000</v>
-      </c>
-      <c r="M9">
-        <v>55000</v>
-      </c>
-      <c r="N9">
-        <v>60</v>
-      </c>
-      <c r="O9">
-        <f>(L9+(M9-L9)/(N9-1)*K9)</f>
-        <v>11525.423728813559</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>10000</v>
-      </c>
-      <c r="D10">
-        <v>55000</v>
-      </c>
-      <c r="E10">
-        <v>60</v>
-      </c>
-      <c r="F10">
-        <f t="shared" ref="F10:F17" si="0">(C10+(D10-C10)/(E10-1)*B10)</f>
-        <v>12288.135593220339</v>
-      </c>
-      <c r="K10">
-        <v>3</v>
-      </c>
-      <c r="L10">
-        <v>10000</v>
-      </c>
-      <c r="M10">
-        <v>55000</v>
-      </c>
-      <c r="N10">
-        <v>60</v>
-      </c>
-      <c r="O10">
-        <f t="shared" ref="O10" si="1">(L10+(M10-L10)/(N10-1)*K10)</f>
-        <v>12288.135593220339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>10000</v>
-      </c>
-      <c r="D11">
-        <v>55000</v>
-      </c>
-      <c r="E11">
-        <v>60</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>13050.847457627118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>10000</v>
-      </c>
-      <c r="D12">
-        <v>55000</v>
-      </c>
-      <c r="E12">
-        <v>60</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>13813.559322033898</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>10000</v>
-      </c>
-      <c r="D13">
-        <v>55000</v>
-      </c>
-      <c r="E13">
-        <v>60</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>14576.271186440677</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>10000</v>
-      </c>
-      <c r="D14">
-        <v>55000</v>
-      </c>
-      <c r="E14">
-        <v>60</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>15338.983050847459</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15">
-        <v>10000</v>
-      </c>
-      <c r="D15">
-        <v>55000</v>
-      </c>
-      <c r="E15">
-        <v>60</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>16101.694915254237</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>9</v>
-      </c>
-      <c r="C16">
-        <v>10000</v>
-      </c>
-      <c r="D16">
-        <v>55000</v>
-      </c>
-      <c r="E16">
-        <v>60</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>16864.406779661018</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17">
-        <v>10000</v>
-      </c>
-      <c r="D17">
-        <v>55000</v>
-      </c>
-      <c r="E17">
-        <v>60</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>17627.118644067796</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>10</v>
-      </c>
-      <c r="D20">
-        <v>20000</v>
-      </c>
-      <c r="E20">
-        <v>60</v>
-      </c>
-      <c r="F20">
-        <f>(C20+(D20-C20)/(E20-1)*B20)</f>
-        <v>348.81355932203388</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>10</v>
-      </c>
-      <c r="D21">
-        <v>20000</v>
-      </c>
-      <c r="E21">
-        <v>60</v>
-      </c>
-      <c r="F21">
-        <f>(C21+(D21-C21)/(E21-1)*B21)</f>
-        <v>687.62711864406776</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>10</v>
-      </c>
-      <c r="D22">
-        <v>20000</v>
-      </c>
-      <c r="E22">
-        <v>60</v>
-      </c>
-      <c r="F22">
-        <f t="shared" ref="F22:F29" si="2">(C22+(D22-C22)/(E22-1)*B22)</f>
-        <v>1026.4406779661017</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23">
-        <v>10</v>
-      </c>
-      <c r="D23">
-        <v>20000</v>
-      </c>
-      <c r="E23">
-        <v>60</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="2"/>
-        <v>1365.2542372881355</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24">
-        <v>10</v>
-      </c>
-      <c r="D24">
-        <v>20000</v>
-      </c>
-      <c r="E24">
-        <v>60</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="2"/>
-        <v>1704.0677966101694</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="D25">
-        <v>20000</v>
-      </c>
-      <c r="E25">
-        <v>60</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="2"/>
-        <v>2042.8813559322034</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B26">
-        <v>7</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>20000</v>
-      </c>
-      <c r="E26">
-        <v>60</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="2"/>
-        <v>2381.694915254237</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B27">
-        <v>8</v>
-      </c>
-      <c r="C27">
-        <v>10</v>
-      </c>
-      <c r="D27">
-        <v>20000</v>
-      </c>
-      <c r="E27">
-        <v>60</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="2"/>
-        <v>2720.5084745762711</v>
-      </c>
-      <c r="Q27">
-        <f>SUM(O8:O119)</f>
-        <v>34576.271186440674</v>
-      </c>
-      <c r="R27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B28">
-        <v>9</v>
-      </c>
-      <c r="C28">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>20000</v>
-      </c>
-      <c r="E28">
-        <v>60</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="2"/>
-        <v>3059.3220338983051</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B29">
-        <v>10</v>
-      </c>
-      <c r="C29">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>20000</v>
-      </c>
-      <c r="E29">
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="2"/>
-        <v>3398.1355932203387</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B30">
-        <v>11</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>20000</v>
-      </c>
-      <c r="E30">
-        <v>60</v>
-      </c>
-      <c r="F30">
-        <f>(C30+(D30-C30)/(E30-1)*B30)</f>
-        <v>3736.9491525423728</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>12</v>
-      </c>
-      <c r="C31">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>20000</v>
-      </c>
-      <c r="E31">
-        <v>60</v>
-      </c>
-      <c r="F31">
-        <f>(C31+(D31-C31)/(E31-1)*B31)</f>
-        <v>4075.7627118644068</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <v>13</v>
-      </c>
-      <c r="C32">
-        <v>10</v>
-      </c>
-      <c r="D32">
-        <v>20000</v>
-      </c>
-      <c r="E32">
-        <v>60</v>
-      </c>
-      <c r="F32">
-        <f t="shared" ref="F32:F38" si="3">(C32+(D32-C32)/(E32-1)*B32)</f>
-        <v>4414.5762711864409</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33">
-        <v>14</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-      <c r="D33">
-        <v>20000</v>
-      </c>
-      <c r="E33">
-        <v>60</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="3"/>
-        <v>4753.389830508474</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34">
-        <v>15</v>
-      </c>
-      <c r="C34">
-        <v>10</v>
-      </c>
-      <c r="D34">
-        <v>20000</v>
-      </c>
-      <c r="E34">
-        <v>60</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="3"/>
-        <v>5092.2033898305081</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35">
-        <v>16</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>20000</v>
-      </c>
-      <c r="E35">
-        <v>60</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="3"/>
-        <v>5431.0169491525421</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36">
-        <v>17</v>
-      </c>
-      <c r="C36">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <v>20000</v>
-      </c>
-      <c r="E36">
-        <v>60</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="3"/>
-        <v>5769.8305084745762</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37">
-        <v>18</v>
-      </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>20000</v>
-      </c>
-      <c r="E37">
-        <v>60</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="3"/>
-        <v>6108.6440677966102</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38">
-        <v>19</v>
-      </c>
-      <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>20000</v>
-      </c>
-      <c r="E38">
-        <v>60</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="3"/>
-        <v>6447.4576271186434</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39">
-        <v>20</v>
-      </c>
-      <c r="C39">
-        <v>10</v>
-      </c>
-      <c r="D39">
-        <v>20000</v>
-      </c>
-      <c r="E39">
-        <v>60</v>
-      </c>
-      <c r="F39">
-        <f>(C39+(D39-C39)/(E39-1)*B39)</f>
-        <v>6786.2711864406774</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B40">
-        <v>21</v>
-      </c>
-      <c r="C40">
-        <v>10</v>
-      </c>
-      <c r="D40">
-        <v>20000</v>
-      </c>
-      <c r="E40">
-        <v>60</v>
-      </c>
-      <c r="F40">
-        <f>(C40+(D40-C40)/(E40-1)*B40)</f>
-        <v>7125.0847457627115</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41">
-        <v>22</v>
-      </c>
-      <c r="C41">
-        <v>10</v>
-      </c>
-      <c r="D41">
-        <v>20000</v>
-      </c>
-      <c r="E41">
-        <v>60</v>
-      </c>
-      <c r="F41">
-        <f t="shared" ref="F41:F48" si="4">(C41+(D41-C41)/(E41-1)*B41)</f>
-        <v>7463.8983050847455</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42">
-        <v>23</v>
-      </c>
-      <c r="C42">
-        <v>10</v>
-      </c>
-      <c r="D42">
-        <v>20000</v>
-      </c>
-      <c r="E42">
-        <v>60</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="4"/>
-        <v>7802.7118644067796</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43">
-        <v>24</v>
-      </c>
-      <c r="C43">
-        <v>10</v>
-      </c>
-      <c r="D43">
-        <v>20000</v>
-      </c>
-      <c r="E43">
-        <v>60</v>
-      </c>
-      <c r="F43">
-        <f t="shared" si="4"/>
-        <v>8141.5254237288136</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44">
-        <v>25</v>
-      </c>
-      <c r="C44">
-        <v>10</v>
-      </c>
-      <c r="D44">
-        <v>20000</v>
-      </c>
-      <c r="E44">
-        <v>60</v>
-      </c>
-      <c r="F44">
-        <f t="shared" si="4"/>
-        <v>8480.3389830508477</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45">
-        <v>26</v>
-      </c>
-      <c r="C45">
-        <v>10</v>
-      </c>
-      <c r="D45">
-        <v>20000</v>
-      </c>
-      <c r="E45">
-        <v>60</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="4"/>
-        <v>8819.1525423728817</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46">
-        <v>27</v>
-      </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>20000</v>
-      </c>
-      <c r="E46">
-        <v>60</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="4"/>
-        <v>9157.966101694914</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47">
-        <v>28</v>
-      </c>
-      <c r="C47">
-        <v>10</v>
-      </c>
-      <c r="D47">
-        <v>20000</v>
-      </c>
-      <c r="E47">
-        <v>60</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="4"/>
-        <v>9496.779661016948</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48">
-        <v>29</v>
-      </c>
-      <c r="C48">
-        <v>10</v>
-      </c>
-      <c r="D48">
-        <v>20000</v>
-      </c>
-      <c r="E48">
-        <v>60</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="4"/>
-        <v>9835.5932203389821</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49">
-        <v>30</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49">
-        <v>20000</v>
-      </c>
-      <c r="E49">
-        <v>60</v>
-      </c>
-      <c r="F49">
-        <f>(C49+(D49-C49)/(E49-1)*B49)</f>
-        <v>10174.406779661016</v>
-      </c>
-      <c r="H49">
-        <f>SUM(F20:F49)</f>
-        <v>157848.30508474578</v>
-      </c>
-      <c r="I49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50">
-        <v>31</v>
-      </c>
-      <c r="C50">
-        <v>10</v>
-      </c>
-      <c r="D50">
-        <v>20000</v>
-      </c>
-      <c r="E50">
-        <v>60</v>
-      </c>
-      <c r="F50">
-        <f t="shared" ref="F50:F59" si="5">(C50+(D50-C50)/(E50-1)*B50)</f>
-        <v>10513.22033898305</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51">
-        <v>32</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>20000</v>
-      </c>
-      <c r="E51">
-        <v>60</v>
-      </c>
-      <c r="F51">
-        <f t="shared" si="5"/>
-        <v>10852.033898305084</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52">
-        <v>33</v>
-      </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="D52">
-        <v>20000</v>
-      </c>
-      <c r="E52">
-        <v>60</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="5"/>
-        <v>11190.847457627118</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53">
-        <v>34</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-      <c r="D53">
-        <v>20000</v>
-      </c>
-      <c r="E53">
-        <v>60</v>
-      </c>
-      <c r="F53">
-        <f t="shared" si="5"/>
-        <v>11529.661016949152</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54">
-        <v>35</v>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-      <c r="D54">
-        <v>20000</v>
-      </c>
-      <c r="E54">
-        <v>60</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="5"/>
-        <v>11868.474576271186</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55">
-        <v>36</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
-      </c>
-      <c r="D55">
-        <v>20000</v>
-      </c>
-      <c r="E55">
-        <v>60</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="5"/>
-        <v>12207.28813559322</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B56">
-        <v>37</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>20000</v>
-      </c>
-      <c r="E56">
-        <v>60</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="5"/>
-        <v>12546.101694915254</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57">
-        <v>38</v>
-      </c>
-      <c r="C57">
-        <v>10</v>
-      </c>
-      <c r="D57">
-        <v>20000</v>
-      </c>
-      <c r="E57">
-        <v>60</v>
-      </c>
-      <c r="F57">
-        <f t="shared" si="5"/>
-        <v>12884.915254237287</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58">
-        <v>39</v>
-      </c>
-      <c r="C58">
-        <v>10</v>
-      </c>
-      <c r="D58">
-        <v>20000</v>
-      </c>
-      <c r="E58">
-        <v>60</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="5"/>
-        <v>13223.728813559321</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B59">
-        <v>40</v>
-      </c>
-      <c r="C59">
-        <v>10</v>
-      </c>
-      <c r="D59">
-        <v>20000</v>
-      </c>
-      <c r="E59">
-        <v>60</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="5"/>
-        <v>13562.542372881355</v>
-      </c>
-      <c r="H59">
-        <f>SUM(F20:F59)</f>
-        <v>278227.11864406784</v>
-      </c>
-      <c r="I59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H68">
-        <f>SUM(F20:F128)</f>
-        <v>278227.11864406784</v>
-      </c>
-      <c r="I68" t="s">
-        <v>99</v>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" t="str">
+        <f>"子弹威力 = "&amp;D3&amp;" ( _parent._parent.空手攻击力 "&amp;F3&amp;E3&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G3&amp;")"&amp;J3</f>
+        <v>子弹威力 = 100+ ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)+_parent._parent.等级*10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" t="str">
+        <f>"子弹威力 = "&amp;D4&amp;" ( _parent._parent.空手攻击力 "&amp;F4&amp;E4&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G4&amp;")"&amp;J4</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" t="str">
+        <f>"子弹威力 = "&amp;D5&amp;" ( _parent._parent.空手攻击力 "&amp;F5&amp;E5&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G5&amp;")"&amp;J5</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" t="str">
+        <f>"子弹威力 = "&amp;D12&amp;" ( _parent._parent.空手攻击力 "&amp;F12&amp;E12&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G12&amp;")"&amp;J12</f>
+        <v>子弹威力 = 500+ ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)+_parent._parent.等级*10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" t="str">
+        <f>"子弹威力 = "&amp;D13&amp;" ( _parent._parent.空手攻击力 "&amp;F13&amp;E13&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G13&amp;")"&amp;J13</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" t="str">
+        <f>"子弹威力 = "&amp;D14&amp;" ( _parent._parent.空手攻击力 "&amp;F14&amp;E14&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G14&amp;")"&amp;J14</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" t="str">
+        <f>"子弹威力 = "&amp;D20&amp;" ( _parent._parent.空手攻击力 "&amp;F20&amp;E20&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G20&amp;" )"&amp;I20&amp;"( _parent._parent.刀属性数组[13]"&amp;H20&amp;" )"&amp;J3</f>
+        <v>子弹威力 = 500+ ( _parent._parent.空手攻击力 /5+100 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13]+100 )+_parent._parent.等级*10</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" t="str">
+        <f>"子弹威力 = "&amp;D21&amp;" ( _parent._parent.空手攻击力 "&amp;F21&amp;E21&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G21&amp;" )"&amp;I21&amp;"( _parent._parent.刀属性数组[13]"&amp;H21&amp;" )"&amp;J4</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 /5 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13] )</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L22" t="str">
+        <f>"子弹威力 = "&amp;D22&amp;" ( _parent._parent.空手攻击力 "&amp;F22&amp;E22&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G22&amp;" )"&amp;I22&amp;"( _parent._parent.刀属性数组[13]"&amp;H22&amp;" )"&amp;J5</f>
+        <v>子弹威力 =  ( _parent._parent.空手攻击力 /5+100 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13] )</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="K26" s="4"/>
+      <c r="L26" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="C30" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15481,44 +14753,44 @@
     <row r="29" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C29">
         <f>21000+5*D29</f>
-        <v>61000</v>
+        <v>23650</v>
       </c>
       <c r="D29">
-        <v>8000</v>
+        <v>530</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
         <f>D29*(1-E29)</f>
-        <v>8000</v>
+        <v>530</v>
       </c>
       <c r="G29">
         <f>1-(1-(F29/(F29+300)))</f>
-        <v>0.96385542168674698</v>
+        <v>0.63855421686746983</v>
       </c>
       <c r="H29">
         <f>(1-(F29/(F29+300)))</f>
-        <v>3.6144578313253017E-2</v>
+        <v>0.36144578313253017</v>
       </c>
       <c r="J29">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="K29">
         <f>J29/H29</f>
-        <v>276666.66666666663</v>
+        <v>221333.33333333331</v>
       </c>
       <c r="M29">
         <f>C29*(1-(F29/(F29+300)))</f>
-        <v>2204.8192771084341</v>
+        <v>8548.1927710843393</v>
       </c>
       <c r="N29">
         <f>M28-M29</f>
-        <v>-1761.4695234138535</v>
+        <v>-8104.8430173897586</v>
       </c>
       <c r="O29">
         <f t="shared" si="4"/>
-        <v>4.5355191256830594</v>
+        <v>9.3587033121916843</v>
       </c>
       <c r="S29">
         <f>1300/18000</f>
@@ -15534,79 +14806,79 @@
     <row r="31" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C31">
         <f>25000+3.5*D31*0.9</f>
-        <v>50200</v>
+        <v>30670</v>
       </c>
       <c r="D31">
-        <v>8000</v>
+        <v>1800</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
         <f>D31*(1-E31)</f>
-        <v>8000</v>
+        <v>1800</v>
       </c>
       <c r="G31">
         <f>1-(1-(F31/(F31+300)))</f>
-        <v>0.96385542168674698</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="H31">
         <f>(1-(F31/(F31+300)))</f>
-        <v>3.6144578313253017E-2</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="J31">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="K31">
         <f>J31/H31</f>
-        <v>276666.66666666663</v>
+        <v>279999.99999999988</v>
       </c>
       <c r="M31">
         <f>C31*(1-(F31/(F31+300)))</f>
-        <v>1814.4578313253014</v>
+        <v>4381.4285714285725</v>
       </c>
       <c r="O31">
         <f t="shared" si="4"/>
-        <v>5.5112881806108893</v>
+        <v>9.1294424519073978</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C32">
         <f>25000+3.5*D32*0.9</f>
-        <v>88000</v>
+        <v>25866.25</v>
       </c>
       <c r="D32">
-        <v>20000</v>
+        <v>275</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
         <f>D32*(1-E32)</f>
-        <v>20000</v>
+        <v>275</v>
       </c>
       <c r="G32">
         <f>1-(1-(F32/(F32+300)))</f>
-        <v>0.98522167487684731</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="H32">
         <f>(1-(F32/(F32+300)))</f>
-        <v>1.4778325123152691E-2</v>
+        <v>0.52173913043478259</v>
       </c>
       <c r="J32">
-        <v>10000</v>
+        <v>180000</v>
       </c>
       <c r="K32">
         <f>J32/H32</f>
-        <v>676666.66666666744</v>
+        <v>345000</v>
       </c>
       <c r="M32">
         <f>C32*(1-(F32/(F32+300)))</f>
-        <v>1300.4926108374368</v>
+        <v>13495.434782608696</v>
       </c>
       <c r="O32">
         <f t="shared" si="4"/>
-        <v>7.6893939393939483</v>
+        <v>13.337843715266033</v>
       </c>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.3">
@@ -19025,7 +18297,6 @@
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -19630,304 +18901,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24AEF7F8-A3BA-4168-B91A-0B80F65D101C}">
-  <dimension ref="A1:AC30"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="7.75" customWidth="1"/>
-    <col min="5" max="5" width="11.58203125" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" t="str">
-        <f>"子弹威力 = "&amp;D3&amp;" ( _parent._parent.空手攻击力 "&amp;F3&amp;E3&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G3&amp;")"&amp;J3</f>
-        <v>子弹威力 = 100+ ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)+_parent._parent.等级*10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" t="str">
-        <f>"子弹威力 = "&amp;D4&amp;" ( _parent._parent.空手攻击力 "&amp;F4&amp;E4&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G4&amp;")"&amp;J4</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" t="str">
-        <f>"子弹威力 = "&amp;D5&amp;" ( _parent._parent.空手攻击力 "&amp;F5&amp;E5&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G5&amp;")"&amp;J5</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 *1+100 ) *(1+_parent._parent.技能等级*1)</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="K8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L12" t="str">
-        <f>"子弹威力 = "&amp;D12&amp;" ( _parent._parent.空手攻击力 "&amp;F12&amp;E12&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G12&amp;")"&amp;J12</f>
-        <v>子弹威力 = 500+ ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)+_parent._parent.等级*10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" t="str">
-        <f>"子弹威力 = "&amp;D13&amp;" ( _parent._parent.空手攻击力 "&amp;F13&amp;E13&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G13&amp;")"&amp;J13</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G14" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" t="str">
-        <f>"子弹威力 = "&amp;D14&amp;" ( _parent._parent.空手攻击力 "&amp;F14&amp;E14&amp;" ) "&amp;"*(1+_parent._parent.技能等级"&amp;G14&amp;")"&amp;J14</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 /3+100 ) *(1+_parent._parent.技能等级*1)</v>
-      </c>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="K17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L20" t="str">
-        <f>"子弹威力 = "&amp;D20&amp;" ( _parent._parent.空手攻击力 "&amp;F20&amp;E20&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G20&amp;" )"&amp;I20&amp;"( _parent._parent.刀属性数组[13]"&amp;H20&amp;" )"&amp;J3</f>
-        <v>子弹威力 = 500+ ( _parent._parent.空手攻击力 /5+100 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13]+100 )+_parent._parent.等级*10</v>
-      </c>
-      <c r="AC20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" t="str">
-        <f>"子弹威力 = "&amp;D21&amp;" ( _parent._parent.空手攻击力 "&amp;F21&amp;E21&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G21&amp;" )"&amp;I21&amp;"( _parent._parent.刀属性数组[13]"&amp;H21&amp;" )"&amp;J4</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 /5 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13] )</v>
-      </c>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="C22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L22" t="str">
-        <f>"子弹威力 = "&amp;D22&amp;" ( _parent._parent.空手攻击力 "&amp;F22&amp;E22&amp;" ) "&amp;"*( 1+_parent._parent.技能等级"&amp;G22&amp;" )"&amp;I22&amp;"( _parent._parent.刀属性数组[13]"&amp;H22&amp;" )"&amp;J5</f>
-        <v>子弹威力 =  ( _parent._parent.空手攻击力 /5+100 ) *( 1+_parent._parent.技能等级*1 )+1*( _parent._parent.刀属性数组[13] )</v>
-      </c>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="K25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="K26" s="4"/>
-      <c r="L26" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="C30" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B594D0C1-9717-419C-89F7-CC28A4B63F17}">
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -20278,7 +19251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF21AD2-DDB9-4BC1-9A90-C782109DDD58}">
   <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -21082,7 +20055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64F594B-8471-4760-8349-0BF477107C61}">
   <dimension ref="C2:P32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -21784,13 +20757,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D334537-191E-473E-8F5E-E80A13E62C45}">
-  <dimension ref="B1:V33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.75" customWidth="1"/>
-    <col min="2" max="2" width="8.9140625" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
     <col min="4" max="4" width="8.5" customWidth="1"/>
     <col min="5" max="5" width="7.9140625" customWidth="1"/>
     <col min="6" max="6" width="8.25" customWidth="1"/>
@@ -21807,12 +20780,12 @@
     <col min="21" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="M1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C2" s="33" t="s">
         <v>238</v>
       </c>
@@ -21820,69 +20793,69 @@
         <v>435</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="G2" s="33" t="s">
         <v>460</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="H2" s="33" t="s">
+        <v>462</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>461</v>
       </c>
-      <c r="H2" s="33" t="s">
-        <v>463</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>462</v>
-      </c>
       <c r="K2" s="33" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M2" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="O2" s="35" t="s">
         <v>468</v>
       </c>
-      <c r="N2" s="35" t="s">
-        <v>467</v>
-      </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="R2" s="35" t="s">
         <v>469</v>
       </c>
-      <c r="P2" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q2" s="35" t="s">
+      <c r="S2" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="R2" s="35" t="s">
-        <v>470</v>
-      </c>
-      <c r="S2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>472</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>473</v>
       </c>
       <c r="U2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
       </c>
       <c r="D3" s="27">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" s="27">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="27">
         <v>3</v>
@@ -21897,208 +20870,208 @@
         <v>1</v>
       </c>
       <c r="J3" s="27">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K3" s="27">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M3" s="49">
         <f>5+C3*D3*9*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2)*SQRT(E3))</f>
-        <v>14.9</v>
+        <v>18.888439450165926</v>
       </c>
       <c r="N3" s="49">
         <f>40+(50+C3*D3*23)*SQRT(E3)*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2))</f>
-        <v>120.3</v>
+        <v>109.54507458009012</v>
       </c>
       <c r="O3" s="49">
-        <f>MAX(-318+C3*D3*390*1.3^(1-E3)/(1.2^(I3-2)*SQRT(E3)*J3*SQRT(K3)),50)</f>
-        <v>150</v>
+        <f t="shared" ref="O3:O6" si="0">MAX(200*(D3-2)+C3*D3*293*1.3^(1-E3)/(1.2^(I3-2)*SQRT(E3)*J3*SQRT(K3)),50)</f>
+        <v>581.27450879982621</v>
       </c>
       <c r="P3" s="49">
-        <f>-240+C3*D3*950*SQRT(E3)*1.3^(1-E3)/(1.2^(I3-2)*J3*SQRT(K3))</f>
-        <v>900</v>
+        <f>MAX(180*(D3-2)+C3*D3*900*SQRT(E3)*1.3^(1-E3)/(1.2^(I3-2)*J3*SQRT(K3)),100)</f>
+        <v>1584.1216598494022</v>
       </c>
       <c r="Q3" s="49">
         <f>30/SQRT(E3)+(50+C3*D3)*K3/(J3*SQRT(E3))+30*(K3-1)</f>
-        <v>81</v>
+        <v>136.10648909600368</v>
       </c>
       <c r="R3" s="49">
         <f>210+(190+C3*D3)*K3*SQRT(E3)/(J3*1.1^(I3-2))</f>
-        <v>420.1</v>
+        <v>516.16801764921502</v>
       </c>
       <c r="S3" s="49">
-        <f t="shared" ref="S3:S7" si="0">C3^1.38*D3^1.38*12*1.25^(1-E3)*J3/(SQRT(E3))</f>
-        <v>12</v>
+        <f>C3^1.15*D3^1.2*12*1.25^(1-E3)/(SQRT(E3))*IF(D3&gt;17,1.2^(D3-15),1)</f>
+        <v>22.820637166202172</v>
       </c>
       <c r="T3" s="49">
-        <f t="shared" ref="T3:T7" si="1">88+C3^1.38*D3^1.38*32*1.25^(1-E3)*J3*SQRT(E3)/1</f>
-        <v>120</v>
+        <f>95+C3^1*D3^1.58*33*1.25^(1-E3)*SQRT(E3)/1+IF(C3&gt;=6,C3*200,0)</f>
+        <v>153.56863807482276</v>
       </c>
       <c r="U3" s="49">
-        <f>_xlfn.FLOOR.MATH(C3^0.9*D3^1.51+IF(D3&gt;16,C3^0.9*(D3-11)^1.51,0))*1000</f>
-        <v>1000</v>
+        <f>_xlfn.FLOOR.MATH(2*C3^1.3*D3^1.3+IF(D3&gt;2,D3*10,0)+IF(D3&gt;8,C3^0.5*D3^0.7)+IF(D3&gt;16,C3^1.2*(D3-15)^2.5,0))*500</f>
+        <v>1500</v>
       </c>
       <c r="V3" s="49">
-        <f t="shared" ref="V3:V8" si="2">U3/25</f>
+        <f>_xlfn.FLOOR.MATH(U3/700)*20</f>
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>97</v>
+        <v>485</v>
       </c>
       <c r="C4" s="34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4" s="27">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E4" s="27">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F4" s="27">
+        <v>2</v>
+      </c>
+      <c r="G4" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="H4" s="27">
+        <v>2</v>
+      </c>
+      <c r="I4" s="27">
+        <v>1</v>
+      </c>
+      <c r="J4" s="27">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K4" s="27">
+        <v>2.9</v>
+      </c>
+      <c r="M4" s="49">
+        <f t="shared" ref="M4:M8" si="1">5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
+        <v>87.608658193499167</v>
+      </c>
+      <c r="N4" s="49">
+        <f t="shared" ref="N4:N7" si="2">40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
+        <v>237.13108861217921</v>
+      </c>
+      <c r="O4" s="49">
+        <f t="shared" si="0"/>
+        <v>5075.0421198956528</v>
+      </c>
+      <c r="P4" s="49">
+        <f t="shared" ref="P4:P7" si="3">MAX(180*(D4-2)+C4*D4*900*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(K4)),100)</f>
+        <v>9044.9499191975083</v>
+      </c>
+      <c r="Q4" s="49">
+        <f t="shared" ref="Q4:Q7" si="4">30/SQRT(E4)+(50+C4*D4)*K4/(J4*SQRT(E4))+30*(K4-1)</f>
+        <v>276.23630124850206</v>
+      </c>
+      <c r="R4" s="49">
+        <f t="shared" ref="R4:R8" si="5">210+(190+C4*D4)*K4*SQRT(E4)/(J4*1.1^(I4-2))</f>
+        <v>736.54928734165037</v>
+      </c>
+      <c r="S4" s="49">
+        <f t="shared" ref="S4:S8" si="6">C4^1.15*D4^1.2*12*1.25^(1-E4)/(SQRT(E4))*IF(D4&gt;17,1.2^(D4-15),1)</f>
+        <v>304.61429344689395</v>
+      </c>
+      <c r="T4" s="49">
+        <f t="shared" ref="T4:T8" si="7">95+C4^1*D4^1.58*33*1.25^(1-E4)*SQRT(E4)/1+IF(C4&gt;=6,C4*200,0)</f>
+        <v>1871.1164335978647</v>
+      </c>
+      <c r="U4" s="49">
+        <f t="shared" ref="U4:U8" si="8">_xlfn.FLOOR.MATH(2*C4^1.3*D4^1.3+IF(D4&gt;2,D4*10,0)+IF(D4&gt;8,C4^0.5*D4^0.7)+IF(D4&gt;16,C4^1.2*(D4-15)^2.5,0))*500</f>
+        <v>96000</v>
+      </c>
+      <c r="V4" s="49">
+        <f t="shared" ref="V4:V9" si="9">_xlfn.FLOOR.MATH(U4/700)*20</f>
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5" s="34">
         <v>3</v>
       </c>
-      <c r="G4" s="27">
-        <v>1</v>
-      </c>
-      <c r="H4" s="27">
-        <v>1</v>
-      </c>
-      <c r="I4" s="27">
-        <v>1</v>
-      </c>
-      <c r="J4" s="27">
-        <v>1</v>
-      </c>
-      <c r="K4" s="27">
-        <v>1</v>
-      </c>
-      <c r="M4" s="49">
-        <f t="shared" ref="M4:M8" si="3">5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
-        <v>3135.6548835666954</v>
-      </c>
-      <c r="N4" s="49">
-        <f t="shared" ref="N4:N8" si="4">40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
-        <v>4083.7625579403157</v>
-      </c>
-      <c r="O4" s="49">
-        <f t="shared" ref="O4:O8" si="5">MAX(-318+C4*D4*390*1.3^(1-E4)/(1.2^(I4-2)*SQRT(E4)*J4*SQRT(K4)),50)</f>
-        <v>150607.46504814885</v>
-      </c>
-      <c r="P4" s="49">
-        <f t="shared" ref="P4:P8" si="6">-240+C4*D4*950*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(K4))</f>
-        <v>183579.47666120695</v>
-      </c>
-      <c r="Q4" s="49">
-        <f t="shared" ref="Q4:Q8" si="7">30/SQRT(E4)+(50+C4*D4)*K4/(J4*SQRT(E4))+30*(K4-1)</f>
-        <v>395.97979746446657</v>
-      </c>
-      <c r="R4" s="49">
-        <f t="shared" ref="R4:R8" si="8">210+(190+C4*D4)*K4*SQRT(E4)/(J4*1.1^(I4-2))</f>
-        <v>513.34880912902895</v>
-      </c>
-      <c r="S4" s="49">
+      <c r="D5" s="27">
+        <v>13</v>
+      </c>
+      <c r="E5" s="27">
+        <v>1.3</v>
+      </c>
+      <c r="F5" s="27">
+        <v>4</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="27">
+        <v>3</v>
+      </c>
+      <c r="I5" s="27">
+        <v>3</v>
+      </c>
+      <c r="J5" s="27">
+        <v>0.9</v>
+      </c>
+      <c r="K5" s="27">
+        <v>2</v>
+      </c>
+      <c r="M5" s="49">
+        <f t="shared" si="1"/>
+        <v>80.557769388855888</v>
+      </c>
+      <c r="N5" s="49">
+        <f t="shared" si="2"/>
+        <v>305.01188004165385</v>
+      </c>
+      <c r="O5" s="49">
         <f t="shared" si="0"/>
-        <v>28416.634700313542</v>
-      </c>
-      <c r="T4" s="49">
-        <f t="shared" si="1"/>
-        <v>37976.846267084722</v>
-      </c>
-      <c r="U4" s="49">
-        <f t="shared" ref="U4:U8" si="9">_xlfn.FLOOR.MATH(C4^0.9*D4^1.51+IF(D4&gt;16,C4^0.9*(D4-11)^1.51,0))*1000</f>
-        <v>951000</v>
-      </c>
-      <c r="V4" s="49">
-        <f t="shared" si="2"/>
-        <v>38040</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C5" s="34">
-        <v>10</v>
-      </c>
-      <c r="D5" s="27">
-        <v>20</v>
-      </c>
-      <c r="E5" s="27">
-        <v>1</v>
-      </c>
-      <c r="F5" s="27">
-        <v>3</v>
-      </c>
-      <c r="G5" s="27">
-        <v>1</v>
-      </c>
-      <c r="H5" s="27">
-        <v>1</v>
-      </c>
-      <c r="I5" s="27">
-        <v>1</v>
-      </c>
-      <c r="J5" s="27">
-        <v>1</v>
-      </c>
-      <c r="K5" s="27">
-        <v>1</v>
-      </c>
-      <c r="M5" s="49">
+        <v>8265.1115410970779</v>
+      </c>
+      <c r="P5" s="49">
         <f t="shared" si="3"/>
-        <v>1985</v>
-      </c>
-      <c r="N5" s="49">
+        <v>26199.046085609491</v>
+      </c>
+      <c r="Q5" s="49">
         <f t="shared" si="4"/>
-        <v>5155</v>
-      </c>
-      <c r="O5" s="49">
+        <v>229.77432661993439</v>
+      </c>
+      <c r="R5" s="49">
         <f t="shared" si="5"/>
-        <v>93282</v>
-      </c>
-      <c r="P5" s="49">
+        <v>737.47509565192433</v>
+      </c>
+      <c r="S5" s="49">
         <f t="shared" si="6"/>
-        <v>227760</v>
-      </c>
-      <c r="Q5" s="49">
+        <v>756.06308092998961</v>
+      </c>
+      <c r="T5" s="49">
         <f t="shared" si="7"/>
-        <v>280</v>
-      </c>
-      <c r="R5" s="49">
+        <v>6170.2529291090304</v>
+      </c>
+      <c r="U5" s="49">
         <f t="shared" si="8"/>
-        <v>639</v>
-      </c>
-      <c r="S5" s="49">
-        <f t="shared" si="0"/>
-        <v>17972.257817993417</v>
-      </c>
-      <c r="T5" s="49">
-        <f t="shared" si="1"/>
-        <v>48014.020847982443</v>
-      </c>
-      <c r="U5" s="49">
+        <v>187000</v>
+      </c>
+      <c r="V5" s="49">
         <f t="shared" si="9"/>
-        <v>951000</v>
-      </c>
-      <c r="V5" s="49">
-        <f t="shared" si="2"/>
-        <v>38040</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.3">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C6" s="34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D6" s="27">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E6" s="27">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="F6" s="27">
         <v>3</v>
@@ -22107,244 +21080,255 @@
         <v>1</v>
       </c>
       <c r="H6" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="27">
-        <v>1</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K6" s="27">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M6" s="49">
+        <f t="shared" si="1"/>
+        <v>171.9387184223385</v>
+      </c>
+      <c r="N6" s="49">
+        <f t="shared" si="2"/>
+        <v>621.50320250447896</v>
+      </c>
+      <c r="O6" s="49">
+        <f t="shared" si="0"/>
+        <v>1715.9646431015246</v>
+      </c>
+      <c r="P6" s="49">
         <f t="shared" si="3"/>
-        <v>1450.9875518136387</v>
-      </c>
-      <c r="N6" s="49">
+        <v>5210.6546571660292</v>
+      </c>
+      <c r="Q6" s="49">
         <f t="shared" si="4"/>
-        <v>5643.2017632778488</v>
-      </c>
-      <c r="O6" s="49">
+        <v>98.537895869181312</v>
+      </c>
+      <c r="R6" s="49">
         <f t="shared" si="5"/>
-        <v>66710.352210090903</v>
-      </c>
-      <c r="P6" s="49">
+        <v>386.60480375905706</v>
+      </c>
+      <c r="S6" s="49">
         <f t="shared" si="6"/>
-        <v>244671.286921486</v>
-      </c>
-      <c r="Q6" s="49">
+        <v>272.30122809761059</v>
+      </c>
+      <c r="T6" s="49">
         <f t="shared" si="7"/>
-        <v>228.61904265976329</v>
-      </c>
-      <c r="R6" s="49">
+        <v>1331.0536970509388</v>
+      </c>
+      <c r="U6" s="49">
         <f t="shared" si="8"/>
-        <v>735.41554982699165</v>
-      </c>
-      <c r="S6" s="49">
-        <f t="shared" si="0"/>
-        <v>13125.08135495143</v>
-      </c>
-      <c r="T6" s="49">
-        <f t="shared" si="1"/>
-        <v>52588.325419805697</v>
-      </c>
-      <c r="U6" s="49">
+        <v>56500</v>
+      </c>
+      <c r="V6" s="49">
         <f t="shared" si="9"/>
-        <v>951000</v>
-      </c>
-      <c r="V6" s="49">
-        <f t="shared" si="2"/>
-        <v>38040</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
       </c>
       <c r="D7" s="27">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E7" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="27">
+        <v>4</v>
+      </c>
+      <c r="G7" s="27">
+        <v>1.2</v>
+      </c>
+      <c r="H7" s="27">
+        <v>10</v>
+      </c>
+      <c r="I7" s="27">
+        <v>3</v>
+      </c>
+      <c r="J7" s="27">
+        <v>1</v>
+      </c>
+      <c r="K7" s="27">
         <v>2</v>
       </c>
-      <c r="F7" s="27">
+      <c r="M7" s="49">
+        <f t="shared" si="1"/>
+        <v>136.21597027036952</v>
+      </c>
+      <c r="N7" s="49">
+        <f t="shared" si="2"/>
+        <v>553.92921689228058</v>
+      </c>
+      <c r="O7" s="49">
+        <f>MAX(200*(D7-2)+C7*D7*293*1.3^(1-E7)/(1.2^(I7-2)*SQRT(E7)*J7*SQRT(K7)),50)</f>
+        <v>15963.859773146431</v>
+      </c>
+      <c r="P7" s="49">
+        <f t="shared" si="3"/>
+        <v>60206.58939845625</v>
+      </c>
+      <c r="Q7" s="49">
+        <f t="shared" si="4"/>
+        <v>299.44387170614959</v>
+      </c>
+      <c r="R7" s="49">
+        <f t="shared" si="5"/>
+        <v>855.77456855192861</v>
+      </c>
+      <c r="S7" s="49">
+        <f t="shared" si="6"/>
+        <v>5054.0361041989854</v>
+      </c>
+      <c r="T7" s="49">
+        <f t="shared" si="7"/>
+        <v>20639.802012802509</v>
+      </c>
+      <c r="U7" s="49">
+        <f t="shared" si="8"/>
+        <v>700000</v>
+      </c>
+      <c r="V7" s="49">
+        <f t="shared" si="9"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C8" s="36">
+        <v>1</v>
+      </c>
+      <c r="D8" s="37">
+        <v>1</v>
+      </c>
+      <c r="E8" s="37">
+        <v>1</v>
+      </c>
+      <c r="F8" s="37">
         <v>3</v>
       </c>
-      <c r="G7" s="27">
-        <v>1</v>
-      </c>
-      <c r="H7" s="27">
-        <v>1</v>
-      </c>
-      <c r="I7" s="27">
-        <v>1</v>
-      </c>
-      <c r="J7" s="27">
-        <v>1</v>
-      </c>
-      <c r="K7" s="27">
-        <v>1</v>
-      </c>
-      <c r="M7" s="49">
-        <f t="shared" si="3"/>
-        <v>201.00999974491097</v>
-      </c>
-      <c r="N7" s="49">
-        <f t="shared" si="4"/>
-        <v>1104.0542843295168</v>
-      </c>
-      <c r="O7" s="49">
-        <f t="shared" si="5"/>
-        <v>8591.5454429504971</v>
-      </c>
-      <c r="P7" s="49">
-        <f t="shared" si="6"/>
-        <v>43165.477798989603</v>
-      </c>
-      <c r="Q7" s="49">
-        <f t="shared" si="7"/>
-        <v>81.317279836452954</v>
-      </c>
-      <c r="R7" s="49">
-        <f t="shared" si="8"/>
-        <v>560.01785668734101</v>
-      </c>
-      <c r="S7" s="49">
-        <f t="shared" si="0"/>
-        <v>917.42408287903868</v>
-      </c>
-      <c r="T7" s="49">
+      <c r="G8" s="37">
+        <v>2</v>
+      </c>
+      <c r="H8" s="37">
+        <v>3</v>
+      </c>
+      <c r="I8" s="37">
+        <v>2</v>
+      </c>
+      <c r="J8" s="37">
+        <v>1</v>
+      </c>
+      <c r="K8" s="37">
+        <v>1</v>
+      </c>
+      <c r="M8" s="48">
         <f t="shared" si="1"/>
-        <v>4980.9284420215408</v>
-      </c>
-      <c r="U7" s="49">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="V7" s="49">
-        <f t="shared" si="2"/>
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C8" s="36">
-        <v>5</v>
-      </c>
-      <c r="D8" s="37">
-        <v>20</v>
-      </c>
-      <c r="E8" s="37">
-        <v>1.5</v>
-      </c>
-      <c r="F8" s="37">
-        <v>4</v>
-      </c>
-      <c r="G8" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="H8" s="37">
-        <v>10</v>
-      </c>
-      <c r="I8" s="37">
-        <v>3</v>
-      </c>
-      <c r="J8" s="37">
-        <v>1</v>
-      </c>
-      <c r="K8" s="37">
-        <v>2</v>
-      </c>
-      <c r="M8" s="48">
-        <f t="shared" si="3"/>
-        <v>136.21597027036952</v>
+        <v>7.598076211353316</v>
       </c>
       <c r="N8" s="48">
         <f>40+(50+C8*D8*23)*SQRT(E8)*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2))</f>
-        <v>553.92921689228058</v>
+        <v>61.073284825421339</v>
       </c>
       <c r="O8" s="48">
-        <f t="shared" si="5"/>
-        <v>16139.014715109584</v>
+        <f>MAX(200*(D8-2)+C8*D8*293*1.3^(1-E8)/(1.2^(I8-2)*SQRT(E8)*J8*SQRT(K8)),50)</f>
+        <v>93</v>
       </c>
       <c r="P8" s="48">
-        <f t="shared" si="6"/>
-        <v>59891.399920592696</v>
+        <f>MAX(180*(D8-2)+C8*D8*900*SQRT(E8)*1.3^(1-E8)/(1.2^(I8-2)*J8*SQRT(K8)),100)</f>
+        <v>720</v>
       </c>
       <c r="Q8" s="48">
         <f>30/SQRT(E8)+(50+C8*D8)*K8/(J8*SQRT(E8))+30*(K8-1)</f>
-        <v>299.44387170614959</v>
+        <v>81</v>
       </c>
       <c r="R8" s="48">
+        <f t="shared" si="5"/>
+        <v>401</v>
+      </c>
+      <c r="S8" s="48">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="T8" s="48">
+        <f t="shared" si="7"/>
+        <v>128</v>
+      </c>
+      <c r="U8" s="48">
         <f t="shared" si="8"/>
-        <v>855.77456855192861</v>
-      </c>
-      <c r="S8" s="48">
-        <f>C8^1.38*D8^1.38*12*1.25^(1-E8)*J8/(SQRT(E8))</f>
-        <v>5042.9029467027194</v>
-      </c>
-      <c r="T8" s="48">
-        <f>88+C8^1.38*D8^1.38*32*1.25^(1-E8)*J8*SQRT(E8)/1</f>
-        <v>20259.611786810874</v>
-      </c>
-      <c r="U8" s="48">
+        <v>1000</v>
+      </c>
+      <c r="V8" s="48">
         <f t="shared" si="9"/>
-        <v>509000</v>
-      </c>
-      <c r="V8" s="48">
-        <f t="shared" si="2"/>
-        <v>20360</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>488</v>
+      </c>
       <c r="C10" s="24" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -22406,10 +21390,10 @@
         <v>438</v>
       </c>
       <c r="I22" s="40">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -22423,7 +21407,7 @@
         <v>439</v>
       </c>
       <c r="I23" s="40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="s">
         <v>450</v>
@@ -22442,11 +21426,11 @@
       <c r="H24" t="s">
         <v>440</v>
       </c>
-      <c r="I24" s="40">
-        <v>5</v>
+      <c r="I24" s="44" t="s">
+        <v>491</v>
       </c>
       <c r="J24" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
@@ -22462,11 +21446,11 @@
       <c r="H25" t="s">
         <v>441</v>
       </c>
-      <c r="I25" s="40">
-        <v>7</v>
+      <c r="I25" s="44" t="s">
+        <v>492</v>
       </c>
       <c r="J25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -22482,11 +21466,11 @@
       <c r="H26" t="s">
         <v>442</v>
       </c>
-      <c r="I26" s="40">
-        <v>9</v>
+      <c r="I26" s="44" t="s">
+        <v>493</v>
       </c>
       <c r="J26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -22503,10 +21487,10 @@
         <v>443</v>
       </c>
       <c r="I27" s="40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -22523,7 +21507,7 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -22540,7 +21524,7 @@
         <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -22557,27 +21541,1075 @@
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D32" s="44"/>
       <c r="H32" s="24" t="s">
         <v>236</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="2" t="s">
         <v>448</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D62D51-4A85-49A4-AACE-F79C8F6223AF}">
+  <dimension ref="A2:R68"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.9140625" customWidth="1"/>
+    <col min="11" max="11" width="4.9140625" customWidth="1"/>
+    <col min="12" max="12" width="9.4140625" customWidth="1"/>
+    <col min="13" max="13" width="9.58203125" customWidth="1"/>
+    <col min="14" max="14" width="11.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+      <c r="D8">
+        <v>55000</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <f>(C8+(D8-C8)/(E8-1)*B8)</f>
+        <v>10762.71186440678</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>10000</v>
+      </c>
+      <c r="M8">
+        <v>55000</v>
+      </c>
+      <c r="N8">
+        <v>60</v>
+      </c>
+      <c r="O8">
+        <f>(L8+(M8-L8)/(N8-1)*K8)</f>
+        <v>10762.71186440678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>55000</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <f>(C9+(D9-C9)/(E9-1)*B9)</f>
+        <v>11525.423728813559</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>10000</v>
+      </c>
+      <c r="M9">
+        <v>55000</v>
+      </c>
+      <c r="N9">
+        <v>60</v>
+      </c>
+      <c r="O9">
+        <f>(L9+(M9-L9)/(N9-1)*K9)</f>
+        <v>11525.423728813559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+      <c r="D10">
+        <v>55000</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ref="F10:F17" si="0">(C10+(D10-C10)/(E10-1)*B10)</f>
+        <v>12288.135593220339</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>10000</v>
+      </c>
+      <c r="M10">
+        <v>55000</v>
+      </c>
+      <c r="N10">
+        <v>60</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ref="O10" si="1">(L10+(M10-L10)/(N10-1)*K10)</f>
+        <v>12288.135593220339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+      <c r="D11">
+        <v>55000</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>13050.847457627118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
+      </c>
+      <c r="D12">
+        <v>55000</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>13813.559322033898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>10000</v>
+      </c>
+      <c r="D13">
+        <v>55000</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>14576.271186440677</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>10000</v>
+      </c>
+      <c r="D14">
+        <v>55000</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>15338.983050847459</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>10000</v>
+      </c>
+      <c r="D15">
+        <v>55000</v>
+      </c>
+      <c r="E15">
+        <v>60</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>16101.694915254237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>10000</v>
+      </c>
+      <c r="D16">
+        <v>55000</v>
+      </c>
+      <c r="E16">
+        <v>60</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>16864.406779661018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>10000</v>
+      </c>
+      <c r="D17">
+        <v>55000</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>17627.118644067796</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>20000</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <f>(C20+(D20-C20)/(E20-1)*B20)</f>
+        <v>348.81355932203388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>20000</v>
+      </c>
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <f>(C21+(D21-C21)/(E21-1)*B21)</f>
+        <v>687.62711864406776</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>20000</v>
+      </c>
+      <c r="E22">
+        <v>60</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:F29" si="2">(C22+(D22-C22)/(E22-1)*B22)</f>
+        <v>1026.4406779661017</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>20000</v>
+      </c>
+      <c r="E23">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>1365.2542372881355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>20000</v>
+      </c>
+      <c r="E24">
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>1704.0677966101694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>20000</v>
+      </c>
+      <c r="E25">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>2042.8813559322034</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>20000</v>
+      </c>
+      <c r="E26">
+        <v>60</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>2381.694915254237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>20000</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>2720.5084745762711</v>
+      </c>
+      <c r="Q27">
+        <f>SUM(O8:O119)</f>
+        <v>34576.271186440674</v>
+      </c>
+      <c r="R27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>20000</v>
+      </c>
+      <c r="E28">
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>3059.3220338983051</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>20000</v>
+      </c>
+      <c r="E29">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="2"/>
+        <v>3398.1355932203387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>11</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>20000</v>
+      </c>
+      <c r="E30">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <f>(C30+(D30-C30)/(E30-1)*B30)</f>
+        <v>3736.9491525423728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>20000</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <f>(C31+(D31-C31)/(E31-1)*B31)</f>
+        <v>4075.7627118644068</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>20000</v>
+      </c>
+      <c r="E32">
+        <v>60</v>
+      </c>
+      <c r="F32">
+        <f t="shared" ref="F32:F38" si="3">(C32+(D32-C32)/(E32-1)*B32)</f>
+        <v>4414.5762711864409</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>20000</v>
+      </c>
+      <c r="E33">
+        <v>60</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>4753.389830508474</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>10</v>
+      </c>
+      <c r="D34">
+        <v>20000</v>
+      </c>
+      <c r="E34">
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>5092.2033898305081</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>16</v>
+      </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
+      <c r="D35">
+        <v>20000</v>
+      </c>
+      <c r="E35">
+        <v>60</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>5431.0169491525421</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <v>20000</v>
+      </c>
+      <c r="E36">
+        <v>60</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>5769.8305084745762</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>20000</v>
+      </c>
+      <c r="E37">
+        <v>60</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>6108.6440677966102</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>20000</v>
+      </c>
+      <c r="E38">
+        <v>60</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>6447.4576271186434</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>20000</v>
+      </c>
+      <c r="E39">
+        <v>60</v>
+      </c>
+      <c r="F39">
+        <f>(C39+(D39-C39)/(E39-1)*B39)</f>
+        <v>6786.2711864406774</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>21</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>20000</v>
+      </c>
+      <c r="E40">
+        <v>60</v>
+      </c>
+      <c r="F40">
+        <f>(C40+(D40-C40)/(E40-1)*B40)</f>
+        <v>7125.0847457627115</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>22</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41">
+        <v>20000</v>
+      </c>
+      <c r="E41">
+        <v>60</v>
+      </c>
+      <c r="F41">
+        <f t="shared" ref="F41:F48" si="4">(C41+(D41-C41)/(E41-1)*B41)</f>
+        <v>7463.8983050847455</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>20000</v>
+      </c>
+      <c r="E42">
+        <v>60</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="4"/>
+        <v>7802.7118644067796</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>24</v>
+      </c>
+      <c r="C43">
+        <v>10</v>
+      </c>
+      <c r="D43">
+        <v>20000</v>
+      </c>
+      <c r="E43">
+        <v>60</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="4"/>
+        <v>8141.5254237288136</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>25</v>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>20000</v>
+      </c>
+      <c r="E44">
+        <v>60</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="4"/>
+        <v>8480.3389830508477</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>26</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>20000</v>
+      </c>
+      <c r="E45">
+        <v>60</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="4"/>
+        <v>8819.1525423728817</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>27</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46">
+        <v>20000</v>
+      </c>
+      <c r="E46">
+        <v>60</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="4"/>
+        <v>9157.966101694914</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>28</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>20000</v>
+      </c>
+      <c r="E47">
+        <v>60</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="4"/>
+        <v>9496.779661016948</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>29</v>
+      </c>
+      <c r="C48">
+        <v>10</v>
+      </c>
+      <c r="D48">
+        <v>20000</v>
+      </c>
+      <c r="E48">
+        <v>60</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="4"/>
+        <v>9835.5932203389821</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49">
+        <v>20000</v>
+      </c>
+      <c r="E49">
+        <v>60</v>
+      </c>
+      <c r="F49">
+        <f>(C49+(D49-C49)/(E49-1)*B49)</f>
+        <v>10174.406779661016</v>
+      </c>
+      <c r="H49">
+        <f>SUM(F20:F49)</f>
+        <v>157848.30508474578</v>
+      </c>
+      <c r="I49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>31</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>20000</v>
+      </c>
+      <c r="E50">
+        <v>60</v>
+      </c>
+      <c r="F50">
+        <f t="shared" ref="F50:F59" si="5">(C50+(D50-C50)/(E50-1)*B50)</f>
+        <v>10513.22033898305</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51">
+        <v>20000</v>
+      </c>
+      <c r="E51">
+        <v>60</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="5"/>
+        <v>10852.033898305084</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>33</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>20000</v>
+      </c>
+      <c r="E52">
+        <v>60</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="5"/>
+        <v>11190.847457627118</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>34</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>20000</v>
+      </c>
+      <c r="E53">
+        <v>60</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="5"/>
+        <v>11529.661016949152</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>35</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>20000</v>
+      </c>
+      <c r="E54">
+        <v>60</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="5"/>
+        <v>11868.474576271186</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>36</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55">
+        <v>20000</v>
+      </c>
+      <c r="E55">
+        <v>60</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="5"/>
+        <v>12207.28813559322</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>37</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+      <c r="D56">
+        <v>20000</v>
+      </c>
+      <c r="E56">
+        <v>60</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="5"/>
+        <v>12546.101694915254</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>38</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <v>20000</v>
+      </c>
+      <c r="E57">
+        <v>60</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="5"/>
+        <v>12884.915254237287</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>20000</v>
+      </c>
+      <c r="E58">
+        <v>60</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="5"/>
+        <v>13223.728813559321</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>40</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59">
+        <v>20000</v>
+      </c>
+      <c r="E59">
+        <v>60</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="5"/>
+        <v>13562.542372881355</v>
+      </c>
+      <c r="H59">
+        <f>SUM(F20:F59)</f>
+        <v>278227.11864406784</v>
+      </c>
+      <c r="I59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <f>SUM(F20:F128)</f>
+        <v>278227.11864406784</v>
+      </c>
+      <c r="I68" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7DA384-14F4-41A0-9A84-BC6B1B60950B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4FA141-5B37-4729-9580-C94818E953A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -1555,10 +1555,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>机枪的弹容量种族优势可额外换1-2层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>强化收益</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1985,6 +1981,10 @@
   </si>
   <si>
     <t>攻速系数只看单次攻击动作的总时长和前后摇的长度，实际代表攻击节奏快慢，默认为3，范围为1~5，代表极慢、慢、中等、快、极快。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机枪的弹容量种族优势可额外换2-4层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>387</v>
+        <v>496</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -15123,7 +15123,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -15137,43 +15137,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K3" t="s">
         <v>389</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>390</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>394</v>
+      </c>
+      <c r="N3" t="s">
+        <v>395</v>
+      </c>
+      <c r="O3" t="s">
+        <v>393</v>
+      </c>
+      <c r="P3" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q3" t="s">
         <v>391</v>
       </c>
-      <c r="M3" t="s">
-        <v>395</v>
-      </c>
-      <c r="N3" t="s">
-        <v>396</v>
-      </c>
-      <c r="O3" t="s">
-        <v>394</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
+        <v>399</v>
+      </c>
+      <c r="S3" t="s">
+        <v>400</v>
+      </c>
+      <c r="T3" t="s">
+        <v>392</v>
+      </c>
+      <c r="U3" t="s">
         <v>397</v>
       </c>
-      <c r="Q3" t="s">
-        <v>392</v>
-      </c>
-      <c r="R3" t="s">
-        <v>400</v>
-      </c>
-      <c r="S3" t="s">
-        <v>401</v>
-      </c>
-      <c r="T3" t="s">
-        <v>393</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>398</v>
-      </c>
-      <c r="V3" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -17758,7 +17758,7 @@
         <v>169</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>170</v>
@@ -17788,10 +17788,10 @@
         <v>154</v>
       </c>
       <c r="S2" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="T2" s="14" t="s">
         <v>403</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -18284,7 +18284,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18300,7 +18300,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18470,7 +18470,7 @@
         <v>236</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -18544,7 +18544,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
@@ -18840,7 +18840,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -18890,7 +18890,7 @@
         <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -20070,7 +20070,7 @@
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>239</v>
@@ -20253,7 +20253,7 @@
         <v>236</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
@@ -20290,7 +20290,7 @@
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
@@ -20315,13 +20315,13 @@
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
+        <v>412</v>
+      </c>
+      <c r="E14" s="35" t="s">
         <v>413</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>414</v>
-      </c>
       <c r="F14" s="33" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>363</v>
@@ -20346,7 +20346,7 @@
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
@@ -20367,7 +20367,7 @@
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
@@ -20388,7 +20388,7 @@
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E17" s="40">
         <v>3</v>
@@ -20409,13 +20409,13 @@
     </row>
     <row r="18" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E18" s="40">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I18" s="46" t="s">
         <v>348</v>
@@ -20433,13 +20433,13 @@
     </row>
     <row r="19" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E19" s="40">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I19" s="46" t="s">
         <v>349</v>
@@ -20457,13 +20457,13 @@
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E20" s="40">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I20" s="46" t="s">
         <v>350</v>
@@ -20481,13 +20481,13 @@
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E21" s="40">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I21" s="46" t="s">
         <v>351</v>
@@ -20505,7 +20505,7 @@
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E22" s="40">
         <v>8</v>
@@ -20526,7 +20526,7 @@
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E23" s="40">
         <v>9</v>
@@ -20534,10 +20534,10 @@
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
+        <v>423</v>
+      </c>
+      <c r="E24" s="43" t="s">
         <v>424</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>425</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -20729,7 +20729,7 @@
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I32" s="46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J32" s="45">
         <v>0</v>
@@ -20782,7 +20782,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="M1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -20790,63 +20790,63 @@
         <v>238</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="G2" s="33" t="s">
         <v>459</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="H2" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>460</v>
       </c>
-      <c r="H2" s="33" t="s">
-        <v>462</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>458</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>461</v>
-      </c>
       <c r="K2" s="33" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M2" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="O2" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="N2" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="R2" s="35" t="s">
         <v>468</v>
       </c>
-      <c r="P2" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q2" s="35" t="s">
+      <c r="S2" s="35" t="s">
         <v>470</v>
       </c>
-      <c r="R2" s="35" t="s">
-        <v>469</v>
-      </c>
-      <c r="S2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>471</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>472</v>
       </c>
       <c r="U2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
@@ -20918,7 +20918,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -20984,13 +20984,13 @@
         <v>96000</v>
       </c>
       <c r="V4" s="49">
-        <f t="shared" ref="V4:V9" si="9">_xlfn.FLOOR.MATH(U4/700)*20</f>
+        <f t="shared" ref="V4:V8" si="9">_xlfn.FLOOR.MATH(U4/700)*20</f>
         <v>2740</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21062,7 +21062,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21134,7 +21134,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
@@ -21206,7 +21206,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C8" s="36">
         <v>1</v>
@@ -21278,13 +21278,13 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -21294,7 +21294,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -21303,32 +21303,32 @@
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -21339,229 +21339,229 @@
         <v>238</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>413</v>
       </c>
-      <c r="C20" s="35" t="s">
-        <v>414</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I21" s="40">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I22" s="40">
         <v>1.5</v>
       </c>
       <c r="J22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I23" s="40">
         <v>2</v>
       </c>
       <c r="J23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C24" s="40">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H24" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C25" s="40">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C26" s="40">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C27" s="40">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I27" s="40">
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I28" s="40">
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
       <c r="H29" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I29" s="40">
         <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
+        <v>423</v>
+      </c>
+      <c r="C30" s="44" t="s">
         <v>424</v>
       </c>
-      <c r="C30" s="44" t="s">
-        <v>425</v>
-      </c>
       <c r="H30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I30" s="40">
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
+        <v>476</v>
+      </c>
+      <c r="C32" s="47" t="s">
         <v>477</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>478</v>
       </c>
       <c r="D32" s="44"/>
       <c r="H32" s="24" t="s">
         <v>236</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4FA141-5B37-4729-9580-C94818E953A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FC2725-28AC-4D1F-8FD2-A5E9E4F1A460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="498">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1627,14 +1627,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>套装特殊部件可根据特点或重量等适当浮动或者面板转移，但同一套装不同部件之间不要偏差过大，否则可能导致混装的强度较高。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御以外的单项属性占比过高时会占用更多数值模型，通常不要超过总分的一半。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>由于项链通常限制等级填写不规范，可以获取时对应的玩家等级作为参考。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1985,6 +1977,18 @@
   </si>
   <si>
     <t>机枪的弹容量种族优势可额外换2-4层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击类手套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御以外的单项属性占比过高时会占用更多数值模型，通常不要超过总分的一半。攻击类手套则是例外，对于空手加成相当于刀位，其他流派的手套的伤害加成也可以相对更高，参考下方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一套装不同部件之间不要偏差过大，否则可能导致混装的强度较高。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2157,7 +2161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2245,6 +2249,7 @@
     <xf numFmtId="176" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2612,7 +2617,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C986475-2ED4-459B-8875-CFCE36210C4F}" name="表2_2" displayName="表2_2" ref="B2:T19" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C986475-2ED4-459B-8875-CFCE36210C4F}" name="表2_2" displayName="表2_2" ref="B2:T21" totalsRowShown="0" headerRowDxfId="8">
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{2647E847-1A87-468E-AC67-15776089B268}" name="类型" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{8C4F1BC9-0719-4D06-910D-C32A022B3F84}" name="具体装备"/>
@@ -4974,7 +4979,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -17684,11 +17689,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09871776-299B-496E-8462-E6326FE1AD56}">
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.08203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="7.9140625" customWidth="1"/>
@@ -17970,7 +17975,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -18284,7 +18289,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>406</v>
+        <v>496</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18300,7 +18305,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>405</v>
+        <v>497</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18311,18 +18316,11 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="S13" t="e">
-        <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T13" t="e">
-        <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
-        <v>#VALUE!</v>
-      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="2"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -18332,223 +18330,302 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
+      <c r="S14" s="51">
+        <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>10</v>
+      </c>
+      <c r="T14" s="51">
+        <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="12">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12">
+        <v>5</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
+        <v>50</v>
+      </c>
+      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <v>0</v>
+      </c>
+      <c r="O15" s="16">
+        <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.7,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.7))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.3,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.3),0)+表2_2[[#This Row],[空手加成]]*4+表2_2[[#This Row],[法抗]]</f>
+        <v>210</v>
+      </c>
+      <c r="P15">
+        <f>表2_2[[#This Row],[限制等级]]*20+表2_2[[#This Row],[重量]]*10</f>
+        <v>210</v>
+      </c>
+      <c r="Q15" s="16">
+        <f>P15*1.25^M15</f>
+        <v>210</v>
+      </c>
+      <c r="S15">
+        <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>12</v>
+      </c>
+      <c r="T15">
+        <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C17" t="s">
         <v>195</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <v>20</v>
       </c>
-      <c r="E15">
+      <c r="E17">
         <v>90</v>
       </c>
-      <c r="F15">
+      <c r="F17">
         <v>120</v>
       </c>
-      <c r="G15">
+      <c r="G17">
         <v>80</v>
       </c>
-      <c r="H15">
+      <c r="H17">
         <v>35</v>
       </c>
-      <c r="I15">
+      <c r="I17">
         <v>0</v>
       </c>
-      <c r="J15">
+      <c r="J17">
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="K17">
         <v>0</v>
       </c>
-      <c r="L15">
+      <c r="L17">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="O15">
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="O17">
         <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>485</v>
       </c>
-      <c r="P15">
+      <c r="P17">
         <f>表2_2[[#This Row],[限制等级]]*20</f>
         <v>400</v>
       </c>
-      <c r="Q15">
-        <f t="shared" ref="Q15:Q16" si="1">P15*1.25^M15</f>
+      <c r="Q17">
+        <f t="shared" ref="Q17:Q18" si="1">P17*1.25^M17</f>
         <v>500</v>
       </c>
-      <c r="S15">
+      <c r="S17">
         <v>0</v>
       </c>
-      <c r="T15">
+      <c r="T17">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
-      <c r="C16" s="1" t="s">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="C18" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D18" s="12">
         <v>35</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E18" s="12">
         <v>100</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F18" s="12">
         <v>250</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G18" s="12">
         <v>250</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H18" s="12">
         <v>0</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I18" s="12">
         <v>0</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J18" s="12">
         <v>0</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K18" s="12">
         <v>0</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L18" s="12">
         <v>0</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M18" s="12">
         <v>0</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O18" s="16">
         <f>表2_2[[#This Row],[防御]]*2+IF(表2_2[[#This Row],[HP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[HP]],表2_2[[#This Row],[HP]]+2*(表2_2[[#This Row],[HP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[MP]]&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[MP]],表2_2[[#This Row],[MP]]+2*(表2_2[[#This Row],[MP]]-表2_2[[#This Row],[加权总分]]*0.5))+IF((表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3)&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3,表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3+2*(表2_2[[#This Row],[伤害加成]]*3+表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.5))+IF(表2_2[[#This Row],[刀/枪总加成]]*3&gt;表2_2[[#This Row],[加权总分]]*0.25,2*(表2_2[[#This Row],[刀/枪总加成]]*3-表2_2[[#This Row],[加权总分]]*0.25),0)+IF(表2_2[[#This Row],[空手加成]]*4&lt;表2_2[[#This Row],[加权总分]]*0.5,表2_2[[#This Row],[空手加成]]*4,表2_2[[#This Row],[空手加成]]*4+2*(表2_2[[#This Row],[空手加成]]*4-表2_2[[#This Row],[加权总分]]*0.5))+表2_2[[#This Row],[法抗]]</f>
         <v>700</v>
       </c>
-      <c r="P16">
+      <c r="P18">
         <f>表2_2[[#This Row],[限制等级]]*20</f>
         <v>700</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q18" s="16">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="S16">
+      <c r="S18">
         <v>0</v>
       </c>
-      <c r="T16">
+      <c r="T18">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B23" s="3"/>
+      <c r="C23" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C25" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>323</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>404</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>325</v>
       </c>
     </row>
@@ -18557,7 +18634,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="S15:T15 S16:T16" calculatedColumn="1"/>
+    <ignoredError sqref="S17:T17 S18:T18" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
@@ -18840,7 +18917,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -18890,7 +18967,7 @@
         <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -20070,7 +20147,7 @@
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>239</v>
@@ -20253,7 +20330,7 @@
         <v>236</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
@@ -20290,7 +20367,7 @@
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
@@ -20315,13 +20392,13 @@
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>363</v>
@@ -20346,7 +20423,7 @@
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
@@ -20367,7 +20444,7 @@
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
@@ -20388,7 +20465,7 @@
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E17" s="40">
         <v>3</v>
@@ -20409,13 +20486,13 @@
     </row>
     <row r="18" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E18" s="40">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I18" s="46" t="s">
         <v>348</v>
@@ -20433,13 +20510,13 @@
     </row>
     <row r="19" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E19" s="40">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I19" s="46" t="s">
         <v>349</v>
@@ -20457,13 +20534,13 @@
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E20" s="40">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I20" s="46" t="s">
         <v>350</v>
@@ -20481,13 +20558,13 @@
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E21" s="40">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I21" s="46" t="s">
         <v>351</v>
@@ -20505,7 +20582,7 @@
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E22" s="40">
         <v>8</v>
@@ -20526,7 +20603,7 @@
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E23" s="40">
         <v>9</v>
@@ -20534,10 +20611,10 @@
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>370</v>
@@ -20729,7 +20806,7 @@
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I32" s="46" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J32" s="45">
         <v>0</v>
@@ -20782,7 +20859,7 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="M1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -20790,63 +20867,63 @@
         <v>238</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>456</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>461</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>460</v>
-      </c>
       <c r="K2" s="33" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M2" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="R2" s="35" t="s">
         <v>466</v>
       </c>
-      <c r="N2" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="O2" s="35" t="s">
-        <v>467</v>
-      </c>
-      <c r="P2" s="35" t="s">
-        <v>464</v>
-      </c>
-      <c r="Q2" s="35" t="s">
+      <c r="S2" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="T2" s="35" t="s">
         <v>469</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>468</v>
-      </c>
-      <c r="S2" s="35" t="s">
-        <v>470</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>471</v>
       </c>
       <c r="U2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
@@ -20918,7 +20995,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -20990,7 +21067,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21062,7 +21139,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21134,7 +21211,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
@@ -21206,7 +21283,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C8" s="36">
         <v>1</v>
@@ -21278,13 +21355,13 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -21294,7 +21371,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -21303,32 +21380,32 @@
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -21339,229 +21416,229 @@
         <v>238</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I21" s="40">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I22" s="40">
         <v>1.5</v>
       </c>
       <c r="J22" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I23" s="40">
         <v>2</v>
       </c>
       <c r="J23" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C24" s="40">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J24" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C25" s="40">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C26" s="40">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H26" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J26" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C27" s="40">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H27" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I27" s="40">
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
       <c r="H28" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I28" s="40">
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
       <c r="H29" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I29" s="40">
         <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H30" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I30" s="40">
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D32" s="44"/>
       <c r="H32" s="24" t="s">
         <v>236</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FC2725-28AC-4D1F-8FD2-A5E9E4F1A460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A18FEF5-5255-461D-BF4D-DAB3B7B36BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="505">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1929,18 +1929,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>boss大僵尸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方舟武士</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对应阶段和档次系数参考下方表格。这两项将决定整体数值大致水平。对于拥有暖机、强力buff、多阶段等显著影响面板的特殊机制单位可能不适用。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>颜色标注：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1989,6 +1981,42 @@
   </si>
   <si>
     <t>同一套装不同部件之间不要偏差过大，否则可能导致混装的强度较高。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大僵尸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段、档次系数、韧性系数参考下方表格。阶段和档次系数将决定整体数值大致水平。对于拥有暖机、强力buff、多阶段等显著影响面板的特殊机制单位可能不适用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短击退可击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长击退可击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长击退不可击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短击退不可击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可击退不可击飞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2161,7 +2189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2249,7 +2277,6 @@
     <xf numFmtId="176" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4979,7 +5006,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -18289,7 +18316,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18305,7 +18332,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18330,18 +18357,18 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="S14" s="51">
+      <c r="S14">
         <f>10+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>10</v>
       </c>
-      <c r="T14" s="51">
+      <c r="T14">
         <f>25+表2_2[[#This Row],[限制等级]]*0.2</f>
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>177</v>
@@ -20836,35 +20863,37 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D334537-191E-473E-8F5E-E80A13E62C45}">
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="4.4140625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="5.9140625" customWidth="1"/>
+    <col min="4" max="4" width="8.25" customWidth="1"/>
     <col min="5" max="5" width="7.9140625" customWidth="1"/>
     <col min="6" max="6" width="8.25" customWidth="1"/>
     <col min="7" max="7" width="8.08203125" customWidth="1"/>
     <col min="8" max="8" width="8.58203125" customWidth="1"/>
     <col min="9" max="9" width="8.5" customWidth="1"/>
     <col min="10" max="10" width="13.08203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" customWidth="1"/>
-    <col min="12" max="12" width="6.58203125" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" customWidth="1"/>
-    <col min="18" max="18" width="9.9140625" customWidth="1"/>
-    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="11" max="11" width="7.9140625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="6.58203125" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
+    <col min="19" max="19" width="9.9140625" customWidth="1"/>
+    <col min="22" max="22" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="M1" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="N1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C2" s="33" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>432</v>
@@ -20888,40 +20917,43 @@
         <v>458</v>
       </c>
       <c r="K2" s="33" t="s">
+        <v>497</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>454</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="N2" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="O2" s="35" t="s">
         <v>463</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="35" t="s">
         <v>465</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="Q2" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="R2" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="S2" s="35" t="s">
         <v>466</v>
       </c>
-      <c r="S2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>468</v>
       </c>
-      <c r="T2" s="35" t="s">
+      <c r="U2" s="35" t="s">
         <v>469</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="V2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="35" t="s">
+      <c r="W2" s="35" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>480</v>
       </c>
@@ -20950,52 +20982,55 @@
         <v>0.8</v>
       </c>
       <c r="K3" s="27">
+        <v>1</v>
+      </c>
+      <c r="L3" s="27">
         <v>1.3</v>
       </c>
-      <c r="M3" s="49">
+      <c r="N3" s="49">
         <f>5+C3*D3*9*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2)*SQRT(E3))</f>
         <v>18.888439450165926</v>
       </c>
-      <c r="N3" s="49">
+      <c r="O3" s="49">
         <f>40+(50+C3*D3*23)*SQRT(E3)*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2))</f>
         <v>109.54507458009012</v>
       </c>
-      <c r="O3" s="49">
-        <f t="shared" ref="O3:O6" si="0">MAX(200*(D3-2)+C3*D3*293*1.3^(1-E3)/(1.2^(I3-2)*SQRT(E3)*J3*SQRT(K3)),50)</f>
+      <c r="P3" s="49">
+        <f>MAX(200*(D3-2)+C3*D3*293*1.3^(1-E3)/(1.2^(I3-2)*SQRT(E3)*J3*SQRT(L3)),50)*(IF(AND(K3&gt;3,D3&lt;9),1-K3/50,1))*(IF(AND(K3&lt;5,D3&gt;12),1+1/K3,1))</f>
         <v>581.27450879982621</v>
       </c>
-      <c r="P3" s="49">
-        <f>MAX(180*(D3-2)+C3*D3*900*SQRT(E3)*1.3^(1-E3)/(1.2^(I3-2)*J3*SQRT(K3)),100)</f>
+      <c r="Q3" s="49">
+        <f>MAX(180*(D3-2)+C3*D3*900*SQRT(E3)*1.3^(1-E3)/(1.2^(I3-2)*J3*SQRT(L3)),100)*(IF(AND(K3&gt;3,D3&lt;9),1-K3/50,1))*(IF(AND(K3&lt;5,D3&gt;12),1+1/K3,1))</f>
         <v>1584.1216598494022</v>
       </c>
-      <c r="Q3" s="49">
-        <f>30/SQRT(E3)+(50+C3*D3)*K3/(J3*SQRT(E3))+30*(K3-1)</f>
+      <c r="R3" s="49">
+        <f>30/SQRT(E3)+(50+C3*D3)*L3/(J3*SQRT(E3))+30*(L3-1)</f>
         <v>136.10648909600368</v>
       </c>
-      <c r="R3" s="49">
-        <f>210+(190+C3*D3)*K3*SQRT(E3)/(J3*1.1^(I3-2))</f>
+      <c r="S3" s="49">
+        <f>210+(190+C3*D3)*L3*SQRT(E3)/(J3*1.1^(I3-2))</f>
         <v>516.16801764921502</v>
       </c>
-      <c r="S3" s="49">
+      <c r="T3" s="49">
         <f>C3^1.15*D3^1.2*12*1.25^(1-E3)/(SQRT(E3))*IF(D3&gt;17,1.2^(D3-15),1)</f>
         <v>22.820637166202172</v>
       </c>
-      <c r="T3" s="49">
+      <c r="U3" s="49">
         <f>95+C3^1*D3^1.58*33*1.25^(1-E3)*SQRT(E3)/1+IF(C3&gt;=6,C3*200,0)</f>
         <v>153.56863807482276</v>
       </c>
-      <c r="U3" s="49">
+      <c r="V3" s="49">
         <f>_xlfn.FLOOR.MATH(2*C3^1.3*D3^1.3+IF(D3&gt;2,D3*10,0)+IF(D3&gt;8,C3^0.5*D3^0.7)+IF(D3&gt;16,C3^1.2*(D3-15)^2.5,0))*500</f>
         <v>1500</v>
       </c>
-      <c r="V3" s="49">
-        <f>_xlfn.FLOOR.MATH(U3/700)*20</f>
+      <c r="W3" s="49">
+        <f>_xlfn.FLOOR.MATH(V3/700)*20</f>
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -21004,7 +21039,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="27">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="27">
         <v>2</v>
@@ -21022,52 +21057,55 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="K4" s="27">
-        <v>2.9</v>
-      </c>
-      <c r="M4" s="49">
-        <f t="shared" ref="M4:M8" si="1">5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
-        <v>87.608658193499167</v>
+        <v>3</v>
+      </c>
+      <c r="L4" s="27">
+        <v>3</v>
       </c>
       <c r="N4" s="49">
-        <f t="shared" ref="N4:N7" si="2">40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
-        <v>237.13108861217921</v>
+        <f>5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
+        <v>81.165501413354804</v>
       </c>
       <c r="O4" s="49">
-        <f t="shared" si="0"/>
-        <v>5075.0421198956528</v>
+        <f>40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
+        <v>244.47507687123712</v>
       </c>
       <c r="P4" s="49">
-        <f t="shared" ref="P4:P7" si="3">MAX(180*(D4-2)+C4*D4*900*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(K4)),100)</f>
-        <v>9044.9499191975083</v>
+        <f t="shared" ref="P4:P8" si="0">MAX(200*(D4-2)+C4*D4*293*1.3^(1-E4)/(1.2^(I4-2)*SQRT(E4)*J4*SQRT(L4)),50)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
+        <v>6394.7248368899818</v>
       </c>
       <c r="Q4" s="49">
-        <f t="shared" ref="Q4:Q7" si="4">30/SQRT(E4)+(50+C4*D4)*K4/(J4*SQRT(E4))+30*(K4-1)</f>
-        <v>276.23630124850206</v>
+        <f t="shared" ref="Q4:Q7" si="1">MAX(180*(D4-2)+C4*D4*900*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(L4)),100)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
+        <v>12209.034532016676</v>
       </c>
       <c r="R4" s="49">
-        <f t="shared" ref="R4:R8" si="5">210+(190+C4*D4)*K4*SQRT(E4)/(J4*1.1^(I4-2))</f>
-        <v>736.54928734165037</v>
+        <f>30/SQRT(E4)+(50+C4*D4)*L4/(J4*SQRT(E4))+30*(L4-1)</f>
+        <v>272.73504259314552</v>
       </c>
       <c r="S4" s="49">
-        <f t="shared" ref="S4:S8" si="6">C4^1.15*D4^1.2*12*1.25^(1-E4)/(SQRT(E4))*IF(D4&gt;17,1.2^(D4-15),1)</f>
-        <v>304.61429344689395</v>
+        <f>210+(190+C4*D4)*L4*SQRT(E4)/(J4*1.1^(I4-2))</f>
+        <v>787.74812851276283</v>
       </c>
       <c r="T4" s="49">
-        <f t="shared" ref="T4:T8" si="7">95+C4^1*D4^1.58*33*1.25^(1-E4)*SQRT(E4)/1+IF(C4&gt;=6,C4*200,0)</f>
-        <v>1871.1164335978647</v>
+        <f>C4^1.15*D4^1.2*12*1.25^(1-E4)/(SQRT(E4))*IF(D4&gt;17,1.2^(D4-15),1)</f>
+        <v>280.8555532243625</v>
       </c>
       <c r="U4" s="49">
-        <f t="shared" ref="U4:U8" si="8">_xlfn.FLOOR.MATH(2*C4^1.3*D4^1.3+IF(D4&gt;2,D4*10,0)+IF(D4&gt;8,C4^0.5*D4^0.7)+IF(D4&gt;16,C4^1.2*(D4-15)^2.5,0))*500</f>
+        <f>95+C4^1*D4^1.58*33*1.25^(1-E4)*SQRT(E4)/1+IF(C4&gt;=6,C4*200,0)</f>
+        <v>1937.2844760253267</v>
+      </c>
+      <c r="V4" s="49">
+        <f>_xlfn.FLOOR.MATH(2*C4^1.3*D4^1.3+IF(D4&gt;2,D4*10,0)+IF(D4&gt;8,C4^0.5*D4^0.7)+IF(D4&gt;16,C4^1.2*(D4-15)^2.5,0))*500</f>
         <v>96000</v>
       </c>
-      <c r="V4" s="49">
-        <f t="shared" ref="V4:V8" si="9">_xlfn.FLOOR.MATH(U4/700)*20</f>
+      <c r="W4" s="49">
+        <f t="shared" ref="W4:W8" si="2">_xlfn.FLOOR.MATH(V4/700)*20</f>
         <v>2740</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21094,52 +21132,55 @@
         <v>0.9</v>
       </c>
       <c r="K5" s="27">
+        <v>4</v>
+      </c>
+      <c r="L5" s="27">
         <v>2</v>
       </c>
-      <c r="M5" s="49">
+      <c r="N5" s="49">
+        <f>5+C5*D5*9*1.25^(1-E5)*J5/(G5*SQRT(H5)*1.2^(F5-3)*1.1^(I5-2)*SQRT(E5))</f>
+        <v>80.557769388855888</v>
+      </c>
+      <c r="O5" s="49">
+        <f>40+(50+C5*D5*23)*SQRT(E5)*1.25^(1-E5)*J5/(G5*SQRT(H5)*1.2^(F5-3)*1.1^(I5-2))</f>
+        <v>305.01188004165385</v>
+      </c>
+      <c r="P5" s="49">
+        <f t="shared" si="0"/>
+        <v>10331.389426371348</v>
+      </c>
+      <c r="Q5" s="49">
         <f t="shared" si="1"/>
-        <v>80.557769388855888</v>
-      </c>
-      <c r="N5" s="49">
+        <v>32748.807607011862</v>
+      </c>
+      <c r="R5" s="49">
+        <f>30/SQRT(E5)+(50+C5*D5)*L5/(J5*SQRT(E5))+30*(L5-1)</f>
+        <v>229.77432661993439</v>
+      </c>
+      <c r="S5" s="49">
+        <f>210+(190+C5*D5)*L5*SQRT(E5)/(J5*1.1^(I5-2))</f>
+        <v>737.47509565192433</v>
+      </c>
+      <c r="T5" s="49">
+        <f>C5^1.15*D5^1.2*12*1.25^(1-E5)/(SQRT(E5))*IF(D5&gt;17,1.2^(D5-15),1)</f>
+        <v>756.06308092998961</v>
+      </c>
+      <c r="U5" s="49">
+        <f>95+C5^1*D5^1.58*33*1.25^(1-E5)*SQRT(E5)/1+IF(C5&gt;=6,C5*200,0)</f>
+        <v>6170.2529291090304</v>
+      </c>
+      <c r="V5" s="49">
+        <f>_xlfn.FLOOR.MATH(2*C5^1.3*D5^1.3+IF(D5&gt;2,D5*10,0)+IF(D5&gt;8,C5^0.5*D5^0.7)+IF(D5&gt;16,C5^1.2*(D5-15)^2.5,0))*500</f>
+        <v>187000</v>
+      </c>
+      <c r="W5" s="49">
         <f t="shared" si="2"/>
-        <v>305.01188004165385</v>
-      </c>
-      <c r="O5" s="49">
-        <f t="shared" si="0"/>
-        <v>8265.1115410970779</v>
-      </c>
-      <c r="P5" s="49">
-        <f t="shared" si="3"/>
-        <v>26199.046085609491</v>
-      </c>
-      <c r="Q5" s="49">
-        <f t="shared" si="4"/>
-        <v>229.77432661993439</v>
-      </c>
-      <c r="R5" s="49">
-        <f t="shared" si="5"/>
-        <v>737.47509565192433</v>
-      </c>
-      <c r="S5" s="49">
-        <f t="shared" si="6"/>
-        <v>756.06308092998961</v>
-      </c>
-      <c r="T5" s="49">
-        <f t="shared" si="7"/>
-        <v>6170.2529291090304</v>
-      </c>
-      <c r="U5" s="49">
-        <f t="shared" si="8"/>
-        <v>187000</v>
-      </c>
-      <c r="V5" s="49">
-        <f t="shared" si="9"/>
         <v>5340</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21166,50 +21207,53 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="K6" s="27">
+        <v>3</v>
+      </c>
+      <c r="L6" s="27">
         <v>1.8</v>
       </c>
-      <c r="M6" s="49">
-        <f t="shared" si="1"/>
+      <c r="N6" s="49">
+        <f>5+C6*D6*9*1.25^(1-E6)*J6/(G6*SQRT(H6)*1.2^(F6-3)*1.1^(I6-2)*SQRT(E6))</f>
         <v>171.9387184223385</v>
       </c>
-      <c r="N6" s="49">
-        <f t="shared" si="2"/>
+      <c r="O6" s="49">
+        <f>40+(50+C6*D6*23)*SQRT(E6)*1.25^(1-E6)*J6/(G6*SQRT(H6)*1.2^(F6-3)*1.1^(I6-2))</f>
         <v>621.50320250447896</v>
       </c>
-      <c r="O6" s="49">
+      <c r="P6" s="49">
         <f t="shared" si="0"/>
         <v>1715.9646431015246</v>
       </c>
-      <c r="P6" s="49">
-        <f t="shared" si="3"/>
+      <c r="Q6" s="49">
+        <f t="shared" si="1"/>
         <v>5210.6546571660292</v>
       </c>
-      <c r="Q6" s="49">
-        <f t="shared" si="4"/>
+      <c r="R6" s="49">
+        <f>30/SQRT(E6)+(50+C6*D6)*L6/(J6*SQRT(E6))+30*(L6-1)</f>
         <v>98.537895869181312</v>
       </c>
-      <c r="R6" s="49">
-        <f t="shared" si="5"/>
+      <c r="S6" s="49">
+        <f>210+(190+C6*D6)*L6*SQRT(E6)/(J6*1.1^(I6-2))</f>
         <v>386.60480375905706</v>
       </c>
-      <c r="S6" s="49">
-        <f t="shared" si="6"/>
+      <c r="T6" s="49">
+        <f>C6^1.15*D6^1.2*12*1.25^(1-E6)/(SQRT(E6))*IF(D6&gt;17,1.2^(D6-15),1)</f>
         <v>272.30122809761059</v>
       </c>
-      <c r="T6" s="49">
-        <f t="shared" si="7"/>
+      <c r="U6" s="49">
+        <f>95+C6^1*D6^1.58*33*1.25^(1-E6)*SQRT(E6)/1+IF(C6&gt;=6,C6*200,0)</f>
         <v>1331.0536970509388</v>
       </c>
-      <c r="U6" s="49">
-        <f t="shared" si="8"/>
+      <c r="V6" s="49">
+        <f>_xlfn.FLOOR.MATH(2*C6^1.3*D6^1.3+IF(D6&gt;2,D6*10,0)+IF(D6&gt;8,C6^0.5*D6^0.7)+IF(D6&gt;16,C6^1.2*(D6-15)^2.5,0))*500</f>
         <v>56500</v>
       </c>
-      <c r="V6" s="49">
-        <f t="shared" si="9"/>
+      <c r="W6" s="49">
+        <f t="shared" si="2"/>
         <v>1600</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>481</v>
       </c>
@@ -21238,50 +21282,53 @@
         <v>1</v>
       </c>
       <c r="K7" s="27">
+        <v>5</v>
+      </c>
+      <c r="L7" s="27">
         <v>2</v>
       </c>
-      <c r="M7" s="49">
+      <c r="N7" s="49">
+        <f>5+C7*D7*9*1.25^(1-E7)*J7/(G7*SQRT(H7)*1.2^(F7-3)*1.1^(I7-2)*SQRT(E7))</f>
+        <v>136.21597027036952</v>
+      </c>
+      <c r="O7" s="49">
+        <f>40+(50+C7*D7*23)*SQRT(E7)*1.25^(1-E7)*J7/(G7*SQRT(H7)*1.2^(F7-3)*1.1^(I7-2))</f>
+        <v>553.92921689228058</v>
+      </c>
+      <c r="P7" s="49">
+        <f t="shared" si="0"/>
+        <v>15963.859773146431</v>
+      </c>
+      <c r="Q7" s="49">
         <f t="shared" si="1"/>
-        <v>136.21597027036952</v>
-      </c>
-      <c r="N7" s="49">
+        <v>60206.58939845625</v>
+      </c>
+      <c r="R7" s="49">
+        <f>30/SQRT(E7)+(50+C7*D7)*L7/(J7*SQRT(E7))+30*(L7-1)</f>
+        <v>299.44387170614959</v>
+      </c>
+      <c r="S7" s="49">
+        <f>210+(190+C7*D7)*L7*SQRT(E7)/(J7*1.1^(I7-2))</f>
+        <v>855.77456855192861</v>
+      </c>
+      <c r="T7" s="49">
+        <f>C7^1.15*D7^1.2*12*1.25^(1-E7)/(SQRT(E7))*IF(D7&gt;17,1.2^(D7-15),1)</f>
+        <v>5054.0361041989854</v>
+      </c>
+      <c r="U7" s="49">
+        <f>95+C7^1*D7^1.58*33*1.25^(1-E7)*SQRT(E7)/1+IF(C7&gt;=6,C7*200,0)</f>
+        <v>20639.802012802509</v>
+      </c>
+      <c r="V7" s="49">
+        <f>_xlfn.FLOOR.MATH(2*C7^1.3*D7^1.3+IF(D7&gt;2,D7*10,0)+IF(D7&gt;8,C7^0.5*D7^0.7)+IF(D7&gt;16,C7^1.2*(D7-15)^2.5,0))*500</f>
+        <v>700000</v>
+      </c>
+      <c r="W7" s="49">
         <f t="shared" si="2"/>
-        <v>553.92921689228058</v>
-      </c>
-      <c r="O7" s="49">
-        <f>MAX(200*(D7-2)+C7*D7*293*1.3^(1-E7)/(1.2^(I7-2)*SQRT(E7)*J7*SQRT(K7)),50)</f>
-        <v>15963.859773146431</v>
-      </c>
-      <c r="P7" s="49">
-        <f t="shared" si="3"/>
-        <v>60206.58939845625</v>
-      </c>
-      <c r="Q7" s="49">
-        <f t="shared" si="4"/>
-        <v>299.44387170614959</v>
-      </c>
-      <c r="R7" s="49">
-        <f t="shared" si="5"/>
-        <v>855.77456855192861</v>
-      </c>
-      <c r="S7" s="49">
-        <f t="shared" si="6"/>
-        <v>5054.0361041989854</v>
-      </c>
-      <c r="T7" s="49">
-        <f t="shared" si="7"/>
-        <v>20639.802012802509</v>
-      </c>
-      <c r="U7" s="49">
-        <f t="shared" si="8"/>
-        <v>700000</v>
-      </c>
-      <c r="V7" s="49">
-        <f t="shared" si="9"/>
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>472</v>
       </c>
@@ -21312,59 +21359,62 @@
       <c r="K8" s="37">
         <v>1</v>
       </c>
-      <c r="M8" s="48">
-        <f t="shared" si="1"/>
+      <c r="L8" s="37">
+        <v>1</v>
+      </c>
+      <c r="N8" s="48">
+        <f>5+C8*D8*9*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2)*SQRT(E8))</f>
         <v>7.598076211353316</v>
       </c>
-      <c r="N8" s="48">
+      <c r="O8" s="48">
         <f>40+(50+C8*D8*23)*SQRT(E8)*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2))</f>
         <v>61.073284825421339</v>
       </c>
-      <c r="O8" s="48">
-        <f>MAX(200*(D8-2)+C8*D8*293*1.3^(1-E8)/(1.2^(I8-2)*SQRT(E8)*J8*SQRT(K8)),50)</f>
+      <c r="P8" s="48">
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="P8" s="48">
-        <f>MAX(180*(D8-2)+C8*D8*900*SQRT(E8)*1.3^(1-E8)/(1.2^(I8-2)*J8*SQRT(K8)),100)</f>
+      <c r="Q8" s="48">
+        <f>MAX(180*(D8-2)+C8*D8*900*SQRT(E8)*1.3^(1-E8)/(1.2^(I8-2)*J8*SQRT(L8)),100)*(IF(AND(K8&gt;3,D8&lt;9),1-K8/50,1))*(IF(AND(K8&lt;5,D8&gt;12),1+1/K8,1))</f>
         <v>720</v>
       </c>
-      <c r="Q8" s="48">
-        <f>30/SQRT(E8)+(50+C8*D8)*K8/(J8*SQRT(E8))+30*(K8-1)</f>
+      <c r="R8" s="48">
+        <f>30/SQRT(E8)+(50+C8*D8)*L8/(J8*SQRT(E8))+30*(L8-1)</f>
         <v>81</v>
       </c>
-      <c r="R8" s="48">
-        <f t="shared" si="5"/>
+      <c r="S8" s="48">
+        <f>210+(190+C8*D8)*L8*SQRT(E8)/(J8*1.1^(I8-2))</f>
         <v>401</v>
       </c>
-      <c r="S8" s="48">
-        <f t="shared" si="6"/>
+      <c r="T8" s="48">
+        <f>C8^1.15*D8^1.2*12*1.25^(1-E8)/(SQRT(E8))*IF(D8&gt;17,1.2^(D8-15),1)</f>
         <v>12</v>
       </c>
-      <c r="T8" s="48">
-        <f t="shared" si="7"/>
+      <c r="U8" s="48">
+        <f>95+C8^1*D8^1.58*33*1.25^(1-E8)*SQRT(E8)/1+IF(C8&gt;=6,C8*200,0)</f>
         <v>128</v>
       </c>
-      <c r="U8" s="48">
-        <f t="shared" si="8"/>
+      <c r="V8" s="48">
+        <f>_xlfn.FLOOR.MATH(2*C8^1.3*D8^1.3+IF(D8&gt;2,D8*10,0)+IF(D8&gt;8,C8^0.5*D8^0.7)+IF(D8&gt;16,C8^1.2*(D8-15)^2.5,0))*500</f>
         <v>1000</v>
       </c>
-      <c r="V8" s="48">
-        <f t="shared" si="9"/>
+      <c r="W8" s="48">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>150</v>
       </c>
@@ -21374,52 +21424,52 @@
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>149</v>
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H19" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
         <v>410</v>
       </c>
@@ -21429,68 +21479,68 @@
       <c r="D20" s="33" t="s">
         <v>414</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="J20" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="K20" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="J20" s="33" t="s">
+      <c r="L20" s="33" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>409</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>434</v>
       </c>
-      <c r="I21" s="40">
-        <v>1</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" s="40">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>412</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>435</v>
       </c>
-      <c r="I22" s="40">
+      <c r="K22" s="40">
         <v>1.5</v>
       </c>
-      <c r="J22" t="s">
+      <c r="L22" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>413</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>436</v>
       </c>
-      <c r="I23" s="40">
+      <c r="K23" s="40">
         <v>2</v>
       </c>
-      <c r="J23" t="s">
+      <c r="L23" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>415</v>
       </c>
@@ -21500,17 +21550,17 @@
       <c r="D24" t="s">
         <v>426</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>437</v>
       </c>
-      <c r="I24" s="44" t="s">
-        <v>488</v>
-      </c>
-      <c r="J24" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="L24" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>416</v>
       </c>
@@ -21520,17 +21570,17 @@
       <c r="D25" t="s">
         <v>423</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>438</v>
       </c>
-      <c r="I25" s="44" t="s">
-        <v>489</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="L25" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>417</v>
       </c>
@@ -21540,17 +21590,20 @@
       <c r="D26" t="s">
         <v>425</v>
       </c>
-      <c r="H26" t="s">
+      <c r="G26" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="J26" t="s">
         <v>439</v>
       </c>
-      <c r="I26" s="44" t="s">
-        <v>490</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="L26" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>418</v>
       </c>
@@ -21560,68 +21613,100 @@
       <c r="D27" t="s">
         <v>424</v>
       </c>
-      <c r="H27" t="s">
+      <c r="G27" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="J27" t="s">
         <v>440</v>
       </c>
-      <c r="I27" s="40">
+      <c r="K27" s="40">
         <v>9</v>
       </c>
-      <c r="J27" t="s">
+      <c r="L27" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>419</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
-      <c r="H28" t="s">
+      <c r="G28" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="H28" s="40">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
         <v>441</v>
       </c>
-      <c r="I28" s="40">
+      <c r="K28" s="40">
         <v>13</v>
       </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>420</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
-      <c r="H29" t="s">
+      <c r="G29" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="H29" s="40">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
         <v>442</v>
       </c>
-      <c r="I29" s="40">
+      <c r="K29" s="40">
         <v>16</v>
       </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>421</v>
       </c>
       <c r="C30" s="44" t="s">
         <v>422</v>
       </c>
-      <c r="H30" t="s">
+      <c r="G30" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="H30" s="40">
+        <v>3</v>
+      </c>
+      <c r="J30" t="s">
         <v>443</v>
       </c>
-      <c r="I30" s="40">
+      <c r="K30" s="40">
         <v>20</v>
       </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G31" s="42" t="s">
+        <v>503</v>
+      </c>
+      <c r="H31" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>474</v>
       </c>
@@ -21629,15 +21714,21 @@
         <v>475</v>
       </c>
       <c r="D32" s="44"/>
-      <c r="H32" s="24" t="s">
+      <c r="G32" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="H32" s="40">
+        <v>5</v>
+      </c>
+      <c r="J32" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I33" s="2" t="s">
+    <row r="33" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K33" s="2" t="s">
         <v>445</v>
       </c>
     </row>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A18FEF5-5255-461D-BF4D-DAB3B7B36BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16273FA-E8F6-4D68-99B1-7D707C4C44FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="522">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2017,6 +2017,74 @@
   </si>
   <si>
     <t>不可击退不可击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流派类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装大全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪械</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳皇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀内力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳内力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物防套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔抗套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血防套</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15134,9 +15202,10 @@
   <dimension ref="B2:V109"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="8.25" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" customWidth="1"/>
+    <col min="9" max="9" width="9.25" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="9.9140625" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
     <col min="12" max="12" width="11.83203125" customWidth="1"/>
     <col min="13" max="13" width="8.33203125" customWidth="1"/>
     <col min="14" max="14" width="11.25" customWidth="1"/>
@@ -15946,7 +16015,7 @@
         <v>3.5985408238146728E-2</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C17">
         <v>8</v>
       </c>
@@ -15955,7 +16024,7 @@
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>9</v>
       </c>
@@ -15964,7 +16033,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>10</v>
       </c>
@@ -15973,7 +16042,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C20">
         <v>11</v>
       </c>
@@ -15982,7 +16051,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>12</v>
       </c>
@@ -15991,7 +16060,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C22">
         <v>13</v>
       </c>
@@ -16000,7 +16069,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C23">
         <v>14</v>
       </c>
@@ -16009,7 +16078,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>15</v>
       </c>
@@ -16017,8 +16086,17 @@
         <f t="shared" si="11"/>
         <v>55000</v>
       </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="H24" t="s">
+        <v>513</v>
+      </c>
+      <c r="I24" t="s">
+        <v>511</v>
+      </c>
+      <c r="J24" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C25">
         <v>16</v>
       </c>
@@ -16026,8 +16104,20 @@
         <f t="shared" si="11"/>
         <v>60000</v>
       </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>514</v>
+      </c>
+      <c r="K25" t="s">
+        <v>506</v>
+      </c>
+      <c r="M25" t="s">
+        <v>507</v>
+      </c>
+      <c r="O25" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C26">
         <v>17</v>
       </c>
@@ -16035,8 +16125,23 @@
         <f t="shared" si="11"/>
         <v>65000</v>
       </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>509</v>
+      </c>
+      <c r="K26" t="str">
+        <f>I25&amp;K25&amp;J26</f>
+        <v>通用重甲攻击套</v>
+      </c>
+      <c r="M26" t="str">
+        <f>I25&amp;M25&amp;J26</f>
+        <v>通用中甲攻击套</v>
+      </c>
+      <c r="O26" t="str">
+        <f>I25&amp;O25&amp;J26</f>
+        <v>通用轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>18</v>
       </c>
@@ -16044,8 +16149,23 @@
         <f t="shared" si="11"/>
         <v>70000</v>
       </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>510</v>
+      </c>
+      <c r="K27" t="str">
+        <f>I25&amp;K25&amp;J27</f>
+        <v>通用重甲一般套</v>
+      </c>
+      <c r="M27" t="str">
+        <f>I25&amp;M25&amp;J27</f>
+        <v>通用中甲一般套</v>
+      </c>
+      <c r="O27" t="str">
+        <f>I25&amp;O25&amp;J27</f>
+        <v>通用轻甲一般套</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>19</v>
       </c>
@@ -16053,8 +16173,23 @@
         <f t="shared" si="11"/>
         <v>75000</v>
       </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>519</v>
+      </c>
+      <c r="K28" t="str">
+        <f>I25&amp;K25&amp;J28</f>
+        <v>通用重甲物防套</v>
+      </c>
+      <c r="M28" t="str">
+        <f>I25&amp;M25&amp;J28</f>
+        <v>通用中甲物防套</v>
+      </c>
+      <c r="O28" t="str">
+        <f>I25&amp;O25&amp;J28</f>
+        <v>通用轻甲物防套</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C29">
         <v>20</v>
       </c>
@@ -16062,8 +16197,23 @@
         <f t="shared" si="11"/>
         <v>80000</v>
       </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>520</v>
+      </c>
+      <c r="K29" t="str">
+        <f>I25&amp;K25&amp;J29</f>
+        <v>通用重甲魔抗套</v>
+      </c>
+      <c r="M29" t="str">
+        <f>I25&amp;M25&amp;J29</f>
+        <v>通用中甲魔抗套</v>
+      </c>
+      <c r="O29" t="str">
+        <f>I25&amp;O25&amp;J29</f>
+        <v>通用轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C30">
         <v>21</v>
       </c>
@@ -16071,8 +16221,23 @@
         <f t="shared" si="11"/>
         <v>85000</v>
       </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>521</v>
+      </c>
+      <c r="K30" t="str">
+        <f>I25&amp;K25&amp;J30</f>
+        <v>通用重甲血防套</v>
+      </c>
+      <c r="M30" t="str">
+        <f>I25&amp;M25&amp;J30</f>
+        <v>通用中甲血防套</v>
+      </c>
+      <c r="O30" t="str">
+        <f>I25&amp;O25&amp;J30</f>
+        <v>通用轻甲血防套</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C31">
         <v>22</v>
       </c>
@@ -16080,8 +16245,20 @@
         <f t="shared" si="11"/>
         <v>90000</v>
       </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>512</v>
+      </c>
+      <c r="K31" t="s">
+        <v>506</v>
+      </c>
+      <c r="M31" t="s">
+        <v>507</v>
+      </c>
+      <c r="O31" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C32">
         <v>23</v>
       </c>
@@ -16089,8 +16266,23 @@
         <f t="shared" si="11"/>
         <v>95000</v>
       </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>509</v>
+      </c>
+      <c r="K32" t="str">
+        <f>I31&amp;K31&amp;J32</f>
+        <v>刀剑重甲攻击套</v>
+      </c>
+      <c r="M32" t="str">
+        <f>I31&amp;M31&amp;J32</f>
+        <v>刀剑中甲攻击套</v>
+      </c>
+      <c r="O32" t="str">
+        <f>I31&amp;O31&amp;J32</f>
+        <v>刀剑轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="33" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>24</v>
       </c>
@@ -16098,8 +16290,23 @@
         <f t="shared" si="11"/>
         <v>100000</v>
       </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>510</v>
+      </c>
+      <c r="K33" t="str">
+        <f>I31&amp;K31&amp;J33</f>
+        <v>刀剑重甲一般套</v>
+      </c>
+      <c r="M33" t="str">
+        <f>I31&amp;M31&amp;J33</f>
+        <v>刀剑中甲一般套</v>
+      </c>
+      <c r="O33" t="str">
+        <f>I31&amp;O31&amp;J33</f>
+        <v>刀剑轻甲一般套</v>
+      </c>
+    </row>
+    <row r="34" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C34">
         <v>25</v>
       </c>
@@ -16107,8 +16314,23 @@
         <f t="shared" si="11"/>
         <v>105000</v>
       </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>519</v>
+      </c>
+      <c r="K34" t="str">
+        <f>I31&amp;K31&amp;J34</f>
+        <v>刀剑重甲物防套</v>
+      </c>
+      <c r="M34" t="str">
+        <f>I31&amp;M31&amp;J34</f>
+        <v>刀剑中甲物防套</v>
+      </c>
+      <c r="O34" t="str">
+        <f>I31&amp;O31&amp;J34</f>
+        <v>刀剑轻甲物防套</v>
+      </c>
+    </row>
+    <row r="35" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C35">
         <v>26</v>
       </c>
@@ -16116,8 +16338,23 @@
         <f t="shared" si="11"/>
         <v>110000</v>
       </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>520</v>
+      </c>
+      <c r="K35" t="str">
+        <f>I31&amp;K31&amp;J35</f>
+        <v>刀剑重甲魔抗套</v>
+      </c>
+      <c r="M35" t="str">
+        <f>I31&amp;M31&amp;J35</f>
+        <v>刀剑中甲魔抗套</v>
+      </c>
+      <c r="O35" t="str">
+        <f>I31&amp;O31&amp;J35</f>
+        <v>刀剑轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="36" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C36">
         <v>27</v>
       </c>
@@ -16125,8 +16362,23 @@
         <f t="shared" si="11"/>
         <v>115000</v>
       </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>521</v>
+      </c>
+      <c r="K36" t="str">
+        <f>I31&amp;K31&amp;J36</f>
+        <v>刀剑重甲血防套</v>
+      </c>
+      <c r="M36" t="str">
+        <f>I31&amp;M31&amp;J36</f>
+        <v>刀剑中甲血防套</v>
+      </c>
+      <c r="O36" t="str">
+        <f>I31&amp;O31&amp;J36</f>
+        <v>刀剑轻甲血防套</v>
+      </c>
+    </row>
+    <row r="37" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C37">
         <v>28</v>
       </c>
@@ -16134,8 +16386,20 @@
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
+        <v>515</v>
+      </c>
+      <c r="K37" t="s">
+        <v>506</v>
+      </c>
+      <c r="M37" t="s">
+        <v>507</v>
+      </c>
+      <c r="O37" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="38" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C38">
         <v>29</v>
       </c>
@@ -16143,8 +16407,23 @@
         <f t="shared" si="11"/>
         <v>125000</v>
       </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>509</v>
+      </c>
+      <c r="K38" t="str">
+        <f>I37&amp;K37&amp;J38</f>
+        <v>枪械重甲攻击套</v>
+      </c>
+      <c r="M38" t="str">
+        <f>I37&amp;M37&amp;J38</f>
+        <v>枪械中甲攻击套</v>
+      </c>
+      <c r="O38" t="str">
+        <f>I37&amp;O37&amp;J38</f>
+        <v>枪械轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="39" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C39">
         <v>30</v>
       </c>
@@ -16152,8 +16431,23 @@
         <f t="shared" si="11"/>
         <v>130000</v>
       </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>510</v>
+      </c>
+      <c r="K39" t="str">
+        <f>I37&amp;K37&amp;J39</f>
+        <v>枪械重甲一般套</v>
+      </c>
+      <c r="M39" t="str">
+        <f>I37&amp;M37&amp;J39</f>
+        <v>枪械中甲一般套</v>
+      </c>
+      <c r="O39" t="str">
+        <f>I37&amp;O37&amp;J39</f>
+        <v>枪械轻甲一般套</v>
+      </c>
+    </row>
+    <row r="40" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C40">
         <v>31</v>
       </c>
@@ -16161,8 +16455,23 @@
         <f t="shared" si="11"/>
         <v>135000</v>
       </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>519</v>
+      </c>
+      <c r="K40" t="str">
+        <f>I37&amp;K37&amp;J40</f>
+        <v>枪械重甲物防套</v>
+      </c>
+      <c r="M40" t="str">
+        <f>I37&amp;M37&amp;J40</f>
+        <v>枪械中甲物防套</v>
+      </c>
+      <c r="O40" t="str">
+        <f>I37&amp;O37&amp;J40</f>
+        <v>枪械轻甲物防套</v>
+      </c>
+    </row>
+    <row r="41" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C41">
         <v>32</v>
       </c>
@@ -16170,8 +16479,23 @@
         <f t="shared" si="11"/>
         <v>140000</v>
       </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>520</v>
+      </c>
+      <c r="K41" t="str">
+        <f>I37&amp;K37&amp;J41</f>
+        <v>枪械重甲魔抗套</v>
+      </c>
+      <c r="M41" t="str">
+        <f>I37&amp;M37&amp;J41</f>
+        <v>枪械中甲魔抗套</v>
+      </c>
+      <c r="O41" t="str">
+        <f>I37&amp;O37&amp;J41</f>
+        <v>枪械轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="42" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C42">
         <v>33</v>
       </c>
@@ -16179,8 +16503,23 @@
         <f t="shared" si="11"/>
         <v>145000</v>
       </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>521</v>
+      </c>
+      <c r="K42" t="str">
+        <f>I37&amp;K37&amp;J42</f>
+        <v>枪械重甲血防套</v>
+      </c>
+      <c r="M42" t="str">
+        <f>I37&amp;M37&amp;J42</f>
+        <v>枪械中甲血防套</v>
+      </c>
+      <c r="O42" t="str">
+        <f>I37&amp;O37&amp;J42</f>
+        <v>枪械轻甲血防套</v>
+      </c>
+    </row>
+    <row r="43" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C43">
         <v>34</v>
       </c>
@@ -16188,8 +16527,20 @@
         <f>C43*5000-20000</f>
         <v>150000</v>
       </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I43" t="s">
+        <v>516</v>
+      </c>
+      <c r="K43" t="s">
+        <v>506</v>
+      </c>
+      <c r="M43" t="s">
+        <v>507</v>
+      </c>
+      <c r="O43" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="44" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C44">
         <v>35</v>
       </c>
@@ -16197,8 +16548,23 @@
         <f t="shared" si="11"/>
         <v>155000</v>
       </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>509</v>
+      </c>
+      <c r="K44" t="str">
+        <f>I43&amp;K43&amp;J44</f>
+        <v>拳皇重甲攻击套</v>
+      </c>
+      <c r="M44" t="str">
+        <f>I43&amp;M43&amp;J44</f>
+        <v>拳皇中甲攻击套</v>
+      </c>
+      <c r="O44" t="str">
+        <f>I43&amp;O43&amp;J44</f>
+        <v>拳皇轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="45" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C45">
         <v>36</v>
       </c>
@@ -16206,8 +16572,23 @@
         <f t="shared" si="11"/>
         <v>160000</v>
       </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>510</v>
+      </c>
+      <c r="K45" t="str">
+        <f>I43&amp;K43&amp;J45</f>
+        <v>拳皇重甲一般套</v>
+      </c>
+      <c r="M45" t="str">
+        <f>I43&amp;M43&amp;J45</f>
+        <v>拳皇中甲一般套</v>
+      </c>
+      <c r="O45" t="str">
+        <f>I43&amp;O43&amp;J45</f>
+        <v>拳皇轻甲一般套</v>
+      </c>
+    </row>
+    <row r="46" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C46">
         <v>37</v>
       </c>
@@ -16215,8 +16596,23 @@
         <f t="shared" si="11"/>
         <v>165000</v>
       </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>519</v>
+      </c>
+      <c r="K46" t="str">
+        <f>I43&amp;K43&amp;J46</f>
+        <v>拳皇重甲物防套</v>
+      </c>
+      <c r="M46" t="str">
+        <f>I43&amp;M43&amp;J46</f>
+        <v>拳皇中甲物防套</v>
+      </c>
+      <c r="O46" t="str">
+        <f>I43&amp;O43&amp;J46</f>
+        <v>拳皇轻甲物防套</v>
+      </c>
+    </row>
+    <row r="47" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C47">
         <v>38</v>
       </c>
@@ -16224,8 +16620,23 @@
         <f t="shared" si="11"/>
         <v>170000</v>
       </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>520</v>
+      </c>
+      <c r="K47" t="str">
+        <f>I43&amp;K43&amp;J47</f>
+        <v>拳皇重甲魔抗套</v>
+      </c>
+      <c r="M47" t="str">
+        <f>I43&amp;M43&amp;J47</f>
+        <v>拳皇中甲魔抗套</v>
+      </c>
+      <c r="O47" t="str">
+        <f>I43&amp;O43&amp;J47</f>
+        <v>拳皇轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="48" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C48">
         <v>39</v>
       </c>
@@ -16233,8 +16644,23 @@
         <f t="shared" si="11"/>
         <v>175000</v>
       </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>521</v>
+      </c>
+      <c r="K48" t="str">
+        <f>I43&amp;K43&amp;J48</f>
+        <v>拳皇重甲血防套</v>
+      </c>
+      <c r="M48" t="str">
+        <f>I43&amp;M43&amp;J48</f>
+        <v>拳皇中甲血防套</v>
+      </c>
+      <c r="O48" t="str">
+        <f>I43&amp;O43&amp;J48</f>
+        <v>拳皇轻甲血防套</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C49">
         <v>40</v>
       </c>
@@ -16242,8 +16668,20 @@
         <f t="shared" si="11"/>
         <v>180000</v>
       </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I49" t="s">
+        <v>517</v>
+      </c>
+      <c r="K49" t="s">
+        <v>506</v>
+      </c>
+      <c r="M49" t="s">
+        <v>507</v>
+      </c>
+      <c r="O49" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C50">
         <v>41</v>
       </c>
@@ -16251,8 +16689,23 @@
         <f t="shared" si="11"/>
         <v>185000</v>
       </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>509</v>
+      </c>
+      <c r="K50" t="str">
+        <f>I49&amp;K49&amp;J50</f>
+        <v>刀内力重甲攻击套</v>
+      </c>
+      <c r="M50" t="str">
+        <f>I49&amp;M49&amp;J50</f>
+        <v>刀内力中甲攻击套</v>
+      </c>
+      <c r="O50" t="str">
+        <f>I49&amp;O49&amp;J50</f>
+        <v>刀内力轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C51">
         <v>42</v>
       </c>
@@ -16260,8 +16713,23 @@
         <f t="shared" si="11"/>
         <v>190000</v>
       </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>510</v>
+      </c>
+      <c r="K51" t="str">
+        <f>I49&amp;K49&amp;J51</f>
+        <v>刀内力重甲一般套</v>
+      </c>
+      <c r="M51" t="str">
+        <f>I49&amp;M49&amp;J51</f>
+        <v>刀内力中甲一般套</v>
+      </c>
+      <c r="O51" t="str">
+        <f>I49&amp;O49&amp;J51</f>
+        <v>刀内力轻甲一般套</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C52">
         <v>43</v>
       </c>
@@ -16269,8 +16737,23 @@
         <f t="shared" si="11"/>
         <v>195000</v>
       </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>519</v>
+      </c>
+      <c r="K52" t="str">
+        <f>I49&amp;K49&amp;J52</f>
+        <v>刀内力重甲物防套</v>
+      </c>
+      <c r="M52" t="str">
+        <f>I49&amp;M49&amp;J52</f>
+        <v>刀内力中甲物防套</v>
+      </c>
+      <c r="O52" t="str">
+        <f>I49&amp;O49&amp;J52</f>
+        <v>刀内力轻甲物防套</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>44</v>
       </c>
@@ -16278,8 +16761,23 @@
         <f t="shared" si="11"/>
         <v>200000</v>
       </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>520</v>
+      </c>
+      <c r="K53" t="str">
+        <f>I49&amp;K49&amp;J53</f>
+        <v>刀内力重甲魔抗套</v>
+      </c>
+      <c r="M53" t="str">
+        <f>I49&amp;M49&amp;J53</f>
+        <v>刀内力中甲魔抗套</v>
+      </c>
+      <c r="O53" t="str">
+        <f>I49&amp;O49&amp;J53</f>
+        <v>刀内力轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C54">
         <v>45</v>
       </c>
@@ -16287,8 +16785,23 @@
         <f t="shared" si="11"/>
         <v>205000</v>
       </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>521</v>
+      </c>
+      <c r="K54" t="str">
+        <f>I49&amp;K49&amp;J54</f>
+        <v>刀内力重甲血防套</v>
+      </c>
+      <c r="M54" t="str">
+        <f>I49&amp;M49&amp;J54</f>
+        <v>刀内力中甲血防套</v>
+      </c>
+      <c r="O54" t="str">
+        <f>I49&amp;O49&amp;J54</f>
+        <v>刀内力轻甲血防套</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C55">
         <v>46</v>
       </c>
@@ -16296,8 +16809,20 @@
         <f t="shared" si="11"/>
         <v>210000</v>
       </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="I55" t="s">
+        <v>518</v>
+      </c>
+      <c r="K55" t="s">
+        <v>506</v>
+      </c>
+      <c r="M55" t="s">
+        <v>507</v>
+      </c>
+      <c r="O55" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C56">
         <v>47</v>
       </c>
@@ -16305,8 +16830,23 @@
         <f t="shared" si="11"/>
         <v>215000</v>
       </c>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>509</v>
+      </c>
+      <c r="K56" t="str">
+        <f>I55&amp;K55&amp;J56</f>
+        <v>拳内力重甲攻击套</v>
+      </c>
+      <c r="M56" t="str">
+        <f>I55&amp;M55&amp;J56</f>
+        <v>拳内力中甲攻击套</v>
+      </c>
+      <c r="O56" t="str">
+        <f>I55&amp;O55&amp;J56</f>
+        <v>拳内力轻甲攻击套</v>
+      </c>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C57">
         <v>48</v>
       </c>
@@ -16314,8 +16854,23 @@
         <f t="shared" si="11"/>
         <v>220000</v>
       </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>510</v>
+      </c>
+      <c r="K57" t="str">
+        <f>I55&amp;K55&amp;J57</f>
+        <v>拳内力重甲一般套</v>
+      </c>
+      <c r="M57" t="str">
+        <f>I55&amp;M55&amp;J57</f>
+        <v>拳内力中甲一般套</v>
+      </c>
+      <c r="O57" t="str">
+        <f>I55&amp;O55&amp;J57</f>
+        <v>拳内力轻甲一般套</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C58">
         <v>49</v>
       </c>
@@ -16323,8 +16878,23 @@
         <f t="shared" si="11"/>
         <v>225000</v>
       </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>519</v>
+      </c>
+      <c r="K58" t="str">
+        <f>I55&amp;K55&amp;J58</f>
+        <v>拳内力重甲物防套</v>
+      </c>
+      <c r="M58" t="str">
+        <f>I55&amp;M55&amp;J58</f>
+        <v>拳内力中甲物防套</v>
+      </c>
+      <c r="O58" t="str">
+        <f>I55&amp;O55&amp;J58</f>
+        <v>拳内力轻甲物防套</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C59">
         <v>50</v>
       </c>
@@ -16332,8 +16902,23 @@
         <f t="shared" ref="D59:D64" si="12">C59*25000-1000000</f>
         <v>250000</v>
       </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J59" t="s">
+        <v>520</v>
+      </c>
+      <c r="K59" t="str">
+        <f>I55&amp;K55&amp;J59</f>
+        <v>拳内力重甲魔抗套</v>
+      </c>
+      <c r="M59" t="str">
+        <f>I55&amp;M55&amp;J59</f>
+        <v>拳内力中甲魔抗套</v>
+      </c>
+      <c r="O59" t="str">
+        <f>I55&amp;O55&amp;J59</f>
+        <v>拳内力轻甲魔抗套</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C60">
         <v>51</v>
       </c>
@@ -16341,8 +16926,23 @@
         <f t="shared" si="12"/>
         <v>275000</v>
       </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>521</v>
+      </c>
+      <c r="K60" t="str">
+        <f>I55&amp;K55&amp;J60</f>
+        <v>拳内力重甲血防套</v>
+      </c>
+      <c r="M60" t="str">
+        <f>I55&amp;M55&amp;J60</f>
+        <v>拳内力中甲血防套</v>
+      </c>
+      <c r="O60" t="str">
+        <f>I55&amp;O55&amp;J60</f>
+        <v>拳内力轻甲血防套</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C61">
         <v>52</v>
       </c>
@@ -16351,7 +16951,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C62">
         <v>53</v>
       </c>
@@ -16360,7 +16960,7 @@
         <v>325000</v>
       </c>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C63">
         <v>54</v>
       </c>
@@ -16369,7 +16969,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C64">
         <v>55</v>
       </c>
@@ -20988,11 +21588,11 @@
         <v>1.3</v>
       </c>
       <c r="N3" s="49">
-        <f>5+C3*D3*9*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2)*SQRT(E3))</f>
+        <f t="shared" ref="N3:N8" si="0">5+C3*D3*9*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2)*SQRT(E3))</f>
         <v>18.888439450165926</v>
       </c>
       <c r="O3" s="49">
-        <f>40+(50+C3*D3*23)*SQRT(E3)*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2))</f>
+        <f t="shared" ref="O3:O8" si="1">40+(50+C3*D3*23)*SQRT(E3)*1.25^(1-E3)*J3/(G3*SQRT(H3)*1.2^(F3-3)*1.1^(I3-2))</f>
         <v>109.54507458009012</v>
       </c>
       <c r="P3" s="49">
@@ -21004,23 +21604,23 @@
         <v>1584.1216598494022</v>
       </c>
       <c r="R3" s="49">
-        <f>30/SQRT(E3)+(50+C3*D3)*L3/(J3*SQRT(E3))+30*(L3-1)</f>
+        <f t="shared" ref="R3:R8" si="2">30/SQRT(E3)+(50+C3*D3)*L3/(J3*SQRT(E3))+30*(L3-1)</f>
         <v>136.10648909600368</v>
       </c>
       <c r="S3" s="49">
-        <f>210+(190+C3*D3)*L3*SQRT(E3)/(J3*1.1^(I3-2))</f>
+        <f t="shared" ref="S3:S8" si="3">210+(190+C3*D3)*L3*SQRT(E3)/(J3*1.1^(I3-2))</f>
         <v>516.16801764921502</v>
       </c>
       <c r="T3" s="49">
-        <f>C3^1.15*D3^1.2*12*1.25^(1-E3)/(SQRT(E3))*IF(D3&gt;17,1.2^(D3-15),1)</f>
+        <f t="shared" ref="T3:T8" si="4">C3^1.15*D3^1.2*12*1.25^(1-E3)/(SQRT(E3))*IF(D3&gt;17,1.2^(D3-15),1)</f>
         <v>22.820637166202172</v>
       </c>
       <c r="U3" s="49">
-        <f>95+C3^1*D3^1.58*33*1.25^(1-E3)*SQRT(E3)/1+IF(C3&gt;=6,C3*200,0)</f>
+        <f t="shared" ref="U3:U8" si="5">95+C3^1*D3^1.58*33*1.25^(1-E3)*SQRT(E3)/1+IF(C3&gt;=6,C3*200,0)</f>
         <v>153.56863807482276</v>
       </c>
       <c r="V3" s="49">
-        <f>_xlfn.FLOOR.MATH(2*C3^1.3*D3^1.3+IF(D3&gt;2,D3*10,0)+IF(D3&gt;8,C3^0.5*D3^0.7)+IF(D3&gt;16,C3^1.2*(D3-15)^2.5,0))*500</f>
+        <f t="shared" ref="V3:V8" si="6">_xlfn.FLOOR.MATH(2*C3^1.3*D3^1.3+IF(D3&gt;2,D3*10,0)+IF(D3&gt;8,C3^0.5*D3^0.7)+IF(D3&gt;16,C3^1.2*(D3-15)^2.5,0))*500</f>
         <v>1500</v>
       </c>
       <c r="W3" s="49">
@@ -21063,43 +21663,43 @@
         <v>3</v>
       </c>
       <c r="N4" s="49">
-        <f>5+C4*D4*9*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2)*SQRT(E4))</f>
+        <f t="shared" si="0"/>
         <v>81.165501413354804</v>
       </c>
       <c r="O4" s="49">
-        <f>40+(50+C4*D4*23)*SQRT(E4)*1.25^(1-E4)*J4/(G4*SQRT(H4)*1.2^(F4-3)*1.1^(I4-2))</f>
+        <f t="shared" si="1"/>
         <v>244.47507687123712</v>
       </c>
       <c r="P4" s="49">
-        <f t="shared" ref="P4:P8" si="0">MAX(200*(D4-2)+C4*D4*293*1.3^(1-E4)/(1.2^(I4-2)*SQRT(E4)*J4*SQRT(L4)),50)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
+        <f t="shared" ref="P4:P8" si="7">MAX(200*(D4-2)+C4*D4*293*1.3^(1-E4)/(1.2^(I4-2)*SQRT(E4)*J4*SQRT(L4)),50)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
         <v>6394.7248368899818</v>
       </c>
       <c r="Q4" s="49">
-        <f t="shared" ref="Q4:Q7" si="1">MAX(180*(D4-2)+C4*D4*900*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(L4)),100)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
+        <f t="shared" ref="Q4:Q7" si="8">MAX(180*(D4-2)+C4*D4*900*SQRT(E4)*1.3^(1-E4)/(1.2^(I4-2)*J4*SQRT(L4)),100)*(IF(AND(K4&gt;3,D4&lt;9),1-K4/50,1))*(IF(AND(K4&lt;5,D4&gt;12),1+1/K4,1))</f>
         <v>12209.034532016676</v>
       </c>
       <c r="R4" s="49">
-        <f>30/SQRT(E4)+(50+C4*D4)*L4/(J4*SQRT(E4))+30*(L4-1)</f>
+        <f t="shared" si="2"/>
         <v>272.73504259314552</v>
       </c>
       <c r="S4" s="49">
-        <f>210+(190+C4*D4)*L4*SQRT(E4)/(J4*1.1^(I4-2))</f>
+        <f t="shared" si="3"/>
         <v>787.74812851276283</v>
       </c>
       <c r="T4" s="49">
-        <f>C4^1.15*D4^1.2*12*1.25^(1-E4)/(SQRT(E4))*IF(D4&gt;17,1.2^(D4-15),1)</f>
+        <f t="shared" si="4"/>
         <v>280.8555532243625</v>
       </c>
       <c r="U4" s="49">
-        <f>95+C4^1*D4^1.58*33*1.25^(1-E4)*SQRT(E4)/1+IF(C4&gt;=6,C4*200,0)</f>
+        <f t="shared" si="5"/>
         <v>1937.2844760253267</v>
       </c>
       <c r="V4" s="49">
-        <f>_xlfn.FLOOR.MATH(2*C4^1.3*D4^1.3+IF(D4&gt;2,D4*10,0)+IF(D4&gt;8,C4^0.5*D4^0.7)+IF(D4&gt;16,C4^1.2*(D4-15)^2.5,0))*500</f>
+        <f t="shared" si="6"/>
         <v>96000</v>
       </c>
       <c r="W4" s="49">
-        <f t="shared" ref="W4:W8" si="2">_xlfn.FLOOR.MATH(V4/700)*20</f>
+        <f t="shared" ref="W4:W8" si="9">_xlfn.FLOOR.MATH(V4/700)*20</f>
         <v>2740</v>
       </c>
     </row>
@@ -21138,43 +21738,43 @@
         <v>2</v>
       </c>
       <c r="N5" s="49">
-        <f>5+C5*D5*9*1.25^(1-E5)*J5/(G5*SQRT(H5)*1.2^(F5-3)*1.1^(I5-2)*SQRT(E5))</f>
+        <f t="shared" si="0"/>
         <v>80.557769388855888</v>
       </c>
       <c r="O5" s="49">
-        <f>40+(50+C5*D5*23)*SQRT(E5)*1.25^(1-E5)*J5/(G5*SQRT(H5)*1.2^(F5-3)*1.1^(I5-2))</f>
+        <f t="shared" si="1"/>
         <v>305.01188004165385</v>
       </c>
       <c r="P5" s="49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>10331.389426371348</v>
       </c>
       <c r="Q5" s="49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>32748.807607011862</v>
       </c>
       <c r="R5" s="49">
-        <f>30/SQRT(E5)+(50+C5*D5)*L5/(J5*SQRT(E5))+30*(L5-1)</f>
+        <f t="shared" si="2"/>
         <v>229.77432661993439</v>
       </c>
       <c r="S5" s="49">
-        <f>210+(190+C5*D5)*L5*SQRT(E5)/(J5*1.1^(I5-2))</f>
+        <f t="shared" si="3"/>
         <v>737.47509565192433</v>
       </c>
       <c r="T5" s="49">
-        <f>C5^1.15*D5^1.2*12*1.25^(1-E5)/(SQRT(E5))*IF(D5&gt;17,1.2^(D5-15),1)</f>
+        <f t="shared" si="4"/>
         <v>756.06308092998961</v>
       </c>
       <c r="U5" s="49">
-        <f>95+C5^1*D5^1.58*33*1.25^(1-E5)*SQRT(E5)/1+IF(C5&gt;=6,C5*200,0)</f>
+        <f t="shared" si="5"/>
         <v>6170.2529291090304</v>
       </c>
       <c r="V5" s="49">
-        <f>_xlfn.FLOOR.MATH(2*C5^1.3*D5^1.3+IF(D5&gt;2,D5*10,0)+IF(D5&gt;8,C5^0.5*D5^0.7)+IF(D5&gt;16,C5^1.2*(D5-15)^2.5,0))*500</f>
+        <f t="shared" si="6"/>
         <v>187000</v>
       </c>
       <c r="W5" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>5340</v>
       </c>
     </row>
@@ -21213,43 +21813,43 @@
         <v>1.8</v>
       </c>
       <c r="N6" s="49">
-        <f>5+C6*D6*9*1.25^(1-E6)*J6/(G6*SQRT(H6)*1.2^(F6-3)*1.1^(I6-2)*SQRT(E6))</f>
+        <f t="shared" si="0"/>
         <v>171.9387184223385</v>
       </c>
       <c r="O6" s="49">
-        <f>40+(50+C6*D6*23)*SQRT(E6)*1.25^(1-E6)*J6/(G6*SQRT(H6)*1.2^(F6-3)*1.1^(I6-2))</f>
+        <f t="shared" si="1"/>
         <v>621.50320250447896</v>
       </c>
       <c r="P6" s="49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1715.9646431015246</v>
       </c>
       <c r="Q6" s="49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>5210.6546571660292</v>
       </c>
       <c r="R6" s="49">
-        <f>30/SQRT(E6)+(50+C6*D6)*L6/(J6*SQRT(E6))+30*(L6-1)</f>
+        <f t="shared" si="2"/>
         <v>98.537895869181312</v>
       </c>
       <c r="S6" s="49">
-        <f>210+(190+C6*D6)*L6*SQRT(E6)/(J6*1.1^(I6-2))</f>
+        <f t="shared" si="3"/>
         <v>386.60480375905706</v>
       </c>
       <c r="T6" s="49">
-        <f>C6^1.15*D6^1.2*12*1.25^(1-E6)/(SQRT(E6))*IF(D6&gt;17,1.2^(D6-15),1)</f>
+        <f t="shared" si="4"/>
         <v>272.30122809761059</v>
       </c>
       <c r="U6" s="49">
-        <f>95+C6^1*D6^1.58*33*1.25^(1-E6)*SQRT(E6)/1+IF(C6&gt;=6,C6*200,0)</f>
+        <f t="shared" si="5"/>
         <v>1331.0536970509388</v>
       </c>
       <c r="V6" s="49">
-        <f>_xlfn.FLOOR.MATH(2*C6^1.3*D6^1.3+IF(D6&gt;2,D6*10,0)+IF(D6&gt;8,C6^0.5*D6^0.7)+IF(D6&gt;16,C6^1.2*(D6-15)^2.5,0))*500</f>
+        <f t="shared" si="6"/>
         <v>56500</v>
       </c>
       <c r="W6" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>1600</v>
       </c>
     </row>
@@ -21288,43 +21888,43 @@
         <v>2</v>
       </c>
       <c r="N7" s="49">
-        <f>5+C7*D7*9*1.25^(1-E7)*J7/(G7*SQRT(H7)*1.2^(F7-3)*1.1^(I7-2)*SQRT(E7))</f>
+        <f t="shared" si="0"/>
         <v>136.21597027036952</v>
       </c>
       <c r="O7" s="49">
-        <f>40+(50+C7*D7*23)*SQRT(E7)*1.25^(1-E7)*J7/(G7*SQRT(H7)*1.2^(F7-3)*1.1^(I7-2))</f>
+        <f t="shared" si="1"/>
         <v>553.92921689228058</v>
       </c>
       <c r="P7" s="49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>15963.859773146431</v>
       </c>
       <c r="Q7" s="49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>60206.58939845625</v>
       </c>
       <c r="R7" s="49">
-        <f>30/SQRT(E7)+(50+C7*D7)*L7/(J7*SQRT(E7))+30*(L7-1)</f>
+        <f t="shared" si="2"/>
         <v>299.44387170614959</v>
       </c>
       <c r="S7" s="49">
-        <f>210+(190+C7*D7)*L7*SQRT(E7)/(J7*1.1^(I7-2))</f>
+        <f t="shared" si="3"/>
         <v>855.77456855192861</v>
       </c>
       <c r="T7" s="49">
-        <f>C7^1.15*D7^1.2*12*1.25^(1-E7)/(SQRT(E7))*IF(D7&gt;17,1.2^(D7-15),1)</f>
+        <f t="shared" si="4"/>
         <v>5054.0361041989854</v>
       </c>
       <c r="U7" s="49">
-        <f>95+C7^1*D7^1.58*33*1.25^(1-E7)*SQRT(E7)/1+IF(C7&gt;=6,C7*200,0)</f>
+        <f t="shared" si="5"/>
         <v>20639.802012802509</v>
       </c>
       <c r="V7" s="49">
-        <f>_xlfn.FLOOR.MATH(2*C7^1.3*D7^1.3+IF(D7&gt;2,D7*10,0)+IF(D7&gt;8,C7^0.5*D7^0.7)+IF(D7&gt;16,C7^1.2*(D7-15)^2.5,0))*500</f>
+        <f t="shared" si="6"/>
         <v>700000</v>
       </c>
       <c r="W7" s="49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20000</v>
       </c>
     </row>
@@ -21363,15 +21963,15 @@
         <v>1</v>
       </c>
       <c r="N8" s="48">
-        <f>5+C8*D8*9*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2)*SQRT(E8))</f>
+        <f t="shared" si="0"/>
         <v>7.598076211353316</v>
       </c>
       <c r="O8" s="48">
-        <f>40+(50+C8*D8*23)*SQRT(E8)*1.25^(1-E8)*J8/(G8*SQRT(H8)*1.2^(F8-3)*1.1^(I8-2))</f>
+        <f t="shared" si="1"/>
         <v>61.073284825421339</v>
       </c>
       <c r="P8" s="48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="Q8" s="48">
@@ -21379,27 +21979,27 @@
         <v>720</v>
       </c>
       <c r="R8" s="48">
-        <f>30/SQRT(E8)+(50+C8*D8)*L8/(J8*SQRT(E8))+30*(L8-1)</f>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="S8" s="48">
-        <f>210+(190+C8*D8)*L8*SQRT(E8)/(J8*1.1^(I8-2))</f>
+        <f t="shared" si="3"/>
         <v>401</v>
       </c>
       <c r="T8" s="48">
-        <f>C8^1.15*D8^1.2*12*1.25^(1-E8)/(SQRT(E8))*IF(D8&gt;17,1.2^(D8-15),1)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="U8" s="48">
-        <f>95+C8^1*D8^1.58*33*1.25^(1-E8)*SQRT(E8)/1+IF(C8&gt;=6,C8*200,0)</f>
+        <f t="shared" si="5"/>
         <v>128</v>
       </c>
       <c r="V8" s="48">
-        <f>_xlfn.FLOOR.MATH(2*C8^1.3*D8^1.3+IF(D8&gt;2,D8*10,0)+IF(D8&gt;8,C8^0.5*D8^0.7)+IF(D8&gt;16,C8^1.2*(D8-15)^2.5,0))*500</f>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="W8" s="48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16273FA-E8F6-4D68-99B1-7D707C4C44FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE4306B-A378-480C-A9F2-0D7C9D32CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="45">
-        <f>G3+H3*0.5+I3/D3+IF(D3&gt;4,K3*300/(D3-2.5),K3*300)+J3*0.5</f>
+        <f>G3+H3*0.5+I3/D3+IF(D3&gt;4,K3*300/(D3-3),K3*300)+J3*0.5</f>
         <v>44333.333333333336</v>
       </c>
       <c r="O3" s="45">
@@ -20870,7 +20870,7 @@
         <v>300</v>
       </c>
       <c r="M4" s="45">
-        <f t="shared" ref="M4:M6" si="0">G4+H4*0.5+I4/D4+IF(D4&gt;4,K4*300/(D4-2.5),K4*300)+J4*0.5</f>
+        <f t="shared" ref="M4:M6" si="0">G4+H4*0.5+I4/D4+IF(D4&gt;4,K4*300/(D4-3),K4*300)+J4*0.5</f>
         <v>160000</v>
       </c>
       <c r="O4" s="45">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE4306B-A378-480C-A9F2-0D7C9D32CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D5AF1-D6C9-479B-8B3C-9936AA524A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -15307,12 +15307,12 @@
         <v>-0.75</v>
       </c>
       <c r="P4" s="41">
-        <f>0.5*(1+(J4-1)^4.2/216)-0.7</f>
+        <f>0.25+0.25*(1+(J4-1)^4.2/216)-0.7</f>
         <v>-0.19999999999999996</v>
       </c>
       <c r="Q4" s="41"/>
       <c r="R4">
-        <f t="shared" ref="R4:R16" si="0">J4*200+600</f>
+        <f>J4*100+700</f>
         <v>800</v>
       </c>
       <c r="S4">
@@ -15334,11 +15334,11 @@
         <v>2</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K15" si="1" xml:space="preserve"> (J5- 1) * (J5 - 1) * (J5 - 1) + 1</f>
+        <f t="shared" ref="K5:K15" si="0" xml:space="preserve"> (J5- 1) * (J5 - 1) * (J5 - 1) + 1</f>
         <v>2</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L15" si="2">_xlfn.FLOOR.MATH(0.5*(J5-1)*(J5-1)*(J5-1)+1)</f>
+        <f t="shared" ref="L5:L15" si="1">_xlfn.FLOOR.MATH(0.5*(J5-1)*(J5-1)*(J5-1)+1)</f>
         <v>1</v>
       </c>
       <c r="M5">
@@ -15350,24 +15350,24 @@
         <v>1</v>
       </c>
       <c r="O5" s="41">
-        <f t="shared" ref="O5:O16" si="3">0.25*(1+(J5-1)^4.2/216)-1</f>
+        <f t="shared" ref="O5:O16" si="2">0.25*(1+(J5-1)^4.2/216)-1</f>
         <v>-0.74884259259259256</v>
       </c>
       <c r="P5" s="41">
-        <f t="shared" ref="P5:P16" si="4">0.5*(1+(J5-1)^4.2/216)-0.7</f>
-        <v>-0.19768518518518519</v>
+        <f t="shared" ref="P5:P16" si="3">0.25+0.25*(1+(J5-1)^4.2/216)-0.7</f>
+        <v>-0.19884259259259252</v>
       </c>
       <c r="Q5" s="41">
-        <f t="shared" ref="Q5:Q16" si="5">O5/M5</f>
+        <f t="shared" ref="Q5:Q16" si="4">O5/M5</f>
         <v>-0.74884259259259256</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+        <f t="shared" ref="R5:R16" si="5">J5*100+700</f>
+        <v>900</v>
       </c>
       <c r="S5">
         <f t="shared" ref="S5:S16" si="6">M5*R5</f>
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="T5" s="41">
         <f>O5/N5</f>
@@ -15375,11 +15375,11 @@
       </c>
       <c r="U5" s="41">
         <f>P5/M5</f>
-        <v>-0.19768518518518519</v>
+        <v>-0.19884259259259252</v>
       </c>
       <c r="V5" s="41">
         <f>P5/N5</f>
-        <v>-0.19768518518518519</v>
+        <v>-0.19884259259259252</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
@@ -15387,11 +15387,11 @@
         <v>3</v>
       </c>
       <c r="K6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="M6">
@@ -15403,24 +15403,24 @@
         <v>2</v>
       </c>
       <c r="O6" s="41">
+        <f t="shared" si="2"/>
+        <v>-0.72872780824079564</v>
+      </c>
+      <c r="P6" s="41">
         <f t="shared" si="3"/>
-        <v>-0.72872780824079564</v>
-      </c>
-      <c r="P6" s="41">
+        <v>-0.17872780824079559</v>
+      </c>
+      <c r="Q6" s="41">
         <f t="shared" si="4"/>
-        <v>-0.15745561648159123</v>
-      </c>
-      <c r="Q6" s="41">
+        <v>-0.24290926941359856</v>
+      </c>
+      <c r="R6">
         <f t="shared" si="5"/>
-        <v>-0.24290926941359856</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="S6">
         <f t="shared" si="6"/>
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="T6" s="41">
         <f t="shared" ref="T6:T16" si="7">O6/N6</f>
@@ -15428,11 +15428,11 @@
       </c>
       <c r="U6" s="41">
         <f t="shared" ref="U6:U16" si="8">P6/M6</f>
-        <v>-5.2485205493863742E-2</v>
+        <v>-5.95759360802652E-2</v>
       </c>
       <c r="V6" s="41">
         <f t="shared" ref="V6:V15" si="9">P6/N6</f>
-        <v>-7.8727808240795616E-2</v>
+        <v>-8.9363904120397797E-2</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.3">
@@ -15440,11 +15440,11 @@
         <v>4</v>
       </c>
       <c r="K7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="L7">
         <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="M7">
@@ -15456,24 +15456,24 @@
         <v>7</v>
       </c>
       <c r="O7" s="41">
+        <f t="shared" si="2"/>
+        <v>-0.63321272441104515</v>
+      </c>
+      <c r="P7" s="41">
         <f t="shared" si="3"/>
-        <v>-0.63321272441104515</v>
-      </c>
-      <c r="P7" s="41">
+        <v>-8.3212724411045103E-2</v>
+      </c>
+      <c r="Q7" s="41">
         <f t="shared" si="4"/>
-        <v>3.3574551177909751E-2</v>
-      </c>
-      <c r="Q7" s="41">
+        <v>-5.276772703425376E-2</v>
+      </c>
+      <c r="R7">
         <f t="shared" si="5"/>
-        <v>-5.276772703425376E-2</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="0"/>
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="S7">
         <f t="shared" si="6"/>
-        <v>16800</v>
+        <v>13200</v>
       </c>
       <c r="T7" s="41">
         <f t="shared" si="7"/>
@@ -15481,11 +15481,11 @@
       </c>
       <c r="U7" s="41">
         <f t="shared" si="8"/>
-        <v>2.7978792648258124E-3</v>
+        <v>-6.9343937009204255E-3</v>
       </c>
       <c r="V7" s="41">
         <f t="shared" si="9"/>
-        <v>4.7963644539871075E-3</v>
+        <v>-1.1887532058720729E-2</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -15496,11 +15496,11 @@
         <v>5</v>
       </c>
       <c r="K8">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="M8">
@@ -15512,24 +15512,24 @@
         <v>21</v>
       </c>
       <c r="O8" s="41">
+        <f t="shared" si="2"/>
+        <v>-0.35903469310432778</v>
+      </c>
+      <c r="P8" s="41">
         <f t="shared" si="3"/>
-        <v>-0.35903469310432778</v>
-      </c>
-      <c r="P8" s="41">
+        <v>0.19096530689567226</v>
+      </c>
+      <c r="Q8" s="41">
         <f t="shared" si="4"/>
-        <v>0.58193061379134448</v>
-      </c>
-      <c r="Q8" s="41">
+        <v>-8.9758673276081943E-3</v>
+      </c>
+      <c r="R8">
         <f t="shared" si="5"/>
-        <v>-8.9758673276081943E-3</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="S8">
         <f t="shared" si="6"/>
-        <v>64000</v>
+        <v>48000</v>
       </c>
       <c r="T8" s="41">
         <f t="shared" si="7"/>
@@ -15537,11 +15537,11 @@
       </c>
       <c r="U8" s="41">
         <f t="shared" si="8"/>
-        <v>1.4548265344783613E-2</v>
+        <v>4.7741326723918067E-3</v>
       </c>
       <c r="V8" s="41">
         <f t="shared" si="9"/>
-        <v>2.7710981609111642E-2</v>
+        <v>9.0935860426510605E-3</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
@@ -15555,11 +15555,11 @@
         <v>6</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="M9">
@@ -15571,24 +15571,24 @@
         <v>54</v>
       </c>
       <c r="O9" s="41">
+        <f t="shared" si="2"/>
+        <v>0.24806833149682728</v>
+      </c>
+      <c r="P9" s="41">
         <f t="shared" si="3"/>
-        <v>0.24806833149682728</v>
-      </c>
-      <c r="P9" s="41">
+        <v>0.79806833149682732</v>
+      </c>
+      <c r="Q9" s="41">
         <f t="shared" si="4"/>
-        <v>1.7961366629936546</v>
-      </c>
-      <c r="Q9" s="41">
+        <v>2.3625555380650215E-3</v>
+      </c>
+      <c r="R9">
         <f t="shared" si="5"/>
-        <v>2.3625555380650215E-3</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="S9">
         <f t="shared" si="6"/>
-        <v>189000</v>
+        <v>136500</v>
       </c>
       <c r="T9" s="41">
         <f t="shared" si="7"/>
@@ -15596,11 +15596,11 @@
       </c>
       <c r="U9" s="41">
         <f t="shared" si="8"/>
-        <v>1.7106063457082425E-2</v>
+        <v>7.6006507761602598E-3</v>
       </c>
       <c r="V9" s="41">
         <f t="shared" si="9"/>
-        <v>3.3261790055438049E-2</v>
+        <v>1.4779043175867172E-2</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -15615,11 +15615,11 @@
         <v>7</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
+        <v>217</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="1"/>
-        <v>217</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="M10">
@@ -15631,24 +15631,24 @@
         <v>117</v>
       </c>
       <c r="O10" s="41">
+        <f t="shared" si="2"/>
+        <v>1.396453621657884</v>
+      </c>
+      <c r="P10" s="41">
         <f t="shared" si="3"/>
-        <v>1.396453621657884</v>
-      </c>
-      <c r="P10" s="41">
+        <v>1.946453621657884</v>
+      </c>
+      <c r="Q10" s="41">
         <f t="shared" si="4"/>
-        <v>4.0929072433157678</v>
-      </c>
-      <c r="Q10" s="41">
+        <v>6.0452537734107534E-3</v>
+      </c>
+      <c r="R10">
         <f t="shared" si="5"/>
-        <v>6.0452537734107534E-3</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="S10">
         <f t="shared" si="6"/>
-        <v>462000</v>
+        <v>323400</v>
       </c>
       <c r="T10" s="41">
         <f t="shared" si="7"/>
@@ -15656,11 +15656,11 @@
       </c>
       <c r="U10" s="41">
         <f t="shared" si="8"/>
-        <v>1.7718213174527132E-2</v>
+        <v>8.4262061543631337E-3</v>
       </c>
       <c r="V10" s="41">
         <f t="shared" si="9"/>
-        <v>3.4982113190733057E-2</v>
+        <v>1.6636355740665677E-2</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
@@ -15675,11 +15675,11 @@
         <v>8</v>
       </c>
       <c r="K11">
+        <f t="shared" si="0"/>
+        <v>344</v>
+      </c>
+      <c r="L11">
         <f t="shared" si="1"/>
-        <v>344</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="M11">
@@ -15691,24 +15691,24 @@
         <v>226</v>
       </c>
       <c r="O11" s="41">
+        <f t="shared" si="2"/>
+        <v>3.3510779641070823</v>
+      </c>
+      <c r="P11" s="41">
         <f t="shared" si="3"/>
-        <v>3.3510779641070823</v>
-      </c>
-      <c r="P11" s="41">
+        <v>3.9010779641070821</v>
+      </c>
+      <c r="Q11" s="41">
         <f t="shared" si="4"/>
-        <v>8.0021559282141652</v>
-      </c>
-      <c r="Q11" s="41">
+        <v>7.4800847413104511E-3</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="5"/>
-        <v>7.4800847413104511E-3</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="0"/>
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="S11">
         <f t="shared" si="6"/>
-        <v>985600</v>
+        <v>672000</v>
       </c>
       <c r="T11" s="41">
         <f t="shared" si="7"/>
@@ -15716,11 +15716,11 @@
       </c>
       <c r="U11" s="41">
         <f t="shared" si="8"/>
-        <v>1.7861955196906618E-2</v>
+        <v>8.7077633127390225E-3</v>
       </c>
       <c r="V11" s="41">
         <f t="shared" si="9"/>
-        <v>3.5407769593867988E-2</v>
+        <v>1.7261406920827796E-2</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
@@ -15735,11 +15735,11 @@
         <v>9</v>
       </c>
       <c r="K12">
+        <f t="shared" si="0"/>
+        <v>513</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="1"/>
-        <v>513</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
         <v>257</v>
       </c>
       <c r="M12">
@@ -15751,24 +15751,24 @@
         <v>398</v>
       </c>
       <c r="O12" s="41">
+        <f t="shared" si="2"/>
+        <v>6.4356192782715125</v>
+      </c>
+      <c r="P12" s="41">
         <f t="shared" si="3"/>
-        <v>6.4356192782715125</v>
-      </c>
-      <c r="P12" s="41">
+        <v>6.9856192782715123</v>
+      </c>
+      <c r="Q12" s="41">
         <f t="shared" si="4"/>
-        <v>14.171238556543026</v>
-      </c>
-      <c r="Q12" s="41">
+        <v>8.125781917009486E-3</v>
+      </c>
+      <c r="R12">
         <f t="shared" si="5"/>
-        <v>8.125781917009486E-3</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="0"/>
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="S12">
         <f t="shared" si="6"/>
-        <v>1900800</v>
+        <v>1267200</v>
       </c>
       <c r="T12" s="41">
         <f t="shared" si="7"/>
@@ -15776,11 +15776,11 @@
       </c>
       <c r="U12" s="41">
         <f t="shared" si="8"/>
-        <v>1.7892977975433114E-2</v>
+        <v>8.8202263614539297E-3</v>
       </c>
       <c r="V12" s="41">
         <f t="shared" si="9"/>
-        <v>3.5606127026490013E-2</v>
+        <v>1.7551807231837972E-2</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
@@ -15795,11 +15795,11 @@
         <v>10</v>
       </c>
       <c r="K13">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="L13">
         <f t="shared" si="1"/>
-        <v>730</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="2"/>
         <v>365</v>
       </c>
       <c r="M13">
@@ -15811,24 +15811,24 @@
         <v>655</v>
       </c>
       <c r="O13" s="41">
+        <f t="shared" si="2"/>
+        <v>11.034327326919785</v>
+      </c>
+      <c r="P13" s="41">
         <f t="shared" si="3"/>
-        <v>11.034327326919785</v>
-      </c>
-      <c r="P13" s="41">
+        <v>11.584327326919786</v>
+      </c>
+      <c r="Q13" s="41">
         <f t="shared" si="4"/>
-        <v>23.36865465383957</v>
-      </c>
-      <c r="Q13" s="41">
+        <v>8.4554232390189922E-3</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="5"/>
-        <v>8.4554232390189922E-3</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="0"/>
-        <v>2600</v>
+        <v>1700</v>
       </c>
       <c r="S13">
         <f t="shared" si="6"/>
-        <v>3393000</v>
+        <v>2218500</v>
       </c>
       <c r="T13" s="41">
         <f t="shared" si="7"/>
@@ -15836,11 +15836,11 @@
       </c>
       <c r="U13" s="41">
         <f t="shared" si="8"/>
-        <v>1.7907015060413464E-2</v>
+        <v>8.8768791777163111E-3</v>
       </c>
       <c r="V13" s="41">
         <f t="shared" si="9"/>
-        <v>3.5677335349373389E-2</v>
+        <v>1.7685995918961504E-2</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
@@ -15855,11 +15855,11 @@
         <v>11</v>
       </c>
       <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="L14">
         <f t="shared" si="1"/>
-        <v>1001</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
         <v>501</v>
       </c>
       <c r="M14">
@@ -15871,24 +15871,24 @@
         <v>1020</v>
       </c>
       <c r="O14" s="41">
+        <f t="shared" si="2"/>
+        <v>17.593671209040679</v>
+      </c>
+      <c r="P14" s="41">
         <f t="shared" si="3"/>
-        <v>17.593671209040679</v>
-      </c>
-      <c r="P14" s="41">
+        <v>18.143671209040679</v>
+      </c>
+      <c r="Q14" s="41">
         <f t="shared" si="4"/>
-        <v>36.487342418081354</v>
-      </c>
-      <c r="Q14" s="41">
+        <v>8.6455386776612669E-3</v>
+      </c>
+      <c r="R14">
         <f t="shared" si="5"/>
-        <v>8.6455386776612669E-3</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="S14">
         <f t="shared" si="6"/>
-        <v>5698000</v>
+        <v>3663000</v>
       </c>
       <c r="T14" s="41">
         <f t="shared" si="7"/>
@@ -15896,11 +15896,11 @@
       </c>
       <c r="U14" s="41">
         <f t="shared" si="8"/>
-        <v>1.7929897994143171E-2</v>
+        <v>8.9158089479315378E-3</v>
       </c>
       <c r="V14" s="41">
         <f t="shared" si="9"/>
-        <v>3.577190433145231E-2</v>
+        <v>1.7787912950039883E-2</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -15915,11 +15915,11 @@
         <v>12</v>
       </c>
       <c r="K15">
+        <f t="shared" si="0"/>
+        <v>1332</v>
+      </c>
+      <c r="L15">
         <f t="shared" si="1"/>
-        <v>1332</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
         <v>666</v>
       </c>
       <c r="M15">
@@ -15931,24 +15931,24 @@
         <v>1521</v>
       </c>
       <c r="O15" s="41">
+        <f t="shared" si="2"/>
+        <v>26.623828068826533</v>
+      </c>
+      <c r="P15" s="41">
         <f t="shared" si="3"/>
-        <v>26.623828068826533</v>
-      </c>
-      <c r="P15" s="41">
+        <v>27.173828068826534</v>
+      </c>
+      <c r="Q15" s="41">
         <f t="shared" si="4"/>
-        <v>54.547656137653064</v>
-      </c>
-      <c r="Q15" s="41">
+        <v>8.7693768342643388E-3</v>
+      </c>
+      <c r="R15">
         <f t="shared" si="5"/>
-        <v>8.7693768342643388E-3</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>1900</v>
       </c>
       <c r="S15">
         <f t="shared" si="6"/>
-        <v>9108000</v>
+        <v>5768400</v>
       </c>
       <c r="T15" s="41">
         <f t="shared" si="7"/>
@@ -15956,11 +15956,11 @@
       </c>
       <c r="U15" s="41">
         <f t="shared" si="8"/>
-        <v>1.7966948661941061E-2</v>
+        <v>8.950536254554194E-3</v>
       </c>
       <c r="V15" s="41">
         <f t="shared" si="9"/>
-        <v>3.586302178675415E-2</v>
+        <v>1.7865764673784704E-2</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
@@ -15983,24 +15983,24 @@
         <v>2187</v>
       </c>
       <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>38.700043908413448</v>
+      </c>
+      <c r="P16" s="41">
         <f t="shared" si="3"/>
-        <v>38.700043908413448</v>
-      </c>
-      <c r="P16" s="41">
+        <v>39.250043908413446</v>
+      </c>
+      <c r="Q16" s="41">
         <f t="shared" si="4"/>
-        <v>78.700087816826894</v>
-      </c>
-      <c r="Q16" s="41">
+        <v>8.8599001621825664E-3</v>
+      </c>
+      <c r="R16">
         <f t="shared" si="5"/>
-        <v>8.8599001621825664E-3</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="S16">
         <f t="shared" si="6"/>
-        <v>13977600</v>
+        <v>8736000</v>
       </c>
       <c r="T16" s="41">
         <f t="shared" si="7"/>
@@ -16008,11 +16008,11 @@
       </c>
       <c r="U16" s="41">
         <f t="shared" si="8"/>
-        <v>1.8017419371984179E-2</v>
+        <v>8.9858159130983169E-3</v>
       </c>
       <c r="V16" s="41">
         <f>P16/N16</f>
-        <v>3.5985408238146728E-2</v>
+        <v>1.7946979381990601E-2</v>
       </c>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D5AF1-D6C9-479B-8B3C-9936AA524A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4529D1D2-43E9-46D8-BC65-D07E307E2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="525">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1141,10 +1141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>喷火的穿刺系数为1.5，狙击枪穿刺系数为1.5，普通穿刺为2，非穿刺为1（其他拥有穿刺效果根据单体段数数量填入穿刺系数，段数较多时可填3或更高的穿刺系数）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（霰弹短枪）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1344,10 +1340,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>超前武器需要减少一层加权，可减为负数。限制等级低于30级的穿刺武器、低于40级的属性伤害武器均视为超前武器。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>限制等级低于40级的属性伤害武器视为超前武器，需减少一层加权等级，可减到负数。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1988,18 +1980,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>韧性系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶段、档次系数、韧性系数参考下方表格。阶段和档次系数将决定整体数值大致水平。对于拥有暖机、强力buff、多阶段等显著影响面板的特殊机制单位可能不适用。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>韧性系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>短击退可击飞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2085,6 +2065,38 @@
   </si>
   <si>
     <t>血防套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>档次系数注释：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霸体系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段、档次系数、霸体系数参考下方表格。阶段和档次系数将决定整体数值大致水平。对于拥有暖机、强力buff、多阶段等显著影响面板的特殊机制单位可能不适用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霸体系数注释：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以击退/击飞动画决定霸体系数的整数位。当怪物的韧性系数值高于20时则添加小数位，每20点韧性增加0.1的霸体系数，最高0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喷火/次级穿刺子弹的穿刺系数为1.5，狙击枪穿刺系数为1.5，普通穿刺为2，非穿刺为1（其他拥有穿刺效果根据单体段数数量填入穿刺系数，段数较多时可填3或更高的穿刺系数）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超前武器需要减少一层加权，可减为负数。具体可查看下方的解锁等级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器类型解锁等级:10级:特效刀/次级穿刺枪/普通霰弹枪;20级:慢射速穿刺枪;30级:属性刀/高射速穿刺枪/慢射速属性枪;35级:穿刺霰弹枪;40级:普通属性枪/慢射速穿刺属性枪;45级:高射速穿刺属性枪。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3058,7 +3070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364195C9-74FB-4CBB-BB5D-941A31102B71}">
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -3113,7 +3125,7 @@
         <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L1" t="s">
         <v>273</v>
@@ -3122,24 +3134,24 @@
         <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O1" t="s">
         <v>165</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="V1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>50</v>
@@ -3175,7 +3187,7 @@
         <v>162</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>12</v>
@@ -3184,58 +3196,58 @@
         <v>221</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R2" s="11" t="s">
         <v>222</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>220</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB2" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="AG2" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="AC2" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>381</v>
-      </c>
       <c r="AH2" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI2" s="14" t="s">
         <v>169</v>
@@ -3244,19 +3256,19 @@
         <v>271</v>
       </c>
       <c r="AK2" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AL2" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AM2" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AN2" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
@@ -3664,7 +3676,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D6" s="12">
         <v>30</v>
@@ -3797,7 +3809,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D7" s="12">
         <v>28</v>
@@ -3930,7 +3942,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D8" s="12">
         <v>35</v>
@@ -4344,7 +4356,7 @@
         <v>157</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>47</v>
@@ -4485,7 +4497,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D13" s="12">
         <v>30</v>
@@ -4618,7 +4630,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D14" s="12">
         <v>32</v>
@@ -4747,11 +4759,11 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D15" s="12">
         <v>15</v>
@@ -4917,7 +4929,7 @@
         <v>276</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>280</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
@@ -4926,10 +4938,10 @@
         <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
@@ -4938,7 +4950,7 @@
         <v>278</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -4949,13 +4961,13 @@
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AL24" s="2" t="s">
         <v>268</v>
@@ -4970,7 +4982,7 @@
         <v>169</v>
       </c>
       <c r="AN25" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AO25" t="s">
         <v>271</v>
@@ -4981,7 +4993,7 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AK26" s="2" t="s">
         <v>269</v>
@@ -5002,7 +5014,7 @@
     </row>
     <row r="27" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AL27" s="28">
         <v>20</v>
@@ -5056,7 +5068,7 @@
     </row>
     <row r="30" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AL30" s="28">
         <v>50</v>
@@ -5074,7 +5086,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -5097,14 +5109,19 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>331</v>
+        <v>523</v>
       </c>
       <c r="AL32" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AM32" s="16">
         <f>IF(AL31&gt;=35,17*AL31-330,7*AL31+15) * IF(AL31&gt;=25, 1 + (MIN(13,(AL31-18)/3.5) - 1) * (MIN(13,(AL31-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(AL31-18)/3.5)  - 1),1)</f>
         <v>355.53265306122444</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="2" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -15224,7 +15241,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -15238,43 +15255,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L3" t="s">
         <v>388</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>392</v>
+      </c>
+      <c r="N3" t="s">
+        <v>393</v>
+      </c>
+      <c r="O3" t="s">
+        <v>391</v>
+      </c>
+      <c r="P3" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q3" t="s">
         <v>389</v>
       </c>
-      <c r="L3" t="s">
+      <c r="R3" t="s">
+        <v>397</v>
+      </c>
+      <c r="S3" t="s">
+        <v>398</v>
+      </c>
+      <c r="T3" t="s">
         <v>390</v>
       </c>
-      <c r="M3" t="s">
-        <v>394</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="U3" t="s">
         <v>395</v>
       </c>
-      <c r="O3" t="s">
-        <v>393</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="V3" t="s">
         <v>396</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>391</v>
-      </c>
-      <c r="R3" t="s">
-        <v>399</v>
-      </c>
-      <c r="S3" t="s">
-        <v>400</v>
-      </c>
-      <c r="T3" t="s">
-        <v>392</v>
-      </c>
-      <c r="U3" t="s">
-        <v>397</v>
-      </c>
-      <c r="V3" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -16087,13 +16104,13 @@
         <v>55000</v>
       </c>
       <c r="H24" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="I24" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="J24" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.3">
@@ -16105,16 +16122,16 @@
         <v>60000</v>
       </c>
       <c r="I25" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="K25" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M25" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O25" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.3">
@@ -16126,7 +16143,7 @@
         <v>65000</v>
       </c>
       <c r="J26" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K26" t="str">
         <f>I25&amp;K25&amp;J26</f>
@@ -16150,7 +16167,7 @@
         <v>70000</v>
       </c>
       <c r="J27" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K27" t="str">
         <f>I25&amp;K25&amp;J27</f>
@@ -16174,7 +16191,7 @@
         <v>75000</v>
       </c>
       <c r="J28" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K28" t="str">
         <f>I25&amp;K25&amp;J28</f>
@@ -16198,7 +16215,7 @@
         <v>80000</v>
       </c>
       <c r="J29" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K29" t="str">
         <f>I25&amp;K25&amp;J29</f>
@@ -16222,7 +16239,7 @@
         <v>85000</v>
       </c>
       <c r="J30" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K30" t="str">
         <f>I25&amp;K25&amp;J30</f>
@@ -16246,16 +16263,16 @@
         <v>90000</v>
       </c>
       <c r="I31" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="K31" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M31" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O31" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.3">
@@ -16267,7 +16284,7 @@
         <v>95000</v>
       </c>
       <c r="J32" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K32" t="str">
         <f>I31&amp;K31&amp;J32</f>
@@ -16291,7 +16308,7 @@
         <v>100000</v>
       </c>
       <c r="J33" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K33" t="str">
         <f>I31&amp;K31&amp;J33</f>
@@ -16315,7 +16332,7 @@
         <v>105000</v>
       </c>
       <c r="J34" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K34" t="str">
         <f>I31&amp;K31&amp;J34</f>
@@ -16339,7 +16356,7 @@
         <v>110000</v>
       </c>
       <c r="J35" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K35" t="str">
         <f>I31&amp;K31&amp;J35</f>
@@ -16363,7 +16380,7 @@
         <v>115000</v>
       </c>
       <c r="J36" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K36" t="str">
         <f>I31&amp;K31&amp;J36</f>
@@ -16387,16 +16404,16 @@
         <v>120000</v>
       </c>
       <c r="I37" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="K37" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M37" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O37" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.3">
@@ -16408,7 +16425,7 @@
         <v>125000</v>
       </c>
       <c r="J38" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K38" t="str">
         <f>I37&amp;K37&amp;J38</f>
@@ -16432,7 +16449,7 @@
         <v>130000</v>
       </c>
       <c r="J39" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K39" t="str">
         <f>I37&amp;K37&amp;J39</f>
@@ -16456,7 +16473,7 @@
         <v>135000</v>
       </c>
       <c r="J40" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K40" t="str">
         <f>I37&amp;K37&amp;J40</f>
@@ -16480,7 +16497,7 @@
         <v>140000</v>
       </c>
       <c r="J41" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K41" t="str">
         <f>I37&amp;K37&amp;J41</f>
@@ -16504,7 +16521,7 @@
         <v>145000</v>
       </c>
       <c r="J42" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K42" t="str">
         <f>I37&amp;K37&amp;J42</f>
@@ -16528,16 +16545,16 @@
         <v>150000</v>
       </c>
       <c r="I43" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="K43" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M43" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O43" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.3">
@@ -16549,7 +16566,7 @@
         <v>155000</v>
       </c>
       <c r="J44" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K44" t="str">
         <f>I43&amp;K43&amp;J44</f>
@@ -16573,7 +16590,7 @@
         <v>160000</v>
       </c>
       <c r="J45" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K45" t="str">
         <f>I43&amp;K43&amp;J45</f>
@@ -16597,7 +16614,7 @@
         <v>165000</v>
       </c>
       <c r="J46" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K46" t="str">
         <f>I43&amp;K43&amp;J46</f>
@@ -16621,7 +16638,7 @@
         <v>170000</v>
       </c>
       <c r="J47" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K47" t="str">
         <f>I43&amp;K43&amp;J47</f>
@@ -16645,7 +16662,7 @@
         <v>175000</v>
       </c>
       <c r="J48" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K48" t="str">
         <f>I43&amp;K43&amp;J48</f>
@@ -16669,16 +16686,16 @@
         <v>180000</v>
       </c>
       <c r="I49" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="K49" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M49" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O49" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.3">
@@ -16690,7 +16707,7 @@
         <v>185000</v>
       </c>
       <c r="J50" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K50" t="str">
         <f>I49&amp;K49&amp;J50</f>
@@ -16714,7 +16731,7 @@
         <v>190000</v>
       </c>
       <c r="J51" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K51" t="str">
         <f>I49&amp;K49&amp;J51</f>
@@ -16738,7 +16755,7 @@
         <v>195000</v>
       </c>
       <c r="J52" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K52" t="str">
         <f>I49&amp;K49&amp;J52</f>
@@ -16762,7 +16779,7 @@
         <v>200000</v>
       </c>
       <c r="J53" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K53" t="str">
         <f>I49&amp;K49&amp;J53</f>
@@ -16786,7 +16803,7 @@
         <v>205000</v>
       </c>
       <c r="J54" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K54" t="str">
         <f>I49&amp;K49&amp;J54</f>
@@ -16810,16 +16827,16 @@
         <v>210000</v>
       </c>
       <c r="I55" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="K55" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M55" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O55" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.3">
@@ -16831,7 +16848,7 @@
         <v>215000</v>
       </c>
       <c r="J56" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K56" t="str">
         <f>I55&amp;K55&amp;J56</f>
@@ -16855,7 +16872,7 @@
         <v>220000</v>
       </c>
       <c r="J57" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="K57" t="str">
         <f>I55&amp;K55&amp;J57</f>
@@ -16879,7 +16896,7 @@
         <v>225000</v>
       </c>
       <c r="J58" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K58" t="str">
         <f>I55&amp;K55&amp;J58</f>
@@ -16903,7 +16920,7 @@
         <v>250000</v>
       </c>
       <c r="J59" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K59" t="str">
         <f>I55&amp;K55&amp;J59</f>
@@ -16927,7 +16944,7 @@
         <v>275000</v>
       </c>
       <c r="J60" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K60" t="str">
         <f>I55&amp;K55&amp;J60</f>
@@ -18390,7 +18407,7 @@
         <v>169</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>170</v>
@@ -18420,10 +18437,10 @@
         <v>154</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -18602,7 +18619,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -18916,7 +18933,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18932,7 +18949,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18968,7 +18985,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>177</v>
@@ -19174,7 +19191,7 @@
         <v>236</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -19218,7 +19235,7 @@
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
@@ -19238,7 +19255,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
@@ -19248,12 +19265,12 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -19359,41 +19376,41 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -19429,7 +19446,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -19544,7 +19561,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -19594,7 +19611,7 @@
         <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -19779,25 +19796,25 @@
         <v>275</v>
       </c>
       <c r="D11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" t="s">
         <v>315</v>
-      </c>
-      <c r="D12" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -19940,12 +19957,12 @@
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -20250,7 +20267,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -20482,7 +20499,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>225</v>
@@ -20703,7 +20720,7 @@
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="N27" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
@@ -20774,7 +20791,7 @@
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>239</v>
@@ -20783,30 +20800,30 @@
         <v>240</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I2" s="33" t="s">
         <v>94</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D3" s="34">
         <v>1.5</v>
@@ -20843,7 +20860,7 @@
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D4" s="34">
         <v>4</v>
@@ -20880,7 +20897,7 @@
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D5" s="34">
         <v>4</v>
@@ -20917,7 +20934,7 @@
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D6" s="36">
         <v>1</v>
@@ -20957,50 +20974,50 @@
         <v>236</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I11" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I12" s="33" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>224</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L12" s="33" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
       </c>
       <c r="I13" s="46" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J13" s="45">
         <v>20</v>
@@ -21019,19 +21036,19 @@
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J14" s="45">
         <v>0</v>
@@ -21050,13 +21067,13 @@
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
       </c>
       <c r="I15" s="46" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J15" s="45">
         <v>0</v>
@@ -21071,13 +21088,13 @@
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J16" s="45">
         <v>0</v>
@@ -21092,13 +21109,13 @@
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E17" s="40">
         <v>3</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J17" s="45">
         <v>0</v>
@@ -21113,16 +21130,16 @@
     </row>
     <row r="18" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E18" s="40">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J18" s="45">
         <v>0</v>
@@ -21137,16 +21154,16 @@
     </row>
     <row r="19" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E19" s="40">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I19" s="46" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J19" s="45">
         <v>0</v>
@@ -21161,16 +21178,16 @@
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E20" s="40">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J20" s="45">
         <v>0</v>
@@ -21185,16 +21202,16 @@
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E21" s="40">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J21" s="45">
         <v>0</v>
@@ -21209,13 +21226,13 @@
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E22" s="40">
         <v>8</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J22" s="45">
         <v>0</v>
@@ -21230,7 +21247,7 @@
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E23" s="40">
         <v>9</v>
@@ -21238,13 +21255,13 @@
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="4:16" x14ac:dyDescent="0.3">
@@ -21267,10 +21284,10 @@
         <v>224</v>
       </c>
       <c r="O25" s="38" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P25" s="39" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="4:16" x14ac:dyDescent="0.3">
@@ -21278,7 +21295,7 @@
         <v>87</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J26" s="45">
         <v>20</v>
@@ -21306,10 +21323,10 @@
     </row>
     <row r="27" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H27" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I27" s="46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J27" s="45">
         <v>0</v>
@@ -21337,7 +21354,7 @@
     </row>
     <row r="28" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I28" s="46" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J28" s="45">
         <v>0</v>
@@ -21361,7 +21378,7 @@
     </row>
     <row r="29" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I29" s="46" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J29" s="45">
         <v>0</v>
@@ -21385,7 +21402,7 @@
     </row>
     <row r="30" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I30" s="46" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J30" s="45">
         <v>0</v>
@@ -21409,7 +21426,7 @@
     </row>
     <row r="31" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I31" s="46" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J31" s="45">
         <v>0</v>
@@ -21433,7 +21450,7 @@
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I32" s="46" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J32" s="45">
         <v>0</v>
@@ -21463,7 +21480,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D334537-191E-473E-8F5E-E80A13E62C45}">
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.4140625" customWidth="1"/>
@@ -21488,74 +21505,74 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="N1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C2" s="33" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>456</v>
       </c>
-      <c r="G2" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>455</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>458</v>
-      </c>
       <c r="K2" s="33" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N2" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q2" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="R2" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="S2" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="O2" s="35" t="s">
-        <v>463</v>
-      </c>
-      <c r="P2" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q2" s="35" t="s">
-        <v>462</v>
-      </c>
-      <c r="R2" s="35" t="s">
+      <c r="T2" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="U2" s="35" t="s">
         <v>467</v>
-      </c>
-      <c r="S2" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>468</v>
-      </c>
-      <c r="U2" s="35" t="s">
-        <v>469</v>
       </c>
       <c r="V2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="W2" s="35" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
@@ -21630,7 +21647,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -21705,7 +21722,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21780,7 +21797,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21855,7 +21872,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
@@ -21930,7 +21947,7 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C8" s="36">
         <v>1</v>
@@ -22005,13 +22022,13 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -22021,7 +22038,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -22030,32 +22047,32 @@
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
@@ -22063,244 +22080,244 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K21" s="40">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K22" s="40">
         <v>1.5</v>
       </c>
       <c r="L22" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K23" s="40">
         <v>2</v>
       </c>
       <c r="L23" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C24" s="40">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J24" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L24" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C25" s="40">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C26" s="40">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="J26" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L26" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C27" s="40">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J27" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K27" s="40">
         <v>9</v>
       </c>
       <c r="L27" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H28" s="40">
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K28" s="40">
         <v>13</v>
       </c>
       <c r="L28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="H29" s="40">
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K29" s="40">
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H30" s="40">
         <v>3</v>
       </c>
       <c r="J30" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K30" s="40">
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G31" s="42" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H31" s="40">
         <v>4</v>
@@ -22308,29 +22325,40 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D32" s="44"/>
       <c r="G32" s="42" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="H32" s="40">
         <v>5</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>236</v>
+        <v>517</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="33" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K33" s="2" t="s">
-        <v>445</v>
-      </c>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="34" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G34" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="35" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="G35" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4529D1D2-43E9-46D8-BC65-D07E307E2957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EA2DAD-573D-45BB-9652-08DF0B91AB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1960,10 +1960,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>机枪的弹容量种族优势可额外换2-4层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击类手套</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2092,11 +2088,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>超前武器需要减少一层加权，可减为负数。具体可查看下方的解锁等级。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武器类型解锁等级:10级:特效刀/次级穿刺枪/普通霰弹枪;20级:慢射速穿刺枪;30级:属性刀/高射速穿刺枪/慢射速属性枪;35级:穿刺霰弹枪;40级:普通属性枪/慢射速穿刺属性枪;45级:高射速穿刺属性枪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大容量机枪（弹容&gt;100）的弹容量种族优势可额外换2-4层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>超前武器需要减少一层加权，可减为负数。具体可查看下方的解锁等级。纵向联弹由于不衰减，当有霰弹值时添加负层级作为平衡，负层级计算方式为-(霰弹值-1)/2。横向联弹有衰减，无需负层级。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4929,7 +4929,7 @@
         <v>276</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
@@ -5086,7 +5086,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>270</v>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AL32" s="2" t="s">
         <v>381</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -16104,13 +16104,13 @@
         <v>55000</v>
       </c>
       <c r="H24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J24" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.3">
@@ -16122,16 +16122,16 @@
         <v>60000</v>
       </c>
       <c r="I25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K25" t="s">
+        <v>500</v>
+      </c>
+      <c r="M25" t="s">
         <v>501</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
         <v>502</v>
-      </c>
-      <c r="O25" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.3">
@@ -16143,7 +16143,7 @@
         <v>65000</v>
       </c>
       <c r="J26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K26" t="str">
         <f>I25&amp;K25&amp;J26</f>
@@ -16167,7 +16167,7 @@
         <v>70000</v>
       </c>
       <c r="J27" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K27" t="str">
         <f>I25&amp;K25&amp;J27</f>
@@ -16191,7 +16191,7 @@
         <v>75000</v>
       </c>
       <c r="J28" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K28" t="str">
         <f>I25&amp;K25&amp;J28</f>
@@ -16215,7 +16215,7 @@
         <v>80000</v>
       </c>
       <c r="J29" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K29" t="str">
         <f>I25&amp;K25&amp;J29</f>
@@ -16239,7 +16239,7 @@
         <v>85000</v>
       </c>
       <c r="J30" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K30" t="str">
         <f>I25&amp;K25&amp;J30</f>
@@ -16263,16 +16263,16 @@
         <v>90000</v>
       </c>
       <c r="I31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K31" t="s">
+        <v>500</v>
+      </c>
+      <c r="M31" t="s">
         <v>501</v>
       </c>
-      <c r="M31" t="s">
+      <c r="O31" t="s">
         <v>502</v>
-      </c>
-      <c r="O31" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.3">
@@ -16284,7 +16284,7 @@
         <v>95000</v>
       </c>
       <c r="J32" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K32" t="str">
         <f>I31&amp;K31&amp;J32</f>
@@ -16308,7 +16308,7 @@
         <v>100000</v>
       </c>
       <c r="J33" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K33" t="str">
         <f>I31&amp;K31&amp;J33</f>
@@ -16332,7 +16332,7 @@
         <v>105000</v>
       </c>
       <c r="J34" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K34" t="str">
         <f>I31&amp;K31&amp;J34</f>
@@ -16356,7 +16356,7 @@
         <v>110000</v>
       </c>
       <c r="J35" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K35" t="str">
         <f>I31&amp;K31&amp;J35</f>
@@ -16380,7 +16380,7 @@
         <v>115000</v>
       </c>
       <c r="J36" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K36" t="str">
         <f>I31&amp;K31&amp;J36</f>
@@ -16404,16 +16404,16 @@
         <v>120000</v>
       </c>
       <c r="I37" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K37" t="s">
+        <v>500</v>
+      </c>
+      <c r="M37" t="s">
         <v>501</v>
       </c>
-      <c r="M37" t="s">
+      <c r="O37" t="s">
         <v>502</v>
-      </c>
-      <c r="O37" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.3">
@@ -16425,7 +16425,7 @@
         <v>125000</v>
       </c>
       <c r="J38" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K38" t="str">
         <f>I37&amp;K37&amp;J38</f>
@@ -16449,7 +16449,7 @@
         <v>130000</v>
       </c>
       <c r="J39" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K39" t="str">
         <f>I37&amp;K37&amp;J39</f>
@@ -16473,7 +16473,7 @@
         <v>135000</v>
       </c>
       <c r="J40" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K40" t="str">
         <f>I37&amp;K37&amp;J40</f>
@@ -16497,7 +16497,7 @@
         <v>140000</v>
       </c>
       <c r="J41" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K41" t="str">
         <f>I37&amp;K37&amp;J41</f>
@@ -16521,7 +16521,7 @@
         <v>145000</v>
       </c>
       <c r="J42" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K42" t="str">
         <f>I37&amp;K37&amp;J42</f>
@@ -16545,16 +16545,16 @@
         <v>150000</v>
       </c>
       <c r="I43" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K43" t="s">
+        <v>500</v>
+      </c>
+      <c r="M43" t="s">
         <v>501</v>
       </c>
-      <c r="M43" t="s">
+      <c r="O43" t="s">
         <v>502</v>
-      </c>
-      <c r="O43" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.3">
@@ -16566,7 +16566,7 @@
         <v>155000</v>
       </c>
       <c r="J44" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K44" t="str">
         <f>I43&amp;K43&amp;J44</f>
@@ -16590,7 +16590,7 @@
         <v>160000</v>
       </c>
       <c r="J45" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K45" t="str">
         <f>I43&amp;K43&amp;J45</f>
@@ -16614,7 +16614,7 @@
         <v>165000</v>
       </c>
       <c r="J46" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K46" t="str">
         <f>I43&amp;K43&amp;J46</f>
@@ -16638,7 +16638,7 @@
         <v>170000</v>
       </c>
       <c r="J47" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K47" t="str">
         <f>I43&amp;K43&amp;J47</f>
@@ -16662,7 +16662,7 @@
         <v>175000</v>
       </c>
       <c r="J48" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K48" t="str">
         <f>I43&amp;K43&amp;J48</f>
@@ -16686,16 +16686,16 @@
         <v>180000</v>
       </c>
       <c r="I49" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K49" t="s">
+        <v>500</v>
+      </c>
+      <c r="M49" t="s">
         <v>501</v>
       </c>
-      <c r="M49" t="s">
+      <c r="O49" t="s">
         <v>502</v>
-      </c>
-      <c r="O49" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.3">
@@ -16707,7 +16707,7 @@
         <v>185000</v>
       </c>
       <c r="J50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K50" t="str">
         <f>I49&amp;K49&amp;J50</f>
@@ -16731,7 +16731,7 @@
         <v>190000</v>
       </c>
       <c r="J51" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K51" t="str">
         <f>I49&amp;K49&amp;J51</f>
@@ -16755,7 +16755,7 @@
         <v>195000</v>
       </c>
       <c r="J52" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K52" t="str">
         <f>I49&amp;K49&amp;J52</f>
@@ -16779,7 +16779,7 @@
         <v>200000</v>
       </c>
       <c r="J53" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K53" t="str">
         <f>I49&amp;K49&amp;J53</f>
@@ -16803,7 +16803,7 @@
         <v>205000</v>
       </c>
       <c r="J54" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K54" t="str">
         <f>I49&amp;K49&amp;J54</f>
@@ -16827,16 +16827,16 @@
         <v>210000</v>
       </c>
       <c r="I55" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K55" t="s">
+        <v>500</v>
+      </c>
+      <c r="M55" t="s">
         <v>501</v>
       </c>
-      <c r="M55" t="s">
+      <c r="O55" t="s">
         <v>502</v>
-      </c>
-      <c r="O55" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.3">
@@ -16848,7 +16848,7 @@
         <v>215000</v>
       </c>
       <c r="J56" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K56" t="str">
         <f>I55&amp;K55&amp;J56</f>
@@ -16872,7 +16872,7 @@
         <v>220000</v>
       </c>
       <c r="J57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K57" t="str">
         <f>I55&amp;K55&amp;J57</f>
@@ -16896,7 +16896,7 @@
         <v>225000</v>
       </c>
       <c r="J58" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K58" t="str">
         <f>I55&amp;K55&amp;J58</f>
@@ -16920,7 +16920,7 @@
         <v>250000</v>
       </c>
       <c r="J59" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K59" t="str">
         <f>I55&amp;K55&amp;J59</f>
@@ -16944,7 +16944,7 @@
         <v>275000</v>
       </c>
       <c r="J60" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K60" t="str">
         <f>I55&amp;K55&amp;J60</f>
@@ -18933,7 +18933,7 @@
         <v>236</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18949,7 +18949,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18985,7 +18985,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>177</v>
@@ -21534,7 +21534,7 @@
         <v>456</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L2" s="33" t="s">
         <v>452</v>
@@ -21647,7 +21647,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -22028,7 +22028,7 @@
         <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -22208,7 +22208,7 @@
         <v>423</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J26" t="s">
         <v>437</v>
@@ -22254,7 +22254,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H28" s="40">
         <v>1</v>
@@ -22277,7 +22277,7 @@
         <v>9</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H29" s="40">
         <v>2</v>
@@ -22300,7 +22300,7 @@
         <v>420</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H30" s="40">
         <v>3</v>
@@ -22317,7 +22317,7 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G31" s="42" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H31" s="40">
         <v>4</v>
@@ -22332,13 +22332,13 @@
       </c>
       <c r="D32" s="44"/>
       <c r="G32" s="42" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H32" s="40">
         <v>5</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>448</v>
@@ -22351,10 +22351,10 @@
     </row>
     <row r="34" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G34" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="35" spans="7:11" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EA2DAD-573D-45BB-9652-08DF0B91AB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BB6B61-58B5-4E4A-85FD-C901D42A8B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -698,10 +698,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>种类系数：有主动战技/特效的可为1.5，效果极其强力时为2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1280,10 +1276,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>短刀为0.5，常规刀为1，长武器为1.5，特效+0.5（强力特效则+1），战技+0.5（强力战技则+1）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>双枪类填1.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1296,10 +1288,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重机枪为1.5，喷火器类为1.5，散弹枪为1.5，轰炸类为1.5，穿刺类为2。只掉落、无法金币或k点购买的武器为0.5，非购买途径明显早于购买途径的物品也为0.5。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>（枪类的攻速等属性参考枪械页）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2097,6 +2085,18 @@
   </si>
   <si>
     <t>超前武器需要减少一层加权，可减为负数。具体可查看下方的解锁等级。纵向联弹由于不衰减，当有霰弹值时添加负层级作为平衡，负层级计算方式为-(霰弹值-1)/2。横向联弹有衰减，无需负层级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大容量机枪（弹容&gt;100）为1.5，喷火器类为1.5，散弹枪为1.5，轰炸类为1.5，次级穿刺为1.5，穿刺类为2。只掉落、无法金币或k点购买的武器为0.5，非购买途径明显早于购买途径的物品也为0.5。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短刀为0.5，常规刀为1，长武器为1.5，特效+0.5（强力特效则+1），强力战技+0.5（战技不强时可不加）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>种类系数：有主动战技/特效的可为1.5，效果极其强力时为2。无购买途径或非购买途径早于购买途径的为0.5，逻辑同上。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3110,7 +3110,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
@@ -3125,33 +3125,33 @@
         <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M1" t="s">
         <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O1" t="s">
         <v>165</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="V1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>50</v>
@@ -3172,7 +3172,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>6</v>
@@ -3181,94 +3181,94 @@
         <v>4</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>162</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="P2" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="R2" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="S2" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="W2" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="R2" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="T2" s="11" t="s">
+      <c r="X2" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y2" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="U2" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="W2" s="14" t="s">
+      <c r="Z2" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="AG2" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="AH2" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI2" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ2" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="AK2" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL2" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="AM2" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="X2" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z2" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="AA2" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="AH2" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="AI2" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AJ2" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="AK2" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="AL2" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="AM2" s="14" t="s">
-        <v>292</v>
-      </c>
       <c r="AN2" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
@@ -3540,7 +3540,7 @@
         <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -3676,7 +3676,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D6" s="12">
         <v>30</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D7" s="12">
         <v>28</v>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D8" s="12">
         <v>35</v>
@@ -4356,7 +4356,7 @@
         <v>157</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>47</v>
@@ -4497,7 +4497,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D13" s="12">
         <v>30</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D14" s="12">
         <v>32</v>
@@ -4759,11 +4759,11 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D15" s="12">
         <v>15</v>
@@ -4902,7 +4902,7 @@
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -4917,40 +4917,40 @@
     <row r="18" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -4961,16 +4961,16 @@
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AL24" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="2:41" x14ac:dyDescent="0.3">
@@ -4979,13 +4979,13 @@
         <v>90</v>
       </c>
       <c r="AM25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AN25" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AO25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="2:41" x14ac:dyDescent="0.3">
@@ -4993,10 +4993,10 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL26" s="28">
         <v>10</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="27" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL27" s="28">
         <v>20</v>
@@ -5032,7 +5032,7 @@
     </row>
     <row r="28" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AL28" s="28">
         <v>30</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="30" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AL30" s="28">
         <v>50</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL31" s="12">
         <v>35</v>
@@ -5109,10 +5109,10 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AL32" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM32" s="16">
         <f>IF(AL31&gt;=35,17*AL31-330,7*AL31+15) * IF(AL31&gt;=25, 1 + (MIN(13,(AL31-18)/3.5) - 1) * (MIN(13,(AL31-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(AL31-18)/3.5)  - 1),1)</f>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -13950,7 +13950,7 @@
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G114">
         <v>393220.33898305101</v>
@@ -15241,7 +15241,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -15255,43 +15255,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M3" t="s">
+        <v>389</v>
+      </c>
+      <c r="N3" t="s">
+        <v>390</v>
+      </c>
+      <c r="O3" t="s">
+        <v>388</v>
+      </c>
+      <c r="P3" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q3" t="s">
         <v>386</v>
       </c>
-      <c r="K3" t="s">
+      <c r="R3" t="s">
+        <v>394</v>
+      </c>
+      <c r="S3" t="s">
+        <v>395</v>
+      </c>
+      <c r="T3" t="s">
         <v>387</v>
       </c>
-      <c r="L3" t="s">
-        <v>388</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="U3" t="s">
         <v>392</v>
       </c>
-      <c r="N3" t="s">
+      <c r="V3" t="s">
         <v>393</v>
-      </c>
-      <c r="O3" t="s">
-        <v>391</v>
-      </c>
-      <c r="P3" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>389</v>
-      </c>
-      <c r="R3" t="s">
-        <v>397</v>
-      </c>
-      <c r="S3" t="s">
-        <v>398</v>
-      </c>
-      <c r="T3" t="s">
-        <v>390</v>
-      </c>
-      <c r="U3" t="s">
-        <v>395</v>
-      </c>
-      <c r="V3" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -16104,13 +16104,13 @@
         <v>55000</v>
       </c>
       <c r="H24" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I24" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J24" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.3">
@@ -16122,16 +16122,16 @@
         <v>60000</v>
       </c>
       <c r="I25" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K25" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M25" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O25" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.3">
@@ -16143,7 +16143,7 @@
         <v>65000</v>
       </c>
       <c r="J26" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K26" t="str">
         <f>I25&amp;K25&amp;J26</f>
@@ -16167,7 +16167,7 @@
         <v>70000</v>
       </c>
       <c r="J27" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K27" t="str">
         <f>I25&amp;K25&amp;J27</f>
@@ -16191,7 +16191,7 @@
         <v>75000</v>
       </c>
       <c r="J28" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K28" t="str">
         <f>I25&amp;K25&amp;J28</f>
@@ -16215,7 +16215,7 @@
         <v>80000</v>
       </c>
       <c r="J29" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K29" t="str">
         <f>I25&amp;K25&amp;J29</f>
@@ -16239,7 +16239,7 @@
         <v>85000</v>
       </c>
       <c r="J30" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K30" t="str">
         <f>I25&amp;K25&amp;J30</f>
@@ -16263,16 +16263,16 @@
         <v>90000</v>
       </c>
       <c r="I31" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K31" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M31" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O31" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.3">
@@ -16284,7 +16284,7 @@
         <v>95000</v>
       </c>
       <c r="J32" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K32" t="str">
         <f>I31&amp;K31&amp;J32</f>
@@ -16308,7 +16308,7 @@
         <v>100000</v>
       </c>
       <c r="J33" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K33" t="str">
         <f>I31&amp;K31&amp;J33</f>
@@ -16332,7 +16332,7 @@
         <v>105000</v>
       </c>
       <c r="J34" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K34" t="str">
         <f>I31&amp;K31&amp;J34</f>
@@ -16356,7 +16356,7 @@
         <v>110000</v>
       </c>
       <c r="J35" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K35" t="str">
         <f>I31&amp;K31&amp;J35</f>
@@ -16380,7 +16380,7 @@
         <v>115000</v>
       </c>
       <c r="J36" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K36" t="str">
         <f>I31&amp;K31&amp;J36</f>
@@ -16404,16 +16404,16 @@
         <v>120000</v>
       </c>
       <c r="I37" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K37" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M37" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O37" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.3">
@@ -16425,7 +16425,7 @@
         <v>125000</v>
       </c>
       <c r="J38" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K38" t="str">
         <f>I37&amp;K37&amp;J38</f>
@@ -16449,7 +16449,7 @@
         <v>130000</v>
       </c>
       <c r="J39" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K39" t="str">
         <f>I37&amp;K37&amp;J39</f>
@@ -16473,7 +16473,7 @@
         <v>135000</v>
       </c>
       <c r="J40" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K40" t="str">
         <f>I37&amp;K37&amp;J40</f>
@@ -16497,7 +16497,7 @@
         <v>140000</v>
       </c>
       <c r="J41" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K41" t="str">
         <f>I37&amp;K37&amp;J41</f>
@@ -16521,7 +16521,7 @@
         <v>145000</v>
       </c>
       <c r="J42" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K42" t="str">
         <f>I37&amp;K37&amp;J42</f>
@@ -16545,16 +16545,16 @@
         <v>150000</v>
       </c>
       <c r="I43" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K43" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M43" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O43" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.3">
@@ -16566,7 +16566,7 @@
         <v>155000</v>
       </c>
       <c r="J44" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K44" t="str">
         <f>I43&amp;K43&amp;J44</f>
@@ -16590,7 +16590,7 @@
         <v>160000</v>
       </c>
       <c r="J45" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K45" t="str">
         <f>I43&amp;K43&amp;J45</f>
@@ -16614,7 +16614,7 @@
         <v>165000</v>
       </c>
       <c r="J46" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K46" t="str">
         <f>I43&amp;K43&amp;J46</f>
@@ -16638,7 +16638,7 @@
         <v>170000</v>
       </c>
       <c r="J47" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K47" t="str">
         <f>I43&amp;K43&amp;J47</f>
@@ -16662,7 +16662,7 @@
         <v>175000</v>
       </c>
       <c r="J48" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K48" t="str">
         <f>I43&amp;K43&amp;J48</f>
@@ -16686,16 +16686,16 @@
         <v>180000</v>
       </c>
       <c r="I49" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="K49" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M49" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O49" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.3">
@@ -16707,7 +16707,7 @@
         <v>185000</v>
       </c>
       <c r="J50" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K50" t="str">
         <f>I49&amp;K49&amp;J50</f>
@@ -16731,7 +16731,7 @@
         <v>190000</v>
       </c>
       <c r="J51" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K51" t="str">
         <f>I49&amp;K49&amp;J51</f>
@@ -16755,7 +16755,7 @@
         <v>195000</v>
       </c>
       <c r="J52" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K52" t="str">
         <f>I49&amp;K49&amp;J52</f>
@@ -16779,7 +16779,7 @@
         <v>200000</v>
       </c>
       <c r="J53" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K53" t="str">
         <f>I49&amp;K49&amp;J53</f>
@@ -16803,7 +16803,7 @@
         <v>205000</v>
       </c>
       <c r="J54" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K54" t="str">
         <f>I49&amp;K49&amp;J54</f>
@@ -16827,16 +16827,16 @@
         <v>210000</v>
       </c>
       <c r="I55" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K55" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M55" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="O55" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.3">
@@ -16848,7 +16848,7 @@
         <v>215000</v>
       </c>
       <c r="J56" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K56" t="str">
         <f>I55&amp;K55&amp;J56</f>
@@ -16872,7 +16872,7 @@
         <v>220000</v>
       </c>
       <c r="J57" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K57" t="str">
         <f>I55&amp;K55&amp;J57</f>
@@ -16896,7 +16896,7 @@
         <v>225000</v>
       </c>
       <c r="J58" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K58" t="str">
         <f>I55&amp;K55&amp;J58</f>
@@ -16920,7 +16920,7 @@
         <v>250000</v>
       </c>
       <c r="J59" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K59" t="str">
         <f>I55&amp;K55&amp;J59</f>
@@ -16944,7 +16944,7 @@
         <v>275000</v>
       </c>
       <c r="J60" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K60" t="str">
         <f>I55&amp;K55&amp;J60</f>
@@ -17429,12 +17429,12 @@
   <sheetData>
     <row r="1" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C1" s="29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
@@ -17536,7 +17536,7 @@
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
@@ -18267,7 +18267,7 @@
     <row r="25" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C25" s="3"/>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.3">
@@ -18278,12 +18278,12 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.3">
@@ -18293,17 +18293,17 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
@@ -18354,42 +18354,42 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
       </c>
       <c r="E1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H1" t="s">
         <v>187</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>188</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>189</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>190</v>
-      </c>
-      <c r="L1" t="s">
-        <v>191</v>
       </c>
       <c r="M1" t="s">
         <v>165</v>
       </c>
       <c r="O1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -18398,25 +18398,25 @@
         <v>112</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>12</v>
@@ -18425,30 +18425,30 @@
         <v>152</v>
       </c>
       <c r="O2" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="P2" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>174</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>175</v>
       </c>
       <c r="R2" s="11" t="s">
         <v>154</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -18504,7 +18504,7 @@
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" s="3">
         <v>18</v>
@@ -18560,7 +18560,7 @@
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D5" s="3">
         <v>21</v>
@@ -18619,7 +18619,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3">
         <v>28</v>
@@ -18737,7 +18737,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D8" s="3">
         <v>31</v>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="3">
         <v>33</v>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="12">
         <v>10</v>
@@ -18926,14 +18926,14 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18949,7 +18949,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18985,10 +18985,10 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D15" s="12">
         <v>10</v>
@@ -19056,10 +19056,10 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" t="s">
         <v>194</v>
-      </c>
-      <c r="C17" t="s">
-        <v>195</v>
       </c>
       <c r="D17">
         <v>20</v>
@@ -19113,7 +19113,7 @@
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" s="12">
         <v>35</v>
@@ -19188,10 +19188,10 @@
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -19218,13 +19218,13 @@
         <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
@@ -19235,12 +19235,12 @@
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
@@ -19250,27 +19250,27 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -19309,10 +19309,10 @@
         <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -19376,41 +19376,41 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J15" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -19446,7 +19446,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -19561,7 +19561,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -19608,10 +19608,10 @@
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" s="42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -19651,7 +19651,7 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>82</v>
@@ -19793,28 +19793,28 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D12" t="s">
-        <v>315</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>319</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -19932,7 +19932,7 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>166</v>
+        <v>524</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">
@@ -19947,7 +19947,7 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
@@ -19957,12 +19957,12 @@
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -19999,13 +19999,13 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F1" t="s">
         <v>43</v>
@@ -20017,7 +20017,7 @@
         <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -20025,7 +20025,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>14</v>
@@ -20034,37 +20034,37 @@
         <v>36</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>213</v>
-      </c>
       <c r="H2" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>211</v>
-      </c>
       <c r="J2" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K2" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>221</v>
-      </c>
       <c r="N2" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="O2" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="P2" s="26" t="s">
         <v>204</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>205</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>154</v>
@@ -20072,10 +20072,10 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D3">
         <v>21</v>
@@ -20114,7 +20114,7 @@
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" s="12">
         <v>35</v>
@@ -20169,10 +20169,10 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="3"/>
@@ -20199,22 +20199,22 @@
         <v>158</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>216</v>
       </c>
       <c r="G8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="N8" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" s="3">
         <v>5</v>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
@@ -20267,7 +20267,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -20280,10 +20280,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>14</v>
@@ -20292,32 +20292,32 @@
         <v>36</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>88</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E13" s="21">
         <v>10</v>
@@ -20349,7 +20349,7 @@
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="D14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E14" s="21">
         <v>0</v>
@@ -20374,10 +20374,10 @@
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E15" s="22">
         <v>1</v>
@@ -20406,7 +20406,7 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E16" s="22">
         <v>1</v>
@@ -20431,7 +20431,7 @@
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E17" s="22">
         <v>1</v>
@@ -20457,7 +20457,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E18" s="22">
         <v>1</v>
@@ -20482,16 +20482,16 @@
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="D20" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.3">
@@ -20499,52 +20499,52 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F22" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="G22" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="H22" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="I22" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="J22" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="J22" s="20" t="s">
+      <c r="K22" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="K22" s="25" t="s">
+      <c r="L22" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="L22" s="25" t="s">
+      <c r="N22" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="P22" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q22" s="26" t="s">
         <v>244</v>
-      </c>
-      <c r="N22" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="P22" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q22" s="26" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E23" s="21">
         <v>1</v>
@@ -20589,7 +20589,7 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E24" s="22">
         <v>0</v>
@@ -20632,7 +20632,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="1"/>
       <c r="D25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E25" s="22">
         <v>0</v>
@@ -20671,7 +20671,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="1"/>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E26" s="22">
         <v>0</v>
@@ -20709,10 +20709,10 @@
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
@@ -20720,14 +20720,14 @@
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="N27" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="24"/>
       <c r="D28" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -20738,7 +20738,7 @@
     <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="D29" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
@@ -20746,13 +20746,13 @@
         <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
@@ -20763,7 +20763,7 @@
         <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -20791,39 +20791,39 @@
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E2" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>240</v>
-      </c>
       <c r="G2" s="33" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I2" s="33" t="s">
         <v>94</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D3" s="34">
         <v>1.5</v>
@@ -20860,7 +20860,7 @@
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D4" s="34">
         <v>4</v>
@@ -20897,7 +20897,7 @@
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D5" s="34">
         <v>4</v>
@@ -20934,7 +20934,7 @@
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D6" s="36">
         <v>1</v>
@@ -20971,53 +20971,53 @@
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I11" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I12" s="33" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L12" s="33" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
       </c>
       <c r="I13" s="46" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J13" s="45">
         <v>20</v>
@@ -21036,19 +21036,19 @@
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E14" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="F14" s="33" t="s">
-        <v>412</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J14" s="45">
         <v>0</v>
@@ -21067,13 +21067,13 @@
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
       </c>
       <c r="I15" s="46" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J15" s="45">
         <v>0</v>
@@ -21088,13 +21088,13 @@
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J16" s="45">
         <v>0</v>
@@ -21109,13 +21109,13 @@
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E17" s="40">
         <v>3</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J17" s="45">
         <v>0</v>
@@ -21130,16 +21130,16 @@
     </row>
     <row r="18" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E18" s="40">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J18" s="45">
         <v>0</v>
@@ -21154,16 +21154,16 @@
     </row>
     <row r="19" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E19" s="40">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I19" s="46" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J19" s="45">
         <v>0</v>
@@ -21178,16 +21178,16 @@
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E20" s="40">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J20" s="45">
         <v>0</v>
@@ -21202,16 +21202,16 @@
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E21" s="40">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J21" s="45">
         <v>0</v>
@@ -21226,13 +21226,13 @@
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E22" s="40">
         <v>8</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J22" s="45">
         <v>0</v>
@@ -21247,7 +21247,7 @@
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E23" s="40">
         <v>9</v>
@@ -21255,18 +21255,18 @@
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I25" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J25" s="33" t="s">
         <v>14</v>
@@ -21275,19 +21275,19 @@
         <v>36</v>
       </c>
       <c r="L25" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M25" s="38" t="s">
         <v>88</v>
       </c>
       <c r="N25" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O25" s="38" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P25" s="39" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="4:16" x14ac:dyDescent="0.3">
@@ -21295,7 +21295,7 @@
         <v>87</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J26" s="45">
         <v>20</v>
@@ -21323,10 +21323,10 @@
     </row>
     <row r="27" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H27" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I27" s="46" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J27" s="45">
         <v>0</v>
@@ -21354,7 +21354,7 @@
     </row>
     <row r="28" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I28" s="46" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J28" s="45">
         <v>0</v>
@@ -21378,7 +21378,7 @@
     </row>
     <row r="29" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I29" s="46" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J29" s="45">
         <v>0</v>
@@ -21402,7 +21402,7 @@
     </row>
     <row r="30" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I30" s="46" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J30" s="45">
         <v>0</v>
@@ -21426,7 +21426,7 @@
     </row>
     <row r="31" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I31" s="46" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J31" s="45">
         <v>0</v>
@@ -21450,7 +21450,7 @@
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I32" s="46" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J32" s="45">
         <v>0</v>
@@ -21505,74 +21505,74 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="N1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C2" s="33" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>451</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="H2" s="33" t="s">
         <v>454</v>
       </c>
-      <c r="G2" s="33" t="s">
-        <v>455</v>
-      </c>
-      <c r="H2" s="33" t="s">
+      <c r="I2" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q2" s="35" t="s">
         <v>457</v>
       </c>
-      <c r="I2" s="33" t="s">
-        <v>453</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>456</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>517</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>452</v>
-      </c>
-      <c r="N2" s="35" t="s">
+      <c r="R2" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="S2" s="35" t="s">
         <v>461</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>463</v>
       </c>
-      <c r="Q2" s="35" t="s">
-        <v>460</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>465</v>
-      </c>
-      <c r="S2" s="35" t="s">
+      <c r="U2" s="35" t="s">
         <v>464</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="U2" s="35" t="s">
-        <v>467</v>
       </c>
       <c r="V2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="W2" s="35" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
@@ -21647,7 +21647,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -21722,7 +21722,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21797,7 +21797,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21872,7 +21872,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
@@ -21947,7 +21947,7 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C8" s="36">
         <v>1</v>
@@ -22022,13 +22022,13 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -22038,7 +22038,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -22047,32 +22047,32 @@
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
@@ -22080,244 +22080,244 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="D20" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>412</v>
-      </c>
       <c r="J20" s="33" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="K21" s="40">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="K22" s="40">
         <v>1.5</v>
       </c>
       <c r="L22" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K23" s="40">
         <v>2</v>
       </c>
       <c r="L23" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C24" s="40">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J24" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="L24" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C25" s="40">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J25" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C26" s="40">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J26" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="L26" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C27" s="40">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J27" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K27" s="40">
         <v>9</v>
       </c>
       <c r="L27" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H28" s="40">
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="K28" s="40">
         <v>13</v>
       </c>
       <c r="L28" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H29" s="40">
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K29" s="40">
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H30" s="40">
         <v>3</v>
       </c>
       <c r="J30" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="K30" s="40">
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G31" s="42" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H31" s="40">
         <v>4</v>
@@ -22325,36 +22325,36 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D32" s="44"/>
       <c r="G32" s="42" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H32" s="40">
         <v>5</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K33" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G34" s="24" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="7:11" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BB6B61-58B5-4E4A-85FD-C901D42A8B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D29C72-1E84-4CF8-8F62-45C2B617F978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2080,10 +2080,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大容量机枪（弹容&gt;100）的弹容量种族优势可额外换2-4层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>超前武器需要减少一层加权，可减为负数。具体可查看下方的解锁等级。纵向联弹由于不衰减，当有霰弹值时添加负层级作为平衡，负层级计算方式为-(霰弹值-1)/2。横向联弹有衰减，无需负层级。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2097,6 +2093,10 @@
   </si>
   <si>
     <t>种类系数：有主动战技/特效的可为1.5，效果极其强力时为2。无购买途径或非购买途径早于购买途径的为0.5，逻辑同上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大容量机枪（弹容&gt;100）的弹容量种族优势可额外换2-3层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>269</v>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AL32" s="2" t="s">
         <v>378</v>
@@ -19804,12 +19804,12 @@
         <v>313</v>
       </c>
       <c r="D12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -19932,7 +19932,7 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D29C72-1E84-4CF8-8F62-45C2B617F978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8BC7CA-EE10-4D90-B5E0-6B6D22837B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2072,10 +2072,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>喷火/次级穿刺子弹的穿刺系数为1.5，狙击枪穿刺系数为1.5，普通穿刺为2，非穿刺为1（其他拥有穿刺效果根据单体段数数量填入穿刺系数，段数较多时可填3或更高的穿刺系数）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武器类型解锁等级:10级:特效刀/次级穿刺枪/普通霰弹枪;20级:慢射速穿刺枪;30级:属性刀/高射速穿刺枪/慢射速属性枪;35级:穿刺霰弹枪;40级:普通属性枪/慢射速穿刺属性枪;45级:高射速穿刺属性枪。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2097,6 +2093,10 @@
   </si>
   <si>
     <t>大容量机枪（弹容&gt;100）的弹容量种族优势可额外换2-3层级，对应种族价格系数，可叠加武器价格层级。穿刺枪的种族优势为群攻，散弹的种族优势为吃拐率，不反映在面板上，所以无额外加权层级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喷火/次级穿刺子弹/高弹速穿刺狙击枪的穿刺系数为1.5，普通穿刺为2，非穿刺为1（其他拥有穿刺效果根据单体段数数量填入穿刺系数，段数较多时可填3或更高的穿刺系数）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3282,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3">
         <v>120</v>
@@ -3309,50 +3309,50 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="Q3">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1914.1695205479452</v>
+        <v>2020.6549657534247</v>
       </c>
       <c r="S3">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>1914.2374083361844</v>
+        <v>2032.7457162809235</v>
       </c>
       <c r="V3">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>1914.0679719372729</v>
+        <v>2031.4614237768487</v>
       </c>
       <c r="W3">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>8384.0625</v>
+        <v>8850.46875</v>
       </c>
       <c r="X3">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
-        <v>8230.4</v>
+        <v>8130.4000000000005</v>
       </c>
       <c r="Y3">
         <f>表2_5[[#This Row],[平衡周期伤害]]*1.25^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>8230.4</v>
+        <v>8130.4000000000005</v>
       </c>
       <c r="Z3">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1232.8767123287671</v>
+        <v>1335.6164383561643</v>
       </c>
       <c r="AA3">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1232.7781579905241</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>1346.0995006284018</v>
       </c>
       <c r="AB3">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>681.29280821917803</v>
+        <v>685.03852739726028</v>
       </c>
       <c r="AC3">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>681.28981394674884</v>
+        <v>685.36192314844709</v>
       </c>
       <c r="AD3">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3368,11 +3368,11 @@
       </c>
       <c r="AG3">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1882.5504347793969</v>
+        <v>1842.9896488815355</v>
       </c>
       <c r="AH3">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>279.46875</v>
+        <v>295.015625</v>
       </c>
       <c r="AI3">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -3384,23 +3384,23 @@
       </c>
       <c r="AK3">
         <f>0.9+(1.1-0.9)*表2_5[[#This Row],[冲击力]]/(表2_5[[#This Row],[冲击力]]+50)</f>
-        <v>0.98888888888888893</v>
+        <v>0.97500000000000009</v>
       </c>
       <c r="AL3">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>0.99719956436010304</v>
+        <v>0.98672392904600204</v>
       </c>
       <c r="AM3">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1914.1695205479452</v>
+        <v>2020.6549657534247</v>
       </c>
       <c r="AN3">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>2328.90625</v>
+        <v>2458.4635416666665</v>
       </c>
       <c r="AO3">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>1.0000885216206508</v>
+        <v>1.0006322012759106</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.3">
@@ -3414,7 +3414,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="3">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F4" s="3">
         <v>150</v>
@@ -3448,19 +3448,19 @@
       </c>
       <c r="Q4">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>4953.8888888888887</v>
+        <v>5052.9629629629626</v>
       </c>
       <c r="S4">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>4935.3835494073419</v>
+        <v>5012.9154416429456</v>
       </c>
       <c r="V4">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>4851.308428662649</v>
+        <v>4929.3345282010032</v>
       </c>
       <c r="W4">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>33438.75</v>
+        <v>34107.5</v>
       </c>
       <c r="X4">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
@@ -3472,19 +3472,19 @@
       </c>
       <c r="Z4">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2577.7777777777778</v>
+        <v>2666.6666666666665</v>
       </c>
       <c r="AA4">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>3020.4208312948876</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>3089.950982653791</v>
       </c>
       <c r="AB4">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2376.1111111111113</v>
+        <v>2386.2962962962961</v>
       </c>
       <c r="AC4">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>1830.8875973677614</v>
+        <v>1839.383545547212</v>
       </c>
       <c r="AD4">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3500,11 +3500,11 @@
       </c>
       <c r="AG4">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>5155.8706610160534</v>
+        <v>5140.6079276294104</v>
       </c>
       <c r="AH4">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>437.984375</v>
+        <v>446.34375</v>
       </c>
       <c r="AI4">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -3520,19 +3520,19 @@
       </c>
       <c r="AL4">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>0.98653212435985971</v>
+        <v>0.98327102157776669</v>
       </c>
       <c r="AM4">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>4953.8888888888887</v>
+        <v>5052.9629629629626</v>
       </c>
       <c r="AN4">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>5573.125</v>
+        <v>5684.583333333333</v>
       </c>
       <c r="AO4">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>1.005756248149515</v>
+        <v>1.0053859295854997</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.3">
@@ -3587,11 +3587,11 @@
       </c>
       <c r="S5">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>3564.3431278887515</v>
+        <v>4091.3816335602987</v>
       </c>
       <c r="V5">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>3264.9952462733104</v>
+        <v>3700.1462170438035</v>
       </c>
       <c r="W5">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -3610,8 +3610,8 @@
         <v>2252.3461939520334</v>
       </c>
       <c r="AA5">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>2504.2768273593201</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>2916.1863740541503</v>
       </c>
       <c r="AB5">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AC5">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>760.71841891399015</v>
+        <v>783.95984298965334</v>
       </c>
       <c r="AD5">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AO5">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.99244001599782883</v>
+        <v>1.005213748461754</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.3">
@@ -3682,7 +3682,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="12">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F6" s="12">
         <v>90</v>
@@ -3716,19 +3716,19 @@
       </c>
       <c r="Q6" s="17">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>7996.0978035281905</v>
+        <v>8159.4099504208452</v>
       </c>
       <c r="S6" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>8015.59672237004</v>
+        <v>8110.1198780917202</v>
       </c>
       <c r="V6">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>7990.9464303756549</v>
+        <v>8091.3454019548099</v>
       </c>
       <c r="W6">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>42459.279336734689</v>
+        <v>43326.466836734689</v>
       </c>
       <c r="X6">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
@@ -3740,19 +3740,19 @@
       </c>
       <c r="Z6">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>3813.5593220338983</v>
+        <v>3954.8022598870057</v>
       </c>
       <c r="AA6">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>3789.2889126141008</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>3875.5988913635333</v>
       </c>
       <c r="AB6">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>4182.5384814942927</v>
+        <v>4204.6076905338405</v>
       </c>
       <c r="AC6">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>4201.6575177615541</v>
+        <v>4215.7465105912761</v>
       </c>
       <c r="AD6">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -3768,11 +3768,11 @@
       </c>
       <c r="AG6">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>6554.6817081442805</v>
+        <v>6533.639561076945</v>
       </c>
       <c r="AH6">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>849.18558673469386</v>
+        <v>866.52933673469386</v>
       </c>
       <c r="AI6">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -3788,19 +3788,19 @@
       </c>
       <c r="AL6">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>0.97946857421484745</v>
+        <v>0.97600421230165579</v>
       </c>
       <c r="AM6">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>7996.0978035281905</v>
+        <v>8159.4099504208452</v>
       </c>
       <c r="AN6">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>9435.3954081632637</v>
+        <v>9628.1037414965976</v>
       </c>
       <c r="AO6">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>1.0030847775303164</v>
+        <v>1.0023203157453116</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.3">
@@ -3818,7 +3818,7 @@
         <v>1300</v>
       </c>
       <c r="F7" s="12">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="G7" s="12">
         <v>9</v>
@@ -3849,15 +3849,15 @@
       </c>
       <c r="Q7" s="17">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>6956.9867189952902</v>
+        <v>7413.1825694212112</v>
       </c>
       <c r="S7" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>6950.0297894248506</v>
+        <v>7546.0677228024406</v>
       </c>
       <c r="V7">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>6852.3512610772741</v>
+        <v>7435.1735866335648</v>
       </c>
       <c r="W7">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -3873,27 +3873,27 @@
       </c>
       <c r="Z7">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>5483.0769230769229</v>
+        <v>5842.622950819672</v>
       </c>
       <c r="AA7">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>3987.6758367719603</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>4497.3035285639362</v>
       </c>
       <c r="AB7">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1473.9097959183673</v>
+        <v>1570.5596186015389</v>
       </c>
       <c r="AC7">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>2864.6754243053138</v>
+        <v>2937.8700580696286</v>
       </c>
       <c r="AD7">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1.3846153846153846</v>
+        <v>1.4754098360655739</v>
       </c>
       <c r="AE7">
         <f>1000*(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))</f>
-        <v>2.7692307692307692</v>
+        <v>2.9508196721311477</v>
       </c>
       <c r="AF7">
         <f>MAX(IF(表2_5[[#This Row],[吃拐率]]&gt;(0.0008*表2_5[[#This Row],[限制等级]]^2+10+(表2_5[[#This Row],[霰弹值]]+表2_5[[#This Row],[穿刺系数]]*2.5-3.5) * 0.2+表2_5[[#This Row],[重量]]*表2_5[[#This Row],[重量]]/50)*1.1^表2_5[[#This Row],[额外加权层数]],(6/(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[霰弹值]])) * (0.0008*表2_5[[#This Row],[限制等级]]^2+10+(表2_5[[#This Row],[霰弹值]]+表2_5[[#This Row],[穿刺系数]]*2.5-3.5) * 0.2+表2_5[[#This Row],[重量]]*表2_5[[#This Row],[重量]]/50)*1.1^表2_5[[#This Row],[额外加权层数]]/表2_5[[#This Row],[吃拐率]] -6/(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[霰弹值]])+1,1),0.1)</f>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AG7">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>6905.9216366212231</v>
+        <v>7004.0280678948675</v>
       </c>
       <c r="AH7">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
@@ -3925,15 +3925,15 @@
       </c>
       <c r="AM7">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>6956.9867189952902</v>
+        <v>7413.1825694212112</v>
       </c>
       <c r="AN7">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>7177.8434402332359</v>
+        <v>7729.9852433281003</v>
       </c>
       <c r="AO7">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>1.0142547462361438</v>
+        <v>1.0149148012318412</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.3">
@@ -3951,7 +3951,7 @@
         <v>900</v>
       </c>
       <c r="F8" s="12">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G8" s="12">
         <v>10</v>
@@ -3982,15 +3982,15 @@
       </c>
       <c r="Q8" s="17">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>10152.784555851327</v>
+        <v>11675.702239229027</v>
       </c>
       <c r="S8" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>10608.682012142001</v>
+        <v>11427.579493597848</v>
       </c>
       <c r="V8">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>10849.242444199579</v>
+        <v>11938.57755418683</v>
       </c>
       <c r="W8">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -4006,27 +4006,27 @@
       </c>
       <c r="Z8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>6666.666666666667</v>
+        <v>7666.666666666667</v>
       </c>
       <c r="AA8">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>5153.2323332905817</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>6077.7069841416824</v>
       </c>
       <c r="AB8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>3486.1178891846585</v>
+        <v>4009.0355725623576</v>
       </c>
       <c r="AC8">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>5696.0101109089965</v>
+        <v>5860.8705700451474</v>
       </c>
       <c r="AD8">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>4.8309178743961354</v>
+        <v>5.5555555555555554</v>
       </c>
       <c r="AE8">
         <f>1000*(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))</f>
-        <v>4.8309178743961354</v>
+        <v>5.5555555555555554</v>
       </c>
       <c r="AF8">
         <f>MAX(IF(表2_5[[#This Row],[吃拐率]]&gt;(0.0008*表2_5[[#This Row],[限制等级]]^2+10+(表2_5[[#This Row],[霰弹值]]+表2_5[[#This Row],[穿刺系数]]*2.5-3.5) * 0.2+表2_5[[#This Row],[重量]]*表2_5[[#This Row],[重量]]/50)*1.1^表2_5[[#This Row],[额外加权层数]],(6/(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[霰弹值]])) * (0.0008*表2_5[[#This Row],[限制等级]]^2+10+(表2_5[[#This Row],[霰弹值]]+表2_5[[#This Row],[穿刺系数]]*2.5-3.5) * 0.2+表2_5[[#This Row],[重量]]*表2_5[[#This Row],[重量]]/50)*1.1^表2_5[[#This Row],[额外加权层数]]/表2_5[[#This Row],[吃拐率]] -6/(表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[霰弹值]])+1,1),0.1)</f>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AG8">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>9621.340695062765</v>
+        <v>9983.7464921642149</v>
       </c>
       <c r="AH8">
         <f>(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
@@ -4058,15 +4058,15 @@
       </c>
       <c r="AM8">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*1.5+30+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>10152.784555851325</v>
+        <v>11675.702239229026</v>
       </c>
       <c r="AN8">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>16166.356946624806</v>
+        <v>21016.264030612248</v>
       </c>
       <c r="AO8">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.97782698346959784</v>
+        <v>0.95719774334340391</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
@@ -4089,7 +4089,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F10" s="31">
         <v>70</v>
@@ -4124,21 +4124,21 @@
       <c r="P10" s="27"/>
       <c r="Q10">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2175.9231596558316</v>
+        <v>2228.5791108986614</v>
       </c>
       <c r="S10">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>2177.2504447235419</v>
+        <v>2231.1009556651052</v>
       </c>
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
       <c r="V10">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>2221.803925305222</v>
+        <v>2276.6301183183987</v>
       </c>
       <c r="W10">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>11380.078125</v>
+        <v>11655.46875</v>
       </c>
       <c r="X10">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
@@ -4150,19 +4150,19 @@
       </c>
       <c r="Z10">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>812.61950286806882</v>
+        <v>860.42065009560224</v>
       </c>
       <c r="AA10">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1272.9404441211784</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>1322.1865617882506</v>
       </c>
       <c r="AB10">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1363.303656787763</v>
+        <v>1368.1584608030594</v>
       </c>
       <c r="AC10">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>948.86348118404374</v>
+        <v>954.44355653014827</v>
       </c>
       <c r="AD10">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4178,11 +4178,11 @@
       </c>
       <c r="AG10">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>2115.1844642179994</v>
+        <v>2108.3018369545916</v>
       </c>
       <c r="AH10" s="27">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>227.6015625</v>
+        <v>233.109375</v>
       </c>
       <c r="AI10">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -4198,19 +4198,19 @@
       </c>
       <c r="AL10">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>0.9996607731708953</v>
+        <v>0.99602289273285605</v>
       </c>
       <c r="AM10">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2175.9231596558316</v>
+        <v>2228.5791108986614</v>
       </c>
       <c r="AN10">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>3251.4508928571427</v>
+        <v>3330.1339285714284</v>
       </c>
       <c r="AO10">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.97994715911956121</v>
+        <v>0.98000151087919229</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.3">
@@ -4227,7 +4227,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="27">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="F11" s="27">
         <v>300</v>
@@ -4262,21 +4262,21 @@
       <c r="P11" s="27"/>
       <c r="Q11">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>3706.590909090909</v>
+        <v>3919.659090909091</v>
       </c>
       <c r="S11">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>3731.7617881206602</v>
+        <v>3933.7139299260343</v>
       </c>
       <c r="T11" s="27"/>
       <c r="U11" s="27"/>
       <c r="V11">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>3580.7831490712351</v>
+        <v>3776.03113711893</v>
       </c>
       <c r="W11">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>12231.75</v>
+        <v>12934.875</v>
       </c>
       <c r="X11">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
@@ -4288,19 +4288,19 @@
       </c>
       <c r="Z11">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2618.181818181818</v>
+        <v>2800</v>
       </c>
       <c r="AA11">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1978.8149744772097</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>2145.5382311354228</v>
       </c>
       <c r="AB11">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1088.409090909091</v>
+        <v>1119.659090909091</v>
       </c>
       <c r="AC11">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>1601.9681745940256</v>
+        <v>1630.4929059835074</v>
       </c>
       <c r="AD11">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4316,11 +4316,11 @@
       </c>
       <c r="AG11">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>3254.3598737779162</v>
+        <v>3241.1440268611004</v>
       </c>
       <c r="AH11" s="27">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>1039.3125</v>
+        <v>1097.90625</v>
       </c>
       <c r="AI11">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -4336,19 +4336,19 @@
       </c>
       <c r="AL11">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>1.0627371836726873</v>
+        <v>1.0579759745327066</v>
       </c>
       <c r="AM11">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>3706.590909090909</v>
+        <v>3919.659090909091</v>
       </c>
       <c r="AN11">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>6795.416666666667</v>
+        <v>7186.041666666667</v>
       </c>
       <c r="AO11">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.9474214369427143</v>
+        <v>0.94705351804608218</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.3">
@@ -4404,13 +4404,13 @@
       </c>
       <c r="S12">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>1960.568781560713</v>
+        <v>2041.3034612513084</v>
       </c>
       <c r="T12" s="27"/>
       <c r="U12" s="27"/>
       <c r="V12">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>2010.8114808268531</v>
+        <v>2084.4948563655889</v>
       </c>
       <c r="W12">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -4429,8 +4429,8 @@
         <v>749.3917274939173</v>
       </c>
       <c r="AA12">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1239.6327646418943</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>1308.3323530734312</v>
       </c>
       <c r="AB12">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AC12">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>771.17871618495883</v>
+        <v>776.16250329215745</v>
       </c>
       <c r="AD12">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AO12">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.97501371971206363</v>
+        <v>0.9792796825655945</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.3">
@@ -4541,11 +4541,11 @@
       </c>
       <c r="S13" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>5861.0382911394163</v>
+        <v>5924.5007565598362</v>
       </c>
       <c r="V13">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>5983.8239946457634</v>
+        <v>6041.6902686835838</v>
       </c>
       <c r="W13">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -4564,8 +4564,8 @@
         <v>1816.4435946462715</v>
       </c>
       <c r="AA13">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>2441.2010784463823</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>2489.0361493029354</v>
       </c>
       <c r="AB13">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AC13">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>3542.6229161993806</v>
+        <v>3552.6541193806479</v>
       </c>
       <c r="AD13">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AO13">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.97948039520944907</v>
+        <v>0.98060319100911442</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.3">
@@ -4674,11 +4674,11 @@
       </c>
       <c r="S14" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>5738.230804796859</v>
+        <v>5842.8543900366094</v>
       </c>
       <c r="V14">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>5739.2477640888637</v>
+        <v>5834.2456624139559</v>
       </c>
       <c r="W14">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
@@ -4697,8 +4697,8 @@
         <v>1693.9890710382513</v>
       </c>
       <c r="AA14">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>2489.6938291494339</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>2567.7053483038144</v>
       </c>
       <c r="AB14">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="AC14">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>3249.5539349394298</v>
+        <v>3266.5403141101415</v>
       </c>
       <c r="AD14">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="AO14">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.99982280617011032</v>
+        <v>1.0014755511030524</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
@@ -4769,7 +4769,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="12">
-        <v>850</v>
+        <v>935</v>
       </c>
       <c r="F15" s="12">
         <v>200</v>
@@ -4803,19 +4803,19 @@
       </c>
       <c r="Q15" s="17">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2399.1629464285716</v>
+        <v>2602.6506696428573</v>
       </c>
       <c r="S15" s="17">
         <f>表2_5[[#This Row],[平衡dps]]*表2_5[[#This Row],[周期dps系数]]*表2_5[[#This Row],[吃拐系数]]*1.1^表2_5[[#This Row],[额外加权层数]]</f>
-        <v>2397.2788735560025</v>
+        <v>2602.6718973408651</v>
       </c>
       <c r="V15">
         <f>表2_5[[#This Row],[平衡裸伤dps]]+表2_5[[#This Row],[平衡增益dps]]</f>
-        <v>2636.2558710452458</v>
+        <v>2861.2992262827256</v>
       </c>
       <c r="W15">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)</f>
-        <v>6717.65625</v>
+        <v>7287.421875</v>
       </c>
       <c r="X15">
         <f xml:space="preserve"> (表2_5[[#This Row],[限制等级]]-1) * 1200*表2_5[[#This Row],[冲击力系数]]/(1.6^(表2_5[[#This Row],[伤害类型系数]]-1)*1.5^(表2_5[[#This Row],[双枪系数]]-1))+表2_5[[#This Row],[弹夹价格]]*5*(1+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(2+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]])</f>
@@ -4827,19 +4827,19 @@
       </c>
       <c r="Z15">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20)*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>1864.2857142857142</v>
+        <v>2046.4285714285713</v>
       </c>
       <c r="AA15">
-        <f>( ((表2_5[[#This Row],[限制等级]]*120.5))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*3/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>1498.7496369024429</v>
+        <f>( ((表2_5[[#This Row],[限制等级]]*120))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*6/表2_5[[#This Row],[伤害类型系数]])/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])+表2_5[[#This Row],[重量]]*66/表2_5[[#This Row],[伤害类型系数]] )/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
+        <v>1700.3081506481715</v>
       </c>
       <c r="AB15">
         <f>1000*(表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>534.87723214285711</v>
+        <v>556.22209821428567</v>
       </c>
       <c r="AC15">
         <f>(表2_5[[#This Row],[平衡裸伤dps]]/(1.5^(2-表2_5[[#This Row],[双枪系数]])+(40-10*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[子弹威力]]))*2*表2_5[[#This Row],[限制等级]]/256+1000*(表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*(26.5+表2_5[[#This Row],[限制等级]]*0.5)/(120*29+900*表2_5[[#This Row],[双枪系数]])/表2_5[[#This Row],[伤害类型系数]]</f>
-        <v>1137.5062341428027</v>
+        <v>1160.9910756345539</v>
       </c>
       <c r="AD15">
         <f>1000*表2_5[[#This Row],[弹容量]]/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
@@ -4855,11 +4855,11 @@
       </c>
       <c r="AG15">
         <f>( ((表2_5[[#This Row],[限制等级]]*200+表2_5[[#This Row],[重量]]*61))*表2_5[[#This Row],[冲击力系数]]*表2_5[[#This Row],[周期伤害系数]]/1.6^(表2_5[[#This Row],[伤害类型系数]]-1)+1000*(表2_5[[#This Row],[弹夹价格]]*5*(8+表2_5[[#This Row],[限制等级]])/(50*表2_5[[#This Row],[伤害类型系数]])+表2_5[[#This Row],[重量]]*660*(1+表2_5[[#This Row],[限制等级]])/(25*表2_5[[#This Row],[伤害类型系数]]))/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]]))/1.5^(表2_5[[#This Row],[双枪系数]]-1)</f>
-        <v>2432.0179857629705</v>
+        <v>2418.5541527194559</v>
       </c>
       <c r="AH15" s="27">
         <f>(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/表2_5[[#This Row],[霰弹值]])</f>
-        <v>1119.609375</v>
+        <v>1214.5703125</v>
       </c>
       <c r="AI15">
         <f>IF(表2_5[[#This Row],[限制等级]]&gt;=35,17*表2_5[[#This Row],[限制等级]]-330,7*表2_5[[#This Row],[限制等级]]+15) * IF(表2_5[[#This Row],[限制等级]]&gt;=25, 1 + (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5) - 1) * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(表2_5[[#This Row],[限制等级]]-18)/3.5)  - 1),1)</f>
@@ -4875,19 +4875,19 @@
       </c>
       <c r="AL15">
         <f>IF(表2_5[[#This Row],[周期伤害]] &lt;=表2_5[[#This Row],[加权周期伤害]]* 5,0.7+0.6/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]))),0.1+1.5/(1+EXP(-(表2_5[[#This Row],[加权周期伤害]]-表2_5[[#This Row],[周期伤害]])/(表2_5[[#This Row],[加权周期伤害]]*10))))</f>
-        <v>1.0638386982365695</v>
+        <v>1.0569077875685204</v>
       </c>
       <c r="AM15">
         <f>1000*(表2_5[[#This Row],[子弹威力]]+20+表2_5[[#This Row],[子弹威力]]*2*表2_5[[#This Row],[限制等级]]/256+表2_5[[#This Row],[伤害加成]]+表2_5[[#This Row],[剧毒]]/(表2_5[[#This Row],[霰弹值]]*3^(表2_5[[#This Row],[穿刺系数]]-1)))*表2_5[[#This Row],[穿刺系数]]*表2_5[[#This Row],[弹容量]]*(1+(表2_5[[#This Row],[霰弹值]]-1)*0.5)/(表2_5[[#This Row],[射击间隔]]*(表2_5[[#This Row],[弹容量]]-1)+900*表2_5[[#This Row],[双枪系数]])</f>
-        <v>2399.1629464285716</v>
+        <v>2602.6506696428573</v>
       </c>
       <c r="AN15">
         <f>1000*表2_5[[#This Row],[周期伤害]]/(表2_5[[#This Row],[射击间隔]]*表2_5[[#This Row],[弹容量]])</f>
-        <v>5598.046875</v>
+        <v>6072.8515625</v>
       </c>
       <c r="AO15">
         <f>IF(表2_5[[#This Row],[周期dps]]&lt;=表2_5[[#This Row],[平衡dps]] * 2,0.85+0.3365/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]))),0.37+1.68/(1+EXP(-(表2_5[[#This Row],[平衡dps]]-表2_5[[#This Row],[周期dps]])/(表2_5[[#This Row],[平衡dps]]*1.5))))</f>
-        <v>0.90934984721551648</v>
+        <v>0.90961192504222721</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.3">
@@ -4929,7 +4929,7 @@
         <v>275</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
@@ -5086,7 +5086,7 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AK31" s="2" t="s">
         <v>269</v>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AL32" s="2" t="s">
         <v>378</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -5129,7 +5129,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="W10:W15 W3:W8 AL3:AL15 X3:X15 Z3:Z15 AB3:AB15 AI3:AI15 AE3:AE15 V3:V15 AC3:AC15 AA3:AA15 AF3:AF15" calculatedColumn="1"/>
+    <ignoredError sqref="W10:W15 W3:W8 AL3:AL15 X3:X15 Z3:Z15 AB3:AB15 AI3:AI15 AE3:AE15 V3:V15 AC3:AC15 AF3:AF15 AA3:AA15" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="2">
     <tablePart r:id="rId2"/>
@@ -19804,12 +19804,12 @@
         <v>313</v>
       </c>
       <c r="D12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -19932,7 +19932,7 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8BC7CA-EE10-4D90-B5E0-6B6D22837B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF3B067-9A1D-45F4-8654-40627FCBDEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="524">
   <si>
     <t>非爆炸类枪械</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1063,10 +1063,6 @@
   </si>
   <si>
     <t>旧版hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只有免费获取途径的装备，或免费获取途径早于可购买时的装备，均填-1层。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3110,7 +3106,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D1" t="s">
         <v>46</v>
@@ -3125,33 +3121,33 @@
         <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M1" t="s">
         <v>42</v>
       </c>
       <c r="N1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O1" t="s">
         <v>165</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="V1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>50</v>
@@ -3181,13 +3177,13 @@
         <v>4</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>162</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>12</v>
@@ -3196,79 +3192,79 @@
         <v>220</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R2" s="11" t="s">
         <v>221</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>219</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="AA2" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="AB2" s="14" t="s">
+      <c r="AC2" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="AG2" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="AD2" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>376</v>
-      </c>
       <c r="AH2" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AI2" s="14" t="s">
         <v>168</v>
       </c>
       <c r="AJ2" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AK2" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AL2" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AM2" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AN2" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
@@ -3540,7 +3536,7 @@
         <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -3676,7 +3672,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D6" s="12">
         <v>30</v>
@@ -3809,7 +3805,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D7" s="12">
         <v>28</v>
@@ -3942,7 +3938,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D8" s="12">
         <v>35</v>
@@ -4356,7 +4352,7 @@
         <v>157</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>47</v>
@@ -4497,7 +4493,7 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D13" s="12">
         <v>30</v>
@@ -4630,7 +4626,7 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D14" s="12">
         <v>32</v>
@@ -4759,11 +4755,11 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D15" s="12">
         <v>15</v>
@@ -4917,40 +4913,40 @@
     <row r="18" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="2:41" x14ac:dyDescent="0.3">
@@ -4961,16 +4957,16 @@
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL24" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="2:41" x14ac:dyDescent="0.3">
@@ -4982,10 +4978,10 @@
         <v>168</v>
       </c>
       <c r="AN25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AO25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="2:41" x14ac:dyDescent="0.3">
@@ -4993,10 +4989,10 @@
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AL26" s="28">
         <v>10</v>
@@ -5014,7 +5010,7 @@
     </row>
     <row r="27" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AL27" s="28">
         <v>20</v>
@@ -5068,7 +5064,7 @@
     </row>
     <row r="30" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL30" s="28">
         <v>50</v>
@@ -5086,10 +5082,10 @@
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL31" s="12">
         <v>35</v>
@@ -5109,10 +5105,10 @@
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AL32" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AM32" s="16">
         <f>IF(AL31&gt;=35,17*AL31-330,7*AL31+15) * IF(AL31&gt;=25, 1 + (MIN(13,(AL31-18)/3.5) - 1) * (MIN(13,(AL31-18)/3.5)  - 1) / 100 + 0.05 * (MIN(13,(AL31-18)/3.5)  - 1),1)</f>
@@ -5121,7 +5117,7 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -15241,7 +15237,7 @@
         <v>126</v>
       </c>
       <c r="I2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -15255,43 +15251,43 @@
         <v>125</v>
       </c>
       <c r="J3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K3" t="s">
         <v>383</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>384</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>388</v>
+      </c>
+      <c r="N3" t="s">
+        <v>389</v>
+      </c>
+      <c r="O3" t="s">
+        <v>387</v>
+      </c>
+      <c r="P3" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q3" t="s">
         <v>385</v>
       </c>
-      <c r="M3" t="s">
-        <v>389</v>
-      </c>
-      <c r="N3" t="s">
-        <v>390</v>
-      </c>
-      <c r="O3" t="s">
-        <v>388</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
+        <v>393</v>
+      </c>
+      <c r="S3" t="s">
+        <v>394</v>
+      </c>
+      <c r="T3" t="s">
+        <v>386</v>
+      </c>
+      <c r="U3" t="s">
         <v>391</v>
       </c>
-      <c r="Q3" t="s">
-        <v>386</v>
-      </c>
-      <c r="R3" t="s">
-        <v>394</v>
-      </c>
-      <c r="S3" t="s">
-        <v>395</v>
-      </c>
-      <c r="T3" t="s">
-        <v>387</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>392</v>
-      </c>
-      <c r="V3" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -16104,13 +16100,13 @@
         <v>55000</v>
       </c>
       <c r="H24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J24" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.3">
@@ -16122,16 +16118,16 @@
         <v>60000</v>
       </c>
       <c r="I25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K25" t="s">
+        <v>496</v>
+      </c>
+      <c r="M25" t="s">
         <v>497</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
         <v>498</v>
-      </c>
-      <c r="O25" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.3">
@@ -16143,7 +16139,7 @@
         <v>65000</v>
       </c>
       <c r="J26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K26" t="str">
         <f>I25&amp;K25&amp;J26</f>
@@ -16167,7 +16163,7 @@
         <v>70000</v>
       </c>
       <c r="J27" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K27" t="str">
         <f>I25&amp;K25&amp;J27</f>
@@ -16191,7 +16187,7 @@
         <v>75000</v>
       </c>
       <c r="J28" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K28" t="str">
         <f>I25&amp;K25&amp;J28</f>
@@ -16215,7 +16211,7 @@
         <v>80000</v>
       </c>
       <c r="J29" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K29" t="str">
         <f>I25&amp;K25&amp;J29</f>
@@ -16239,7 +16235,7 @@
         <v>85000</v>
       </c>
       <c r="J30" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K30" t="str">
         <f>I25&amp;K25&amp;J30</f>
@@ -16263,16 +16259,16 @@
         <v>90000</v>
       </c>
       <c r="I31" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K31" t="s">
+        <v>496</v>
+      </c>
+      <c r="M31" t="s">
         <v>497</v>
       </c>
-      <c r="M31" t="s">
+      <c r="O31" t="s">
         <v>498</v>
-      </c>
-      <c r="O31" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.3">
@@ -16284,7 +16280,7 @@
         <v>95000</v>
       </c>
       <c r="J32" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K32" t="str">
         <f>I31&amp;K31&amp;J32</f>
@@ -16308,7 +16304,7 @@
         <v>100000</v>
       </c>
       <c r="J33" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K33" t="str">
         <f>I31&amp;K31&amp;J33</f>
@@ -16332,7 +16328,7 @@
         <v>105000</v>
       </c>
       <c r="J34" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K34" t="str">
         <f>I31&amp;K31&amp;J34</f>
@@ -16356,7 +16352,7 @@
         <v>110000</v>
       </c>
       <c r="J35" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K35" t="str">
         <f>I31&amp;K31&amp;J35</f>
@@ -16380,7 +16376,7 @@
         <v>115000</v>
       </c>
       <c r="J36" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K36" t="str">
         <f>I31&amp;K31&amp;J36</f>
@@ -16404,16 +16400,16 @@
         <v>120000</v>
       </c>
       <c r="I37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K37" t="s">
+        <v>496</v>
+      </c>
+      <c r="M37" t="s">
         <v>497</v>
       </c>
-      <c r="M37" t="s">
+      <c r="O37" t="s">
         <v>498</v>
-      </c>
-      <c r="O37" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.3">
@@ -16425,7 +16421,7 @@
         <v>125000</v>
       </c>
       <c r="J38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K38" t="str">
         <f>I37&amp;K37&amp;J38</f>
@@ -16449,7 +16445,7 @@
         <v>130000</v>
       </c>
       <c r="J39" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K39" t="str">
         <f>I37&amp;K37&amp;J39</f>
@@ -16473,7 +16469,7 @@
         <v>135000</v>
       </c>
       <c r="J40" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K40" t="str">
         <f>I37&amp;K37&amp;J40</f>
@@ -16497,7 +16493,7 @@
         <v>140000</v>
       </c>
       <c r="J41" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K41" t="str">
         <f>I37&amp;K37&amp;J41</f>
@@ -16521,7 +16517,7 @@
         <v>145000</v>
       </c>
       <c r="J42" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K42" t="str">
         <f>I37&amp;K37&amp;J42</f>
@@ -16545,16 +16541,16 @@
         <v>150000</v>
       </c>
       <c r="I43" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K43" t="s">
+        <v>496</v>
+      </c>
+      <c r="M43" t="s">
         <v>497</v>
       </c>
-      <c r="M43" t="s">
+      <c r="O43" t="s">
         <v>498</v>
-      </c>
-      <c r="O43" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.3">
@@ -16566,7 +16562,7 @@
         <v>155000</v>
       </c>
       <c r="J44" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K44" t="str">
         <f>I43&amp;K43&amp;J44</f>
@@ -16590,7 +16586,7 @@
         <v>160000</v>
       </c>
       <c r="J45" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K45" t="str">
         <f>I43&amp;K43&amp;J45</f>
@@ -16614,7 +16610,7 @@
         <v>165000</v>
       </c>
       <c r="J46" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K46" t="str">
         <f>I43&amp;K43&amp;J46</f>
@@ -16638,7 +16634,7 @@
         <v>170000</v>
       </c>
       <c r="J47" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K47" t="str">
         <f>I43&amp;K43&amp;J47</f>
@@ -16662,7 +16658,7 @@
         <v>175000</v>
       </c>
       <c r="J48" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K48" t="str">
         <f>I43&amp;K43&amp;J48</f>
@@ -16686,16 +16682,16 @@
         <v>180000</v>
       </c>
       <c r="I49" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K49" t="s">
+        <v>496</v>
+      </c>
+      <c r="M49" t="s">
         <v>497</v>
       </c>
-      <c r="M49" t="s">
+      <c r="O49" t="s">
         <v>498</v>
-      </c>
-      <c r="O49" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.3">
@@ -16707,7 +16703,7 @@
         <v>185000</v>
       </c>
       <c r="J50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K50" t="str">
         <f>I49&amp;K49&amp;J50</f>
@@ -16731,7 +16727,7 @@
         <v>190000</v>
       </c>
       <c r="J51" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K51" t="str">
         <f>I49&amp;K49&amp;J51</f>
@@ -16755,7 +16751,7 @@
         <v>195000</v>
       </c>
       <c r="J52" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K52" t="str">
         <f>I49&amp;K49&amp;J52</f>
@@ -16779,7 +16775,7 @@
         <v>200000</v>
       </c>
       <c r="J53" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K53" t="str">
         <f>I49&amp;K49&amp;J53</f>
@@ -16803,7 +16799,7 @@
         <v>205000</v>
       </c>
       <c r="J54" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K54" t="str">
         <f>I49&amp;K49&amp;J54</f>
@@ -16827,16 +16823,16 @@
         <v>210000</v>
       </c>
       <c r="I55" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K55" t="s">
+        <v>496</v>
+      </c>
+      <c r="M55" t="s">
         <v>497</v>
       </c>
-      <c r="M55" t="s">
+      <c r="O55" t="s">
         <v>498</v>
-      </c>
-      <c r="O55" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.3">
@@ -16848,7 +16844,7 @@
         <v>215000</v>
       </c>
       <c r="J56" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K56" t="str">
         <f>I55&amp;K55&amp;J56</f>
@@ -16872,7 +16868,7 @@
         <v>220000</v>
       </c>
       <c r="J57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K57" t="str">
         <f>I55&amp;K55&amp;J57</f>
@@ -16896,7 +16892,7 @@
         <v>225000</v>
       </c>
       <c r="J58" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K58" t="str">
         <f>I55&amp;K55&amp;J58</f>
@@ -16920,7 +16916,7 @@
         <v>250000</v>
       </c>
       <c r="J59" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K59" t="str">
         <f>I55&amp;K55&amp;J59</f>
@@ -16944,7 +16940,7 @@
         <v>275000</v>
       </c>
       <c r="J60" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K60" t="str">
         <f>I55&amp;K55&amp;J60</f>
@@ -17429,12 +17425,12 @@
   <sheetData>
     <row r="1" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C1" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
@@ -17536,7 +17532,7 @@
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
@@ -18407,7 +18403,7 @@
         <v>168</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>169</v>
@@ -18437,10 +18433,10 @@
         <v>154</v>
       </c>
       <c r="S2" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="T2" s="14" t="s">
         <v>397</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -18560,7 +18556,7 @@
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D5" s="3">
         <v>21</v>
@@ -18619,7 +18615,7 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -18933,7 +18929,7 @@
         <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -18949,7 +18945,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -18985,7 +18981,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>176</v>
@@ -19191,7 +19187,7 @@
         <v>235</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -19235,7 +19231,7 @@
         <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
@@ -19255,7 +19251,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.3">
@@ -19265,12 +19261,12 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -19312,7 +19308,7 @@
         <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H2" t="s">
         <v>36</v>
@@ -19376,41 +19372,41 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -19446,7 +19442,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -19561,7 +19557,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>31</v>
@@ -19608,10 +19604,10 @@
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" s="42" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -19623,7 +19619,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B594D0C1-9717-419C-89F7-CC28A4B63F17}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="11.75" customWidth="1"/>
@@ -19651,7 +19647,7 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>82</v>
@@ -19793,28 +19789,28 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -19932,7 +19928,7 @@
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">
@@ -19947,22 +19943,17 @@
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>130</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -20267,7 +20258,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
@@ -20499,7 +20490,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>224</v>
@@ -20720,7 +20711,7 @@
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="N27" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.3">
@@ -20791,7 +20782,7 @@
   <sheetData>
     <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>238</v>
@@ -20800,30 +20791,30 @@
         <v>239</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I2" s="33" t="s">
         <v>94</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D3" s="34">
         <v>1.5</v>
@@ -20860,7 +20851,7 @@
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D4" s="34">
         <v>4</v>
@@ -20897,7 +20888,7 @@
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" s="34">
         <v>4</v>
@@ -20934,7 +20925,7 @@
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D6" s="36">
         <v>1</v>
@@ -20974,50 +20965,50 @@
         <v>235</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D9" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D10" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I11" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="I12" s="33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J12" s="33" t="s">
         <v>223</v>
       </c>
       <c r="K12" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="L12" s="33" t="s">
         <v>348</v>
       </c>
-      <c r="L12" s="33" t="s">
-        <v>349</v>
-      </c>
       <c r="M12" s="35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H13" t="s">
         <v>87</v>
       </c>
       <c r="I13" s="46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J13" s="45">
         <v>20</v>
@@ -21036,19 +21027,19 @@
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D14" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="E14" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>406</v>
-      </c>
       <c r="F14" s="33" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J14" s="45">
         <v>0</v>
@@ -21067,13 +21058,13 @@
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E15" s="40">
         <v>1</v>
       </c>
       <c r="I15" s="46" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J15" s="45">
         <v>0</v>
@@ -21088,13 +21079,13 @@
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E16" s="40">
         <v>2</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J16" s="45">
         <v>0</v>
@@ -21109,13 +21100,13 @@
     </row>
     <row r="17" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E17" s="40">
         <v>3</v>
       </c>
       <c r="I17" s="46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J17" s="45">
         <v>0</v>
@@ -21130,16 +21121,16 @@
     </row>
     <row r="18" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E18" s="40">
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J18" s="45">
         <v>0</v>
@@ -21154,16 +21145,16 @@
     </row>
     <row r="19" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E19" s="40">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I19" s="46" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J19" s="45">
         <v>0</v>
@@ -21178,16 +21169,16 @@
     </row>
     <row r="20" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E20" s="40">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J20" s="45">
         <v>0</v>
@@ -21202,16 +21193,16 @@
     </row>
     <row r="21" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E21" s="40">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I21" s="46" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J21" s="45">
         <v>0</v>
@@ -21226,13 +21217,13 @@
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E22" s="40">
         <v>8</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J22" s="45">
         <v>0</v>
@@ -21247,7 +21238,7 @@
     </row>
     <row r="23" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E23" s="40">
         <v>9</v>
@@ -21255,13 +21246,13 @@
     </row>
     <row r="24" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
+        <v>415</v>
+      </c>
+      <c r="E24" s="43" t="s">
         <v>416</v>
       </c>
-      <c r="E24" s="43" t="s">
-        <v>417</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="4:16" x14ac:dyDescent="0.3">
@@ -21284,10 +21275,10 @@
         <v>223</v>
       </c>
       <c r="O25" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P25" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="4:16" x14ac:dyDescent="0.3">
@@ -21295,7 +21286,7 @@
         <v>87</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J26" s="45">
         <v>20</v>
@@ -21323,10 +21314,10 @@
     </row>
     <row r="27" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H27" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I27" s="46" t="s">
         <v>359</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>360</v>
       </c>
       <c r="J27" s="45">
         <v>0</v>
@@ -21354,7 +21345,7 @@
     </row>
     <row r="28" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I28" s="46" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J28" s="45">
         <v>0</v>
@@ -21378,7 +21369,7 @@
     </row>
     <row r="29" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I29" s="46" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J29" s="45">
         <v>0</v>
@@ -21402,7 +21393,7 @@
     </row>
     <row r="30" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I30" s="46" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J30" s="45">
         <v>0</v>
@@ -21426,7 +21417,7 @@
     </row>
     <row r="31" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I31" s="46" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J31" s="45">
         <v>0</v>
@@ -21450,7 +21441,7 @@
     </row>
     <row r="32" spans="4:16" x14ac:dyDescent="0.3">
       <c r="I32" s="46" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J32" s="45">
         <v>0</v>
@@ -21505,74 +21496,74 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="N1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C2" s="33" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F2" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="G2" s="33" t="s">
         <v>451</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="H2" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="J2" s="33" t="s">
         <v>452</v>
       </c>
-      <c r="H2" s="33" t="s">
-        <v>454</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>450</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>453</v>
-      </c>
       <c r="K2" s="33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N2" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="P2" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="O2" s="35" t="s">
-        <v>458</v>
-      </c>
-      <c r="P2" s="35" t="s">
+      <c r="Q2" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="R2" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="S2" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="Q2" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="R2" s="35" t="s">
+      <c r="T2" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="S2" s="35" t="s">
-        <v>461</v>
-      </c>
-      <c r="T2" s="35" t="s">
+      <c r="U2" s="35" t="s">
         <v>463</v>
-      </c>
-      <c r="U2" s="35" t="s">
-        <v>464</v>
       </c>
       <c r="V2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="W2" s="35" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C3" s="34">
         <v>1</v>
@@ -21647,7 +21638,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C4" s="34">
         <v>1</v>
@@ -21722,7 +21713,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C5" s="34">
         <v>3</v>
@@ -21797,7 +21788,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C6" s="34">
         <v>4</v>
@@ -21872,7 +21863,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C7" s="34">
         <v>5</v>
@@ -21947,7 +21938,7 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C8" s="36">
         <v>1</v>
@@ -22022,13 +22013,13 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>235</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -22038,7 +22029,7 @@
       <c r="B11" s="6"/>
       <c r="C11" s="24"/>
       <c r="D11" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -22047,32 +22038,32 @@
       </c>
       <c r="B12" s="15"/>
       <c r="D12" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D13" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D15" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="D16" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D17" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
@@ -22080,244 +22071,244 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="C20" s="35" t="s">
-        <v>406</v>
-      </c>
       <c r="D20" s="33" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C21" s="40">
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K21" s="40">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C22" s="40">
         <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K22" s="40">
         <v>1.5</v>
       </c>
       <c r="L22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C23" s="40">
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K23" s="40">
         <v>2</v>
       </c>
       <c r="L23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C24" s="40">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J24" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L24" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C25" s="40">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L25" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C26" s="40">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C27" s="40">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G27" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="H27" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="H27" s="35" t="s">
-        <v>406</v>
-      </c>
       <c r="J27" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K27" s="40">
         <v>9</v>
       </c>
       <c r="L27" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C28" s="40">
         <v>8</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H28" s="40">
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K28" s="40">
         <v>13</v>
       </c>
       <c r="L28" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C29" s="40">
         <v>9</v>
       </c>
       <c r="G29" s="42" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H29" s="40">
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K29" s="40">
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
+        <v>415</v>
+      </c>
+      <c r="C30" s="44" t="s">
         <v>416</v>
       </c>
-      <c r="C30" s="44" t="s">
-        <v>417</v>
-      </c>
       <c r="G30" s="42" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H30" s="40">
         <v>3</v>
       </c>
       <c r="J30" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K30" s="40">
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G31" s="42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H31" s="40">
         <v>4</v>
@@ -22325,36 +22316,36 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
+        <v>468</v>
+      </c>
+      <c r="C32" s="47" t="s">
         <v>469</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>470</v>
       </c>
       <c r="D32" s="44"/>
       <c r="G32" s="42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H32" s="40">
         <v>5</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="33" spans="7:11" x14ac:dyDescent="0.3">
       <c r="K33" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G34" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="35" spans="7:11" x14ac:dyDescent="0.3">

--- a/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
+++ b/0.说明文件与教程/武器-技能数值-价格-合成表填写的参考公式（修改后请勿上传git）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Steam\steamapps\common\CRAZYFLASHER7StandAloneStarter\project\CrazyFlashNight\0.说明文件与教程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF3B067-9A1D-45F4-8654-40627FCBDEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89790DB6-DD62-4625-9185-58030C88AE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="651" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="枪械" sheetId="12" r:id="rId1"/>
